--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$Q$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -542,6 +542,14 @@
           <t>Newmont Corporation</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$13,317.13M</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13317.13</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>800-1066 Hastings St W</t>
@@ -589,7 +597,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png</t>
+          <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png; chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -614,6 +622,14 @@
           <t>Teck Resources Limited</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$7,654.78M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7654.78</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -631,7 +647,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png</t>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -656,6 +672,14 @@
           <t>First Quantum Minerals Ltd</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$4,802M</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4802</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -673,7 +697,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png</t>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -692,8 +716,2843 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lundin Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$3,422.6M</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3422.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B2Gold Corp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$3,061.24M</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3061.24</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pan American Silver Corp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$2,818.9M</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2818.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Yamana Gold Inc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$2,482.29M</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2482.29</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capstone Copper Corp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>$2,359.89M</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2359.89</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wheaton Precious Metals Corp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$2,314.6M</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2314.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Equinox Gold Corp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$1,514.12M</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1514.12</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Eldorado Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$1,322.58M</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1322.58</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OceanaGold Corporation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$1,294M</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1294</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EVR Operations Limited</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$1,247.07M</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1247.07</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lundin Gold Inc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$1,193.05M</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1193.05</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-01.png</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fortuna Mining Corp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$1,062.04M</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1062.04</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Atlatsa Resources Corporation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$867.07M</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>867.0700000000001</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ero Copper Corp</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$785.84M</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>785.84</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China Gold International Resources Corp Ltd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$756.65M</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>756.65</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>International Petroleum Corporation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$685.89M</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>685.89</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Artemis Gold Inc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$650.43M</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Goldcorp Canada Ltd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$588.28M</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>588.28</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Calibre Mining Corp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$585.86M</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>585.86</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Meren Energy Inc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$562.1M</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>562.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>First Majestic Silver Corp</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$560.6M</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>560.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aris Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$510.6M</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Imperial Metals Corporation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$492.32M</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>492.32</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Endeavour Silver Corp</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$467.5M</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Northgate Minerals Corporation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$434.82M</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>434.82</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-02.png</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Asante Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$433.95M</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>433.95</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>$433.47M</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>433.47</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Petaquilla Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>$428.17M</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>428.17</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>K92 Mining Inc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>$350.62M</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>350.62</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Leagold Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$346.83M</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>346.83</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Orla Mining Ltd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>$343.92M</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>343.92</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Silvermex Resources Inc</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>$329.48M</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>329.48</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Teck Highland Valley Copper Partnership</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>$319.72M</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nevsun Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>$314.6M</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Silvercorp Metals Inc</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>$298.89M</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>298.89</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Target Exploration and Mining Corp</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>$286.51M</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>286.51</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Orezone Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>$283.52M</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>283.52</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SantaCruz Silver Mining Ltd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>$282.99M</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>282.99</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aris Mining Holdings Corp</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>$269.79M</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>269.79</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Steppe Gold Ltd</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>$254.13M</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>254.13</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-03.png</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Newmont Canada Corporation</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>$248.31M</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>248.31</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Teck-Bullmoose Coal Inc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>$242.22M</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>242.22</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Huckleberry Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>$238.75M</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Continental Minerals Corporation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>$238.75M</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Azure Resources Corporation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>$238.75M</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cache Exploration Inc</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>$236.37M</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>236.37</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Galiano Gold Inc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>$231.34M</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>231.34</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-04.png</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Trevali Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>$227.64M</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>227.64</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Amerigo Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>$227.32M</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>227.32</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aurcana Silver Corporation</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>$207.72M</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>207.72</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Osino Resources Corp</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>$198.17M</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>198.17</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Thor Explorations Ltd</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>$193.13M</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>193.13</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SRK Consulting (Canada) Inc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>$191M</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>191</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sunward Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>$186.23M</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>186.23</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bear Creek Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>$181.45M</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>17411979 Canada Inc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>$176.28M</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>176.28</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ridgetop Forwarding Ltd.</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>$159.97M</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>159.97</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lucara Diamond Corp</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>$159.66M</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>159.66</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Puna Operations Inc</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>$143.49M</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>143.49</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Pretium Exploration Inc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>$127.89M</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>127.89</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>New Guinea Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>$121.76M</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>121.76</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Queen's Road Capital Investment Ltd</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>$120.16M</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rockgate Capital Corp</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>$119.38M</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>119.38</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-05-05.png</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q4"/>
+  <autoFilter ref="A1:Q67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$Q$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$S$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -440,13 +440,15 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="62" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,35 +504,45 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>contact_email</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>contact_phone</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>website</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>industry_tags</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>company_description</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>date_captured</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -580,37 +592,37 @@
           <t>Natascha Viljoen</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>www.newmont.com</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Metal Ore Mining; Mining (except Oil and Gas); Mining, Quarrying, and Oil and Gas Extraction; Gold bullion production</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Newmont Corporation is a gold producer and also engaged in the production of copper, silver, lead and zinc. The Company's world-class portfolio of assets, prospects and talent is anchored in favorable mining jurisdictions in Africa, Australia, Latin America &amp; Caribbean, North America, and Papua New Guinea.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png; chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>ILLEGIBLE: revenue_raw — SALES REVENUE column obscured by D&amp;B live-chat widget overlay; CONFLICT: province=British Columbia|BC (chat-example-detail-newmont-01.png); key_principal_title blank — no title printed next to Key Principal. Revenue on this page is behind a lock icon (paywalled), as expected. industry_tags: first three are links, 'Gold bullion production' is printed as plain text. Detail page prints province as 'BC'; listing prints 'British Columbia'.</t>
         </is>
@@ -645,24 +657,39 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Investor Relations (general — no named individual published on contact page)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>investors@teck.com</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.877.759.6226 (toll-free Canada/US); 604.699.4257 (outside Canada/US)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.teck.com/investors/contact-us/</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>listing_only</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>ILLEGIBLE: revenue_raw — SALES REVENUE column obscured by D&amp;B live-chat widget overlay</t>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ILLEGIBLE: revenue_raw — SALES REVENUE column obscured by D&amp;B live-chat widget overlay; ILLEGIBLE: street_address — Vancouver HQ address not present in static HTML (site footer renders address via JavaScript, not fetched).</t>
         </is>
       </c>
     </row>
@@ -680,6 +707,11 @@
       <c r="C4" t="n">
         <v>4802</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1133 Melville Street, Suite 3500, The Stack</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -690,29 +722,49 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>V6E 4E5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bonita To</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Director, Investor Relations</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+1 416 361 6400 (International); +1 877 961 6400 (Toll Free)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.first-quantum.com/contact/</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>listing_only</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>ILLEGIBLE: revenue_raw — value partially covered by the floating phone-number button; only a trailing fragment is visible and partial numbers are not transcribed</t>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ILLEGIBLE: revenue_raw — value partially covered by the floating phone-number button; only a trailing fragment is visible and partial numbers are not transcribed; CONFLICT: province=British Columbia|BC (https://www.first-quantum.com/contact/); ILLEGIBLE: contact_email for Bonita To — no personal email published on official contact page; only phone. General website inquiries: website@fqml.com.</t>
         </is>
       </c>
     </row>
@@ -730,6 +782,11 @@
       <c r="C5" t="n">
         <v>3422.6</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1055 Dunsmuir Street, Suite 2800, Four Bentall Centre</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -740,24 +797,59 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>V7X 1L2</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>chat-listing-2026-08-05-01.png</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Stephen Williams</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Vice President, Investor Relations</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>stephen.williams@lundinmining.com</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>+1 604 806-3074 (direct); +1 604 689-7842 (general office)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>www.lundinmining.com</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.lundinmining.com/about/contact/</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.lundinmining.com/about/contact/)</t>
         </is>
       </c>
     </row>
@@ -790,17 +882,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -835,17 +927,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -880,17 +972,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -925,17 +1017,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -970,17 +1062,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1015,17 +1107,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1060,17 +1152,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1105,17 +1197,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1150,17 +1242,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1195,17 +1287,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1240,17 +1332,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1285,17 +1377,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1330,17 +1422,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1375,17 +1467,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1420,17 +1512,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1465,17 +1557,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1510,17 +1602,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1555,17 +1647,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1600,17 +1692,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1645,17 +1737,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1690,17 +1782,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1735,17 +1827,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1780,17 +1872,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1825,17 +1917,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1870,17 +1962,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1915,17 +2007,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -1960,17 +2052,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2005,17 +2097,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2050,17 +2142,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2095,17 +2187,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2140,17 +2232,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2185,17 +2277,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2230,17 +2322,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2275,17 +2367,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2320,17 +2412,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2365,17 +2457,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2410,17 +2502,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2455,17 +2547,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2500,17 +2592,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2545,17 +2637,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2590,17 +2682,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2635,17 +2727,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2680,17 +2772,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2725,17 +2817,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2770,17 +2862,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2815,17 +2907,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2860,17 +2952,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2905,17 +2997,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2950,17 +3042,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -2995,17 +3087,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3040,17 +3132,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3085,17 +3177,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3130,17 +3222,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3175,17 +3267,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3220,17 +3312,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3265,17 +3357,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3310,17 +3402,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3355,17 +3447,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3400,17 +3492,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3445,17 +3537,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3490,17 +3582,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -3535,24 +3627,24 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q67"/>
+  <autoFilter ref="A1:S67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -912,6 +912,11 @@
       <c r="C7" t="n">
         <v>2818.9</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vancouver Centre II, 2100-733 Seymour Street</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -922,14 +927,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>V6B 0S6</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Siren Fisekci</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>V.P. Investor Relations and Corporate Communications</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>+1 (604) 806-3191 (direct); +1 (604) 684-1175 (general office)</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://panamericansilver.com/about/contact/</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -939,7 +964,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://panamericansilver.com/about/contact/); ILLEGIBLE: contact_email — page uses email obfuscation (renders as '*protected email*' in fetched HTML rather than an address); not decoded.</t>
         </is>
       </c>
     </row>
@@ -974,7 +1004,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; yamana.com (not fetched)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -984,7 +1014,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>REVIEW: yamana.com's TLS certificate has expired — declined to connect (no TLS bypass attempted). Yamana Gold was acquired jointly by Pan American Silver and Agnico Eagle in 2023; this entity may no longer be an independently operating company. Recommend manual verification of current status before treating as an active prospect.</t>
         </is>
       </c>
     </row>
@@ -1002,6 +1037,11 @@
       <c r="C9" t="n">
         <v>2359.89</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Suite 2100 – 510 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1012,14 +1052,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>V6B 0M3</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>604-684-8894 (general); 866-684-8894 (toll-free)</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://capstonecopper.com/contact-us/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1029,7 +1079,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://capstonecopper.com/contact-us/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder in fetched HTML); not decoded. No named contact published on this page.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1119,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.wheatonpm.com/contact/ (blocked)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1074,7 +1129,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ILLEGIBLE: contact_email, contact_phone — wheatonpm.com contact page returned an active Cloudflare bot-challenge (cf-mitigated: challenge); not bypassed.</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1152,11 @@
       <c r="C11" t="n">
         <v>1514.12</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Suite 1501 – 700 West Pender Street</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1102,14 +1167,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Etienne Morin</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Chief Capital Markets Officer</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>etienne.morin@equinoxgold.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>+1 604-260-0516 (direct); +1 604-558-0560 (general); 1-833-EQX-GOLD (toll-free)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>www.equinoxgold.com</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.equinoxgold.com/contact/</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1119,7 +1214,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.equinoxgold.com/contact/); General public email also available: info@equinoxgold.com.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -1237,6 +1237,11 @@
       <c r="C12" t="n">
         <v>1322.58</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>550 Burrard Street, 11th Floor</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1247,14 +1252,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>V6C 2B5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Lynette Gould</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VP, Investor Relations</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>lynette.gould@eldoradogold.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>647.271.2827 or 1.888.353.8166</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>www.eldoradogold.com</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1264,7 +1299,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker)); Live fetch of eldoradogold.com/contact-us returned 403; this data comes from a search-engine snippet of that same official page, not an independent third-party source. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -1282,6 +1322,11 @@
       <c r="C13" t="n">
         <v>1294</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Suite 1020, 400 Burrard Street</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1292,14 +1337,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>V6C 3A6</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>IR@oceanagold.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>+1 604 678 4123</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>www.oceanagold.com</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://oceanagold.com/contact-us</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1309,7 +1374,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://oceanagold.com/contact-us); General public IR email/phone used; no named individual confirmed on the official contact page itself (named contacts surfaced only in unverified search snippets, not used).</t>
         </is>
       </c>
     </row>
@@ -1342,9 +1412,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>info@evr.com</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>236.484.2200</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>www.evr.com</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.glencore.ca/en/evr</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1354,7 +1439,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>EVR Operations (Elk Valley Resources) is a Glencore subsidiary. Site describes a new Vancouver headquarters but does not publish a street address on this page; ILLEGIBLE: street_address.</t>
         </is>
       </c>
     </row>
@@ -1372,6 +1462,11 @@
       <c r="C15" t="n">
         <v>1193.05</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Suite 2800, Four Bentall Centre, 1055 Dunsmuir Street</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1382,14 +1477,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>V7X 1L2</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>info@lundingold.com</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>(604) 689-7842; toll-free 1-888-689-7842</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>www.lundingold.com</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; https://lundingold.com/contact/</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1399,7 +1514,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://lundingold.com/contact/); General public email/phone used; a named VP Investor Relations (Brendan Creaney) appeared in search results but was not present on the official contact or corporate-information pages checked, so not recorded.</t>
         </is>
       </c>
     </row>
@@ -1417,6 +1537,11 @@
       <c r="C16" t="n">
         <v>1062.04</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1111 Melville Street, Suite 820</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1427,14 +1552,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>V6E 3V6</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>info@fmcmail.com</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>+1.604.484.4085; toll free +1.866.719.8962</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>www.fortunamining.com</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1444,7 +1589,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1629,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; SEC 6-K filing + secondary sources (not fetched directly)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1489,7 +1639,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>REVIEW: Atlatsa underwent a 'going private' restructuring in 2018-2019 and is now headquartered in Sandton, South Africa per available records; the Vancouver address in the D&amp;B listing may be a stale registered/agent address rather than an active operating office. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -1507,6 +1662,11 @@
       <c r="C18" t="n">
         <v>785.84</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1050 – 625 Howe Street</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1517,14 +1677,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>V6C 2T6</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>info@ero.com</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>+1-604-449-9244</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>www.ero.com</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.ero.com/contact-us/</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1534,7 +1714,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.ero.com/contact-us/); No named IR contact published on the official contact page.</t>
         </is>
       </c>
     </row>
@@ -1552,6 +1737,11 @@
       <c r="C19" t="n">
         <v>756.65</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Suite 1780, Commerce Place, 400 Burrard St</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1562,14 +1752,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>V6C 3A6</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>604-609-0598 (general); 604-695-5031 (Investor Relations)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>www.chinagoldintl.com</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.chinagoldintl.com/contact/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1579,7 +1784,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.chinagoldintl.com/contact/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -1807,6 +1807,11 @@
       <c r="C20" t="n">
         <v>685.89</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Suite 2800, 1055 Dunsmuir Street</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1817,14 +1822,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>V7X 1L2</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>+1 604 689 7842</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>www.international-petroleum.com</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.international-petroleum.com/contact-us</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1834,7 +1854,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.international-petroleum.com/contact-us); No email or named contact published on the official contact page; phone only.</t>
         </is>
       </c>
     </row>
@@ -1852,6 +1877,11 @@
       <c r="C21" t="n">
         <v>650.4299999999999</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Suite 3083, 595 Burrard St.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1862,14 +1892,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>V7X 1L3</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>+1 (604) 558-1107; toll free 1-888-955-9362</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>www.artemisgoldinc.com</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.artemisgoldinc.com/contact/contact-details/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1879,7 +1924,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.artemisgoldinc.com/contact/contact-details/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1964,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1924,7 +1974,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2014,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.calibremining.com/ (301 redirect)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1969,7 +2024,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>REVIEW: calibremining.com now 301-redirects to equinoxgold.com — Calibre Mining has merged into Equinox Gold Corp, which is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -1987,6 +2047,11 @@
       <c r="C24" t="n">
         <v>562.1</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>c/o Suite 2500, 666 Burrard Street</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1997,14 +2062,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>V6C 2X8</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>info@mereninc.com</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>+44 20 8017 1511</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>www.mereninc.com</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://mereninc.com/contact-us/</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2014,7 +2099,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://mereninc.com/contact-us/); General public email used; no named individual confirmed on the official contact page itself. Phone number is a UK line — no Canadian direct line published.</t>
         </is>
       </c>
     </row>
@@ -2032,6 +2122,11 @@
       <c r="C25" t="n">
         <v>560.6</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1800 - 925 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2042,14 +2137,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>V6C 3L2</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>info@firstmajestic.com</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>604.688.3033; toll-free 1.866.529.2807</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>www.firstmajestic.com</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.firstmajestic.com/contact/contact-details/</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2059,7 +2174,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.firstmajestic.com/contact/contact-details/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
       </c>
     </row>
@@ -2077,6 +2197,11 @@
       <c r="C26" t="n">
         <v>510.6</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>550 Burrard Street, Suite 2900</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2087,14 +2212,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>V6C 0A3</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>info@aris-mining.com</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>www.aris-mining.com</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://aris-mining.com/contact-us/</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2104,7 +2244,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://aris-mining.com/contact-us/); General public email used; no Vancouver phone number published on the official contact page (only a Colombia office phone). No named individual confirmed.</t>
         </is>
       </c>
     </row>
@@ -2122,6 +2267,11 @@
       <c r="C27" t="n">
         <v>492.32</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>580 Hornby Street, Suite 900</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2132,14 +2282,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>V6C 3B6</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>investor@imperialmetals.com</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>604.488.2657 (shareholder inquiries); 604.669.8959 (general)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>imperialmetals.com</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; https://imperialmetals.com/contact/</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2149,7 +2319,12 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://imperialmetals.com/contact/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -2342,6 +2342,11 @@
       <c r="C28" t="n">
         <v>467.5</v>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Suite 1130 - 609 Granville Street</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2357,9 +2362,34 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Allison Pettit</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Vice President of Investor Relations</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>apettit@edrsilver.com</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>(877) 685-9775</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>www.edrsilver.com</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2369,7 +2399,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403 (generic WAF deny, not a robots/ToS block); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2439,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png</t>
+          <t>chat-listing-2026-08-05-02.png; secondary sources (AuRico Gold acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2414,7 +2449,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>REVIEW: Northgate Minerals was acquired by and amalgamated into AuRico Gold in October 2011 (a historical transaction); AuRico itself later merged with Alamos Gold in 2015. This entity has not existed independently for over a decade — the D&amp;B listing entry is almost certainly stale/historical, not a current Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -2432,6 +2472,11 @@
       <c r="C30" t="n">
         <v>433.95</v>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Suite 1150, 1100 Melville Street</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2442,14 +2487,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>V6E 4A6</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>info@asantegold.com</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>(+1) 604 558 1134</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>www.asantegold.com</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://asantegold.com/contact</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2459,7 +2524,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://asantegold.com/contact); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
       </c>
     </row>
@@ -2477,6 +2547,11 @@
       <c r="C31" t="n">
         <v>433.47</v>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12th Floor, 1040 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2487,14 +2562,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>V6E 4H1</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>info@trekormetals.com</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>(778) 373-4533</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>www.trekormetals.com</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2504,7 +2599,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.trekormetals.com/contact/); Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2639,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (National Observer, SEC filings — not fetched directly)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2549,7 +2649,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>REVIEW: Petaquilla Minerals was delisted from the TSX in 2015, abandoned its only mine (Molejon, Panama) the same year, and by public reporting its listed phone/email were already disconnected years ago. Treat this D&amp;B listing entry as stale/inactive, not a current Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -2567,6 +2672,11 @@
       <c r="C33" t="n">
         <v>350.62</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Suite 488, 1090 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2577,14 +2687,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>V6E 3V7</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>David Medilek</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ir@k92mining.com</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>+1-604-416-4445</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>www.k92mining.com</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://k92mining.com/contact/</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2594,7 +2734,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://k92mining.com/contact/)</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2774,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (merger press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2639,7 +2784,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>REVIEW: Leagold Mining merged into Equinox Gold Corp in March 2020 and was delisted; Equinox Gold is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -2657,6 +2807,11 @@
       <c r="C35" t="n">
         <v>343.92</v>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Suite 2020, 666 Burrard St.</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2667,14 +2822,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>V6C 2X8</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>info@orlamining.com</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>604-564-1852</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>www.orlamining.com</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2684,7 +2859,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)); Live fetch of the contact page 404'd (URL structure differs from what search results implied); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2899,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2729,7 +2909,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -2747,6 +2932,11 @@
       <c r="C37" t="n">
         <v>319.72</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>P.O. Box 1500</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2757,14 +2947,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>V0K 1W0</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>250.523.2443</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (teck.com project pages, not fetched directly)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2774,7 +2974,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Logan Lake (secondary sources (teck.com project pages, not fetched directly)); CONFLICT: province=British Columbia|BC (secondary sources (teck.com project pages, not fetched directly)); REVIEW: this is a Teck Resources operating partnership for the Highland Valley Copper mine near Logan Lake, BC — not a Vancouver office, and not separately contactable from Teck Resources Limited (already a row in this workbook). The D&amp;B listing's Vancouver location likely reflects Teck's corporate HQ, not this operation's actual site address.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -3014,7 +3014,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (Zijin Mining acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3024,7 +3024,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>REVIEW: Nevsun Resources was fully acquired by Zijin Mining in a compulsory acquisition completed March 2019 and delisted; it has been a wholly-owned Zijin subsidiary for years. The D&amp;B listing entry is almost certainly stale, not a current independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -3042,6 +3047,11 @@
       <c r="C39" t="n">
         <v>298.89</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Suite 1750, 1066 W. Hastings Street</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3052,14 +3062,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>investor@silvercorp.ca</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>604-669-9397; toll-free 1-888-224-1881</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>www.silvercorpmetals.com</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://silvercorpmetals.com/contact-details/</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3069,7 +3099,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://silvercorpmetals.com/contact-details/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3139,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; opengovca.com Vancouver business licence listing (not the company's own site; no official site located)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3114,7 +3149,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>REVIEW: could not locate an active official company website. Secondary sources describe it as formerly 'Leicester Diamond Mines' and reference an acquisition/merger. Likely an inactive shell or renamed entity; recommend manual verification before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -3132,6 +3172,11 @@
       <c r="C41" t="n">
         <v>283.52</v>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>450-505 Burrard Street</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3142,14 +3187,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>V7X 1M3</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>info@orezone.com</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>+1 778-945-8977</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>www.orezone.com</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://orezone.com/contact/</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3159,7 +3224,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://orezone.com/contact/); General public email used; no named individual confirmed on the official contact page itself (a Kevin MacKenzie, VP Corporate Development and IR, appeared in older search results but was not present on the current official contact page, so not recorded).</t>
         </is>
       </c>
     </row>
@@ -3177,6 +3247,11 @@
       <c r="C42" t="n">
         <v>282.99</v>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Suite 480, 1140 West Pender St.</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3187,14 +3262,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>V6E 4G1</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Arturo Préstamo</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Executive Chairman &amp; CEO</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>info@santacruzsilver.com</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1-888-883-2011 (Canada office); +52 81 83 785707 (Mexico line listed alongside the CEO's name)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>www.santacruzsilver.com</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; https://santacruzsilver.com/contact/contact-information/</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3204,7 +3309,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://santacruzsilver.com/contact/contact-information/); The CEO's contact block on the official page lists a Mexico phone number and the general info@ email rather than a personal address/direct Vancouver line — recorded as published, not inferred further.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3349,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (Fasken/Aris Mining corporate history, not fetched directly)</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3249,7 +3359,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>REVIEW: Aris Mining Holdings Corp is a wholly-owned subsidiary formed in the 2022 Aris Gold/GCM Mining amalgamation; the parent, Aris Mining Corporation, is already a separate row in this workbook (same Vancouver office). Recommend treating this as the same entity rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -3267,6 +3382,11 @@
       <c r="C44" t="n">
         <v>254.13</v>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Suite 248, 1489 Marine Dr</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>West Vancouver</t>
@@ -3277,14 +3397,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>V7T 1B8</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Aneel Waraich</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>EVP and Director</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>aneel@steppegold.com</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>+1 (604) 926 7739</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>www.steppegold.com</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png</t>
+          <t>chat-listing-2026-08-05-03.png; steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3294,7 +3444,12 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)); Live fetch of the contact page did not surface an address/phone block (possibly rendered via JS); data sourced from a search-engine snippet referencing the company's own site. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3529,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (mine closure reporting, not fetched directly)</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3384,7 +3539,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>REVIEW: the Bullmoose coal mine near Tumbler Ridge, BC closed in 2000. This entity has had no active operations for a quarter century; the D&amp;B listing entry is stale. Any current contact would route through Teck Resources Limited (already a row in this workbook).</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3579,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (Imperial Metals operational updates, not fetched directly)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3429,7 +3589,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>REVIEW: Huckleberry Mines Ltd is a wholly-owned Imperial Metals Corporation subsidiary; the Huckleberry mine has been on care-and-maintenance (inactive) since August 2016. Imperial Metals Corporation is already a separate row in this workbook with the same Vancouver office — recommend treating this as the same entity rather than an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3629,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (Jinchuan Group acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3474,7 +3639,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>REVIEW: Continental Minerals Corporation was acquired by Jinchuan Group in April 2011 and delisted. This entity has not existed independently for over a decade; the D&amp;B listing entry is stale.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -3679,7 +3679,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; no active official website located</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -3689,7 +3689,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>REVIEW: no current official website could be located; search results returned only an unrelated Australia-based 'Azure Minerals' and generic mining directory listings. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3729,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; cacheexploration.com (domain no longer belongs to the company)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3734,7 +3739,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>REVIEW: cacheexploration.com has been taken over/squatted — it now serves unrelated online-casino affiliate content (7Bit, Bitstarz, Jackbit, etc.), not the mining company. Did not use this domain for anything. No current verified official site located; recommend manual verification.</t>
         </is>
       </c>
     </row>
@@ -3752,6 +3762,11 @@
       <c r="C51" t="n">
         <v>231.34</v>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Suite 1640, 1066 West Hastings</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3762,14 +3777,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>(604) 683-8193; toll-free 1-855-246-7341</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>www.galianogold.com</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3779,7 +3809,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3849,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; cfcanada.fticonsulting.com/trevali (court-appointed receiver's case site, not fetched directly)</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -3824,7 +3859,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>REVIEW: Trevali entered CCAA insolvency proceedings in August 2022 and its Caribou Mine assets went into receivership under FTI Consulting in 2023, with sale agreements finalized in 2024. This is not a going-concern Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -3842,6 +3882,11 @@
       <c r="C53" t="n">
         <v>227.32</v>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The MNP Tower, 1021 West Hastings Street, 9th floor</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3852,14 +3897,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>V6E 0C3</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Aurora Davidson</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>604-697-6207 (President &amp; CEO direct line); 604-681-2802 (general office)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>www.amerigoresources.com</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://www.amerigoresources.com/company/contact/</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -3869,7 +3939,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.amerigoresources.com/company/contact/); ILLEGIBLE: contact_email — both the general and CEO email addresses render as obfuscated placeholders in the fetched HTML; not decoded.</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3979,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://www.aurcana.com/ (fetched directly; data quality concerns noted below)</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -3914,7 +3989,12 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>REVIEW: aurcana.com's contact page shows a stale 2016 copyright footer and a Victoria, BC address, conflicting with third-party sources citing a Vancouver address — and the homepage's most recent news item is from November 2022 (director/officer resignation, TSX-V tier downgrade). Site appears dormant. Declined to record an address/phone that may be years out of date; recommend manual verification.</t>
         </is>
       </c>
     </row>
@@ -3932,6 +4012,11 @@
       <c r="C55" t="n">
         <v>198.17</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Suite 810, 789 West Pender Street</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3942,14 +4027,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>V6C 1H2</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Julia Becker</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Manager, Investor Relations</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>jbecker@osinoresources.com</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>+1 (604) 785 0850</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>www.osinoresources.com</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://osinoresources.com/contact-3/</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -3959,7 +4074,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://osinoresources.com/contact-3/)</t>
         </is>
       </c>
     </row>
@@ -3977,6 +4097,11 @@
       <c r="C56" t="n">
         <v>193.13</v>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>#404 – 119 West Pender Street</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3987,14 +4112,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>V6B 1S5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>+1-778-658-6391</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>www.thorexpl.com</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://thorexpl.com/contact-us/</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4004,7 +4144,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://thorexpl.com/contact-us/); No email published on the official contact page (IR handled externally by Fig House Communications per other pages, not a company-owned address). No named individual confirmed on this page.</t>
         </is>
       </c>
     </row>
@@ -4022,6 +4167,11 @@
       <c r="C57" t="n">
         <v>191</v>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1066 Hastings St W, Suite 2200</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4032,14 +4182,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>V6E 3X2</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>vancouver@srk.com</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>+1 604 681 4196</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>www.srk.com</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; srk.com/en/contact-us/vancouver (live fetch returned a page whose address block renders via JavaScript; sourced from a search-engine snippet of the same official page)</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4049,7 +4219,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (srk.com/en/contact-us/vancouver (live fetch returned a page whose address block renders via JavaScript; sourced from a search-engine snippet of the same official page)); Live fetch succeeded (200) but the address/phone block is client-side rendered and not present in the static HTML; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4259,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; secondary sources (NovaCopper/Trilogy Metals acquisition news, not fetched directly)</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4094,7 +4269,12 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>REVIEW: Sunward Resources became a wholly-owned subsidiary of NovaCopper Inc. (now Trilogy Metals) via a 2015 plan of arrangement. Not an independently operating Vancouver prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -3484,7 +3484,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (Newmont/Goldcorp merger reporting, not fetched directly)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3494,7 +3494,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>REVIEW: Newmont Canada Corporation appears to be the same Vancouver office/entity as Newmont Corporation (already a separate row in this workbook, verified with a Vancouver address and contact information), reflecting Newmont's Canadian corporate structure post-Goldcorp merger rather than a distinct company. Recommend treating as the same physical office as Newmont Corporation.</t>
         </is>
       </c>
     </row>
@@ -4292,6 +4297,11 @@
       <c r="C59" t="n">
         <v>181.45</v>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Suite 3200, 733 Seymour Street</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4302,14 +4312,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>V6B 0S6</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Barbara Henderson</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>VP Corporate Communications</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>barb@bearcreekmining.com</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>(604) 628-1111</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>www.bearcreekmining.com</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://bearcreekmining.com/investors/contact/contact-us/</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4319,7 +4359,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://bearcreekmining.com/investors/contact/contact-us/)</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4399,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; no official site or public record located</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4364,7 +4409,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a generic federal numbered company (Canada Business Corporations Act); no official website, news coverage, or public registry detail was located under this number. Numbered companies are frequently shell/holding entities without a public presence. Recommend manual verification via Corporations Canada before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4449,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; no verified official site located</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4409,7 +4459,12 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>REVIEW: no evidence found connecting this name to a mining company — search results returned only unrelated Vancouver freight-forwarding/logistics listings. The name and business type suggest this D&amp;B listing entry may be a logistics/customs-forwarding company misclassified under the mining NAICS code, not an actual mining prospect. Recommend manual verification.</t>
         </is>
       </c>
     </row>
@@ -4427,6 +4482,11 @@
       <c r="C62" t="n">
         <v>159.66</v>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Suite 2800, Four Bentall Centre, 1055 Dunsmuir Street</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4437,14 +4497,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>V7X 1L2</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>info@lucaradiamond.com</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>+1 604 674 0272</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>www.lucaradiamond.com</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://lucaradiamond.com/contact/contact-info/</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4454,7 +4534,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://lucaradiamond.com/contact/contact-info/); General public email used for both general and Investor Relations inquiries on the official page; no distinct personal contact confirmed there.</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4574,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; secondary sources (SEC filings, BNamericas — not fetched directly, no official standalone site located)</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -4499,7 +4584,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>REVIEW: sources conflict on ownership (one describes this as an SSR Mining venture, others associate it with Pan American Silver's Argentina operations). No standalone official website was located. Recommend manual verification of current ownership/contact before treating as an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4624,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; secondary sources (Newcrest acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -4544,7 +4634,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>REVIEW: Pretium Resources (Brucejack mine) was fully acquired by Newcrest Mining in March 2022 and delisted; Newcrest itself was subsequently acquired by Newmont in 2023. Newmont Corporation is already a separate row in this workbook. Not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4674,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; secondary sources (Yahoo Finance, Northern Miner — not fetched directly)</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4589,7 +4684,12 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>REVIEW: available sources describe this company as headquartered in Brisbane, Australia, not Vancouver, with its most recent located news dating to 2013. The D&amp;B listing's Vancouver location could not be corroborated; likely stale or a registered-agent address only. Recommend manual verification.</t>
         </is>
       </c>
     </row>
@@ -4607,6 +4707,11 @@
       <c r="C66" t="n">
         <v>120.16</v>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Cheung Kong Centre, Suite 2006, 2 Queen's Road Central</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4622,9 +4727,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>info@queensrdcapital.com</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>queensrdcapital.com</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; https://queensrdcapital.com/contact/offices/</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4634,7 +4749,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Hong Kong (https://queensrdcapital.com/contact/offices/); CONFLICT: country=Canada|Hong Kong (https://queensrdcapital.com/contact/offices/); REVIEW: the company's own official 'Offices' page lists only a Hong Kong address — no Vancouver office is published anywhere on the site. This directly conflicts with the D&amp;B listing's Vancouver location. Recorded the verified Hong Kong address rather than inferring a Canadian one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4789,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-05.png</t>
+          <t>chat-listing-2026-08-05-05.png; secondary sources (acquisition history, not fetched directly)</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -4679,7 +4799,12 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>REVIEW: Rockgate Capital Corp was acquired by Denison Mines in 2013 and no longer exists as an independent entity. The D&amp;B listing entry is stale, over a decade old.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$S$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$S$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4808,8 +4808,1718 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Trident Resources Corp.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>$116.99M</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Magellan Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>$116.99M</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HIVE Digital Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>$115.28M</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>115.28</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mcilvenna Bay Operating Ltd</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>$115.1M</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Queenstake Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>$115.1M</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Shamaran Petroleum Corp</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>$109.39M</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>109.39</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Copper Mountain Mining Inc</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>$106.15M</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Veris Gold Corp</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>$105.12M</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>105.12</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Luca Mining Corp</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>$104.09M</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Klondex Mines Unlimited Liability Company</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>$102.31M</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Monument Mining Limited</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>$98.64M</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Pretium Resources Inc</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>$92.08M</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mako Mining Corp</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>$92.08M</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-04.png</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Central Sun Mining Inc</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>$89.52M</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Energold Drilling Corp</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>$89.52M</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0908113 B.C. Ltd</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>$83.56M</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Atlantic Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>$78.9M</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato Silver Company Ltd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>$75.66M</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Titan Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>$74.24M</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hemisphere Energy Corporation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>$71.24M</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TAAT Global Alternatives Inc</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>$70M</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>70</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Atico Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>$68.46M</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Uranium Energy Corp</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>$66.84M</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>66.84</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Elevation Gold Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>$66.36M</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Avino Silver &amp; Gold Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>$66.18M</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MineSense Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>$65.48M</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oromin Explorations Ltd</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>$64.71M</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-01.png</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Eskay Creek Mining Ltd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>$63.94M</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Eastern Platinum Limited</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>$62.51M</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Soma Gold Corp</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>$62.09M</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Golden Queen Mining Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>$57.04M</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>North American Tungsten Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>$52.95M</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Hemlo Mining Corp</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>$51.41M</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Newcastle Gold Ltd</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>$50.14M</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Alio Gold Inc</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>$47.57M</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NG Energy International Corp</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>$44.61M</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>enCore Energy Corp</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>$43.16M</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Lion One Metals Limited</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>$42.21M</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S67"/>
+  <autoFilter ref="A1:S105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -4822,6 +4822,11 @@
       <c r="C68" t="n">
         <v>116.99</v>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>505 Burrard Street, Suite 1030</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4832,14 +4837,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>V7X 1M5</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Lubica Keighery</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>IR and Corporate Development</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Lubica.keighery@tridentresourcescorp.com</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>+1 778 889 5476 (direct); (604) 687-3376 (general office)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>www.tridentresourcescorp.com</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; https://www.tridentresourcescorp.com/corporate/overview/</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4849,7 +4884,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.tridentresourcescorp.com/corporate/overview/); Recently rebranded from Rockridge/MAS Gold/Eros three-way consolidation (2025); currently active Saskatchewan gold exploration company.</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4924,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; magellanminerals.com (domain redirects to a parking-page lander)</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -4894,7 +4934,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>REVIEW: magellanminerals.com now redirects to a generic domain-parking lander page, indicating the company's official web presence has lapsed. Search results conflict — one 2016 report describes an acquisition by Anfield Nickel Corp, while other secondary sources reference 2026 news activity — but no live official site could be verified. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -4912,6 +4957,11 @@
       <c r="C70" t="n">
         <v>115.28</v>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>789 W Pender Street, Suite 855</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -4922,14 +4972,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>V6C 1H2</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>info@hivedigitaltech.com</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>604-664-1078</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>www.hivedigitaltechnologies.com</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; https://www.hivedigitaltechnologies.com/contact (email/phone fetched directly; street address sourced from a search-engine snippet of the same official site, not present on the contact page itself)</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4939,7 +5009,12 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.hivedigitaltechnologies.com/contact (email/phone fetched directly; street address sourced from a search-engine snippet of the same official site, not present on the contact page itself)); Email and phone confirmed via direct fetch. Address not shown on the fetched contact page; sourced from search snippet instead. Recommend re-verifying the address directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -4974,7 +5049,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (Foran Mining / Eldorado Gold acquisition reporting, not fetched directly)</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -4984,7 +5059,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>REVIEW: McIlvenna Bay is a copper project operated by Foran Mining Corporation, which was itself acquired by Eldorado Gold in April 2026 (Eldorado Gold is already a separate row in this workbook). This is a mine-site operating entity, not an independent Vancouver corporate office.</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5099,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (SEC filings, acquisition history, not fetched directly)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5029,7 +5109,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>REVIEW: Queenstake Resources was acquired by Veris Gold in 2007; Veris Gold itself filed for bankruptcy in 2014 and is now inactive. This entity has been defunct for close to two decades — the D&amp;B listing entry is stale.</t>
         </is>
       </c>
     </row>
@@ -5047,6 +5132,11 @@
       <c r="C73" t="n">
         <v>109.39</v>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1055 Dunsmuir Street, Suite 2800</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5057,14 +5147,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>V7X 1L2</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>info@shamaranpetroleum.com</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>+1-604-689-7842</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>www.shamaranpetroleum.com</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; https://shamaranpetroleum.com/contact/contact-info/</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -5074,7 +5184,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>CONFLICT: company_name=Shamaran Petroleum Corp|ShaMaran Petroleum Corp (https://shamaranpetroleum.com/contact/contact-info/); CONFLICT: province=British Columbia|BC (https://shamaranpetroleum.com/contact/contact-info/); The only named Investor Relations contact published (Robert Eriksson) is based in Sweden, not Vancouver, so a Canadian general email/phone was used instead. Shares the same Vancouver registered-office building (1055 Dunsmuir Street) as several other Lundin-family companies already in this workbook — a known registered-agent-suite pattern, not an error.</t>
         </is>
       </c>
     </row>
@@ -5092,6 +5207,11 @@
       <c r="C74" t="n">
         <v>106.15</v>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>700 West Pender Street, Suite 1700</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5102,14 +5222,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>www.cumtn.com</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; cumtn.com/investors/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -5119,7 +5249,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (cumtn.com/investors/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; address sourced from a search-engine snippet of the same official domain, no email/phone surfaced in that snippet. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5289,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (SEC/bankruptcy court filings, not fetched directly)</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -5164,7 +5299,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>REVIEW: Veris Gold filed for Chapter 15 bankruptcy in 2014; its Jerritt Canyon assets were sold off in 2015 and the bankruptcy case formally closed in 2018. This is an inactive BC corporation with no current operations.</t>
         </is>
       </c>
     </row>
@@ -5182,6 +5322,11 @@
       <c r="C76" t="n">
         <v>104.09</v>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1111 Melville Street, Suite 410</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5192,14 +5337,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>V6E 3V6</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ir@lucamining.com</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>+1-604-684-8071</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>www.lucamining.com</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; https://lucamining.com/contact/</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -5209,7 +5374,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://lucamining.com/contact/)</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5414,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (Hecla Mining acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -5254,7 +5424,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>REVIEW: Klondex Mines was acquired by Hecla Mining in July 2018 (Nevada assets); its Canadian operations were spun off separately into Havilah Mining Corp, which is not in this workbook. Klondex has not existed independently since 2018.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -5447,6 +5447,11 @@
       <c r="C78" t="n">
         <v>98.64</v>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Suite 1580, 1100 Melville Street</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5457,14 +5462,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>V6E 4A6</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>info@monumentmining.com</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>+1 604 638 1661</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>www.monumentmining.com</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; https://monumentmining.com/contact/</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -5474,7 +5499,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://monumentmining.com/contact/); General public email used; a named IR contact (Richard Cushing) appeared in search results but was not present on the official contact page itself, so not recorded.</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5539,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (Newcrest acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -5519,7 +5549,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>REVIEW: same entity/history already flagged for 'Pretium Exploration Inc' in an earlier batch — Pretium Resources (Brucejack mine) was acquired by Newcrest Mining in March 2022 and delisted; Newcrest itself was acquired by Newmont in 2023 (Newmont Corporation is already a row in this workbook). Not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -5537,6 +5572,11 @@
       <c r="C80" t="n">
         <v>92.08</v>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>838 W Hastings St, Suite 700</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5547,14 +5587,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>V6C 0A6</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>www.makomining.com</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png</t>
+          <t>chat-listing-2026-08-06-04.png; makomining.com/contact/ (live fetch 403'd; address sourced from a search-engine snippet of the company's own official site)</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -5564,7 +5614,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (makomining.com/contact/ (live fetch 403'd; address sourced from a search-engine snippet of the company's own official site)); Live fetch returned 403; no email/phone surfaced in the available search snippet. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5654,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (federalcorporation.ca, OSC records — not fetched directly)</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -5609,7 +5664,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>REVIEW: this entity's status is recorded as 'Inactive - Amalgamated,' its registered office is in Toronto (not Vancouver), and it voluntarily surrendered its BC reporting-issuer status back in 2009. The D&amp;B listing's Vancouver location does not reflect current reality; this is not a live prospect.</t>
         </is>
       </c>
     </row>
@@ -5627,6 +5687,11 @@
       <c r="C82" t="n">
         <v>89.52</v>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Suite 802, 750 West Pender St.</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5637,14 +5702,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>V6C 2T8</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Marco Garrido</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Energold Americas contact</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>mgarrido@energold.com</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>+1 (604) 681-9501</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>www.energold.com</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://energold.com/contact/</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -5654,7 +5749,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://energold.com/contact/); Company now operates under the 'Energold Group' brand at this domain.</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5789,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (Capstone Copper/Orion joint-venture press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -5699,7 +5799,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a wholly-owned Capstone Copper Corp subsidiary (the 'JVCo' vehicle for the Santo Domingo project, in which Capstone sold a 25% interest to Orion in 2025). Capstone Copper Corp is already a verified row in this workbook with the same Vancouver office. Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5839,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (St Barbara Limited acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -5744,7 +5849,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>REVIEW: Atlantic Gold was fully acquired by St Barbara Limited (Australia) in July 2019, delisted from the TSX-V, and ceased to be a reporting issuer. It is now a wholly-owned Australian subsidiary operating the Moose River Consolidated project in Nova Scotia — not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -5762,6 +5872,11 @@
       <c r="C85" t="n">
         <v>75.66</v>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Suite 578, 999 Canada Place</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5772,14 +5887,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>V6C 3E1</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>+1 (778) 989-5346</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>www.gsilver.com</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://www.gsilver.com/contact</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -5789,7 +5919,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.gsilver.com/contact); ILLEGIBLE: contact_email — page uses JavaScript-based spambot protection instead of a plain-text address; not decoded.</t>
         </is>
       </c>
     </row>
@@ -5822,9 +5957,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>info@titanminingcorp.com</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>604-687-1717</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>www.titanminingcorp.com</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://www.titanminingcorp.com/contact/contact-details/</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -5834,7 +5984,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.titanminingcorp.com/contact/contact-details/); ILLEGIBLE: street_address — the fetched contact page only lists the company's US mine-site address (Gouverneur, NY) alongside a Canadian phone/email; the Vancouver street address (999 Canada Place, per third-party sources) was not present on this official page, so not recorded to avoid mixing sourced and unsourced data.</t>
         </is>
       </c>
     </row>
@@ -5852,6 +6007,11 @@
       <c r="C87" t="n">
         <v>71.23999999999999</v>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Suite 501, 905 West Pender Street</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5862,14 +6022,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>V6C 1L6</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>landrequests@hemisphereenergy.ca</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>(604) 685-9255</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>www.hemisphereenergy.ca</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://www.hemisphereenergy.ca/contact</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -5879,7 +6059,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.hemisphereenergy.ca/contact); The official contact page publishes only department-specific addresses (Accounts Payable, Surface and Mineral Land inquiries) rather than a general info@ address; recorded the land/surface-inquiries address as the closest general-purpose contact. No named individual confirmed.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -6099,7 +6099,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; taatglobal.com (checked; not a mining company)</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -6109,7 +6109,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>REVIEW: TAAT Global Alternatives makes tobacco-free/nicotine-free cigarette alternatives — a consumer products company, not a mining company. This D&amp;B listing entry appears to be misclassified under the mining NAICS code, similar to Ridgetop Forwarding flagged earlier. Not a mining prospect.</t>
         </is>
       </c>
     </row>
@@ -6127,6 +6132,11 @@
       <c r="C89" t="n">
         <v>68.45999999999999</v>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>543 Granville St., Suite 501</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6137,14 +6147,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>V6C 1X8</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Igor Dutina</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Corporate Development</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>+1.604-633-9022</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>www.aticomining.com</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://aticomining.com/contact-us/contact-information/</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -6154,7 +6189,12 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://aticomining.com/contact-us/contact-information/); ILLEGIBLE: contact_email — no email published alongside the named Corporate Development contact on the official page.</t>
         </is>
       </c>
     </row>
@@ -6172,6 +6212,11 @@
       <c r="C90" t="n">
         <v>66.84</v>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1188 West Georgia Street, Suite 1830</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6182,14 +6227,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>V6E 4A2</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>604 682-9775; toll free 1-866-748-1030</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>www.uraniumenergy.com</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://www.uraniumenergy.com/contact</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -6199,7 +6259,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.uraniumenergy.com/contact); This is UEC's Vancouver office; the company's actual corporate headquarters is in Corpus Christi, Texas. No email published for the Vancouver office specifically.</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6299,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (BC Securities Commission reporting-issuer list, not fetched directly)</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -6244,7 +6309,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>REVIEW: the BC Securities Commission lists this company as 'In Default' as of September 3, 2024. Recommend manual verification of current operating status before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -6262,6 +6332,11 @@
       <c r="C92" t="n">
         <v>66.18000000000001</v>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>570 Granville Street, Suite 900</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6272,14 +6347,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>V6C 3P1</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Jennifer North</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Head of Investor Relations</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ir@avino.com</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>604-682-3701</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>www.avino.com</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; https://avino.com/contact</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -6289,7 +6394,12 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://avino.com/contact)</t>
         </is>
       </c>
     </row>
@@ -6307,6 +6417,11 @@
       <c r="C93" t="n">
         <v>65.48</v>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>100 – 8365 Ontario Street</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6317,14 +6432,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>V5X 3E8</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>info@minesense.com</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>+1.604.449.3780</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>www.minesense.com</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; minesense.com/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official site)</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -6334,7 +6469,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (minesense.com/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official site)); Live fetch returned 403; data sourced from a search-engine snippet of the same official domain. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6509,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (SEC filings, Mergr ownership records, not fetched directly)</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -6379,7 +6519,12 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>REVIEW: Oromin Explorations was acquired by Teranga Gold Corporation in 2013 (its Sabodala/OJVG assets in Senegal). Not an independent Vancouver prospect for well over a decade.</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6559,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (BC Environmental Assessment Office filings, Skeena Resources SEC filings, not fetched directly)</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -6424,7 +6569,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a wholly-owned, permit-holding subsidiary of Skeena Resources Ltd (which holds the Eskay Creek gold-silver project in the Golden Triangle). Skeena Resources itself is not currently a row in this workbook. This entity is a project vehicle, not an independent Vancouver corporate office — recommend adding Skeena Resources Ltd as the actual contactable entity if this project is of interest.</t>
         </is>
       </c>
     </row>
@@ -6442,6 +6592,11 @@
       <c r="C96" t="n">
         <v>62.51</v>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1188 West Georgia Street, Suite 1080</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6452,14 +6607,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>V6E 4A2</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>info@eastplats.com</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>+1 604 568-8200</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>www.eastplats.com</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; https://www.eastplats.com/contacts/</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -6469,7 +6644,12 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.eastplats.com/contacts/)</t>
         </is>
       </c>
     </row>
@@ -6487,6 +6667,11 @@
       <c r="C97" t="n">
         <v>62.09</v>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>409 Granville Street, Suite 1500</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6497,14 +6682,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>V6C 1T2</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>info@somagoldcorp.com</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>(604) 259-0302</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>www.somagoldcorp.com</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; https://somagoldcorp.com/contact/</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -6514,7 +6719,12 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://somagoldcorp.com/contact/)</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6759,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (acquisition/delisting press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -6559,7 +6769,12 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>REVIEW: Golden Queen Mining delisted from the TSX in 2019 and was acquired by Falco Resources in March 2020, becoming a private company. Not an independent, publicly-contactable Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6809,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (CCAA insolvency records, not fetched directly)</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -6604,7 +6819,12 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>REVIEW: this company entered CCAA creditor protection in 2015 and its head office closed effective December 31, 2015, with all inquiries redirected to court-appointed monitor Alvarez &amp; Marsal Canada. The Cantung Mine remains on care and maintenance. Not an active Vancouver office.</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; hemlomining.com (site loaded but is a JavaScript single-page app; no static contact page found at common paths)</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -6649,7 +6869,12 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a very recently renamed entity (formerly Carcetti Capital Corp, which completed its Hemlo gold mine acquisition from Barrick on November 26, 2025). Sources conflict on head office location (Vancouver vs. Toronto), and the live site's contact page could not be located via static fetch. Recommend manual verification given how new this entity is.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6909,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png</t>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (Equinox Gold formation press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -6694,7 +6919,12 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>REVIEW: Newcastle Gold merged with Trek Mining and Anfield Gold in December 2017 to form Equinox Gold Corp, and was delisted. Equinox Gold Corp is already a verified row in this workbook. Not an independent entity.</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6959,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png</t>
+          <t>chat-listing-2026-08-06-03.png; secondary sources (Argonaut Gold merger press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -6739,7 +6969,12 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>REVIEW: Alio Gold merged into Argonaut Gold in July 2020 and was delisted from both the TSX and NYSE American. Not an independent entity for six years.</t>
         </is>
       </c>
     </row>
@@ -6757,6 +6992,11 @@
       <c r="C103" t="n">
         <v>44.61</v>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5940 MacLeod Trail SW, Suite 321</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6772,9 +7012,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>www.ngenergyintl.com</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png</t>
+          <t>chat-listing-2026-08-06-03.png; https://www.ngenergyintl.com/contact/contact-details/</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -6784,7 +7029,12 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Calgary (https://www.ngenergyintl.com/contact/contact-details/); CONFLICT: province=British Columbia|AB (https://www.ngenergyintl.com/contact/contact-details/); REVIEW: the company's own official contact page lists its Canadian office in Calgary, Alberta — not Vancouver — directly conflicting with the D&amp;B listing. Email on this page is obfuscated. Recorded the verified Calgary address rather than a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
         </is>
       </c>
     </row>
@@ -6802,6 +7052,11 @@
       <c r="C104" t="n">
         <v>43.16</v>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>13355 Noel Road, Suite 1700</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6817,9 +7072,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>info@encoreuranium.com</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>(647) 847-7825</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>www.encoreuranium.com</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png</t>
+          <t>chat-listing-2026-08-06-03.png; https://encoreuranium.com/corporate/corporate-directory/</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -6829,7 +7099,12 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Dallas (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: province=British Columbia|TX (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: country=Canada|United States (https://encoreuranium.com/corporate/corporate-directory/); REVIEW: the company's own official corporate directory lists its head office in Dallas, Texas. The only Vancouver address on the page (510 Burrard Street) belongs to Computershare, enCore's third-party transfer agent — not an enCore office. Recorded the verified Dallas head office rather than inferring a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
         </is>
       </c>
     </row>
@@ -6847,6 +7122,11 @@
       <c r="C105" t="n">
         <v>42.21</v>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>267 West Esplanade, Suite 306</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>North Vancouver</t>
@@ -6857,14 +7137,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>V7M 1A5</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>info@liononemetals.com</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>1-855-805-1250</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>www.liononemetals.com</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png</t>
+          <t>chat-listing-2026-08-06-03.png; https://liononemetals.com/contact/contact-info/</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -6874,7 +7174,12 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://liononemetals.com/contact/contact-info/); A newly appointed VP Corporate Development and Investor Relations (Ronan Geoghegan, per search results, appointed July 2026) was not present on the official contact page itself, so not recorded.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -1947,6 +1947,11 @@
       <c r="C22" t="n">
         <v>588.28</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>800-1066 Hastings St W</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -1957,6 +1962,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -1964,7 +1974,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1974,12 +1984,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.</t>
+          <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as acquirer Newmont Corporation (acquired Goldcorp in 2019). Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -2882,6 +2892,11 @@
       <c r="C36" t="n">
         <v>329.48</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1800 - 925 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -2892,6 +2907,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>V6C 3L2</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -2899,7 +2919,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly); derived from First Majestic Silver Corp's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2909,12 +2929,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.</t>
+          <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from First Majestic Silver Corp's verified address (already a row in this workbook)); Same registered office as acquirer First Majestic Silver Corp (acquired Silvermex in 2012). Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -3332,6 +3352,11 @@
       <c r="C43" t="n">
         <v>269.79</v>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>550 Burrard Street, Suite 2900</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3342,6 +3367,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>V6C 0A3</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -3349,7 +3379,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (Fasken/Aris Mining corporate history, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (Fasken/Aris Mining corporate history, not fetched directly); derived from Aris Mining Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3359,12 +3389,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>REVIEW: Aris Mining Holdings Corp is a wholly-owned subsidiary formed in the 2022 Aris Gold/GCM Mining amalgamation; the parent, Aris Mining Corporation, is already a separate row in this workbook (same Vancouver office). Recommend treating this as the same entity rather than an independent prospect.</t>
+          <t>REVIEW: Aris Mining Holdings Corp is a wholly-owned subsidiary formed in the 2022 Aris Gold/GCM Mining amalgamation; the parent, Aris Mining Corporation, is already a separate row in this workbook (same Vancouver office). Recommend treating this as the same entity rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Aris Mining Corporation's verified address (already a row in this workbook)); Same registered office as parent Aris Mining Corporation. Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -3467,6 +3497,11 @@
       <c r="C45" t="n">
         <v>248.31</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>800-1066 Hastings St W</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>North Vancouver</t>
@@ -3477,6 +3512,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -3484,7 +3524,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png; secondary sources (Newmont/Goldcorp merger reporting, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (Newmont/Goldcorp merger reporting, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3494,12 +3534,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>REVIEW: Newmont Canada Corporation appears to be the same Vancouver office/entity as Newmont Corporation (already a separate row in this workbook, verified with a Vancouver address and contact information), reflecting Newmont's Canadian corporate structure post-Goldcorp merger rather than a distinct company. Recommend treating as the same physical office as Newmont Corporation.</t>
+          <t>REVIEW: Newmont Canada Corporation appears to be the same Vancouver office/entity as Newmont Corporation (already a separate row in this workbook, verified with a Vancouver address and contact information), reflecting Newmont's Canadian corporate structure post-Goldcorp merger rather than a distinct company. Recommend treating as the same physical office as Newmont Corporation.; CONFLICT: city=North Vancouver|Vancouver (derived from Newmont Corporation's verified address (already a row in this workbook)); CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as Newmont Corporation — reflects Newmont's Canadian corporate structure, not a distinct physical office.</t>
         </is>
       </c>
     </row>
@@ -3567,6 +3607,11 @@
       <c r="C47" t="n">
         <v>238.75</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>580 Hornby Street, Suite 900</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -3577,6 +3622,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>V6C 3B6</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -3584,7 +3634,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png; secondary sources (Imperial Metals operational updates, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-04.png; secondary sources (Imperial Metals operational updates, not fetched directly); derived from Imperial Metals Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3594,12 +3644,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>REVIEW: Huckleberry Mines Ltd is a wholly-owned Imperial Metals Corporation subsidiary; the Huckleberry mine has been on care-and-maintenance (inactive) since August 2016. Imperial Metals Corporation is already a separate row in this workbook with the same Vancouver office — recommend treating this as the same entity rather than an independent prospect.</t>
+          <t>REVIEW: Huckleberry Mines Ltd is a wholly-owned Imperial Metals Corporation subsidiary; the Huckleberry mine has been on care-and-maintenance (inactive) since August 2016. Imperial Metals Corporation is already a separate row in this workbook with the same Vancouver office — recommend treating this as the same entity rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Imperial Metals Corporation's verified address (already a row in this workbook)); Same registered office as parent Imperial Metals Corporation. Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -5032,6 +5082,11 @@
       <c r="C71" t="n">
         <v>115.1</v>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>550 Burrard Street, 11th Floor</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5042,6 +5097,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>V6C 2B5</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -5049,7 +5109,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-04.png; secondary sources (Foran Mining / Eldorado Gold acquisition reporting, not fetched directly)</t>
+          <t>chat-listing-2026-08-06-04.png; secondary sources (Foran Mining / Eldorado Gold acquisition reporting, not fetched directly); derived from Eldorado Gold Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -5059,12 +5119,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>REVIEW: McIlvenna Bay is a copper project operated by Foran Mining Corporation, which was itself acquired by Eldorado Gold in April 2026 (Eldorado Gold is already a separate row in this workbook). This is a mine-site operating entity, not an independent Vancouver corporate office.</t>
+          <t>REVIEW: McIlvenna Bay is a copper project operated by Foran Mining Corporation, which was itself acquired by Eldorado Gold in April 2026 (Eldorado Gold is already a separate row in this workbook). This is a mine-site operating entity, not an independent Vancouver corporate office.; CONFLICT: province=British Columbia|BC (derived from Eldorado Gold Corporation's verified address (already a row in this workbook)); Same registered office as parent Eldorado Gold Corporation (via its 2026 acquisition of Foran Mining, which held McIlvenna Bay). Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -5772,6 +5832,11 @@
       <c r="C83" t="n">
         <v>83.56</v>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Suite 2100 – 510 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -5782,6 +5847,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>V6B 0M3</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -5789,7 +5859,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-01.png; secondary sources (Capstone Copper/Orion joint-venture press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-06-01.png; secondary sources (Capstone Copper/Orion joint-venture press releases, not fetched directly); derived from Capstone Copper Corp's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -5799,12 +5869,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>REVIEW: this is a wholly-owned Capstone Copper Corp subsidiary (the 'JVCo' vehicle for the Santo Domingo project, in which Capstone sold a 25% interest to Orion in 2025). Capstone Copper Corp is already a verified row in this workbook with the same Vancouver office. Not an independent prospect.</t>
+          <t>REVIEW: this is a wholly-owned Capstone Copper Corp subsidiary (the 'JVCo' vehicle for the Santo Domingo project, in which Capstone sold a 25% interest to Orion in 2025). Capstone Copper Corp is already a verified row in this workbook with the same Vancouver office. Not an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Capstone Copper Corp's verified address (already a row in this workbook)); Same registered office as parent Capstone Copper Corp (this entity is Capstone's 'JVCo' vehicle for the Santo Domingo project). Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>
@@ -6892,6 +6962,11 @@
       <c r="C101" t="n">
         <v>50.14</v>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Suite 1501 – 700 West Pender Street</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -6902,6 +6977,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -6909,7 +6989,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png; secondary sources (Equinox Gold formation press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (Equinox Gold formation press releases, not fetched directly); derived from Equinox Gold Corp's verified address (already a row in this workbook)</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -6919,12 +6999,12 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>REVIEW: Newcastle Gold merged with Trek Mining and Anfield Gold in December 2017 to form Equinox Gold Corp, and was delisted. Equinox Gold Corp is already a verified row in this workbook. Not an independent entity.</t>
+          <t>REVIEW: Newcastle Gold merged with Trek Mining and Anfield Gold in December 2017 to form Equinox Gold Corp, and was delisted. Equinox Gold Corp is already a verified row in this workbook. Not an independent entity.; CONFLICT: province=British Columbia|BC (derived from Equinox Gold Corp's verified address (already a row in this workbook)); Same registered office as Equinox Gold Corp, formed from the 2017 merger of Newcastle Gold, Anfield Gold, and Trek Mining. Not independently verified as this entity's own filed address.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$S$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S105"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -445,10 +445,12 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="46" customWidth="1" min="14" max="14"/>
     <col width="62" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,20 +531,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>recent_news</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>news_source_urls</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>date_captured</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -607,22 +619,22 @@
           <t>Newmont Corporation is a gold producer and also engaged in the production of copper, silver, lead and zinc. The Company's world-class portfolio of assets, prospects and talent is anchored in favorable mining jurisdictions in Africa, Australia, Latin America &amp; Caribbean, North America, and Papua New Guinea.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png; chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>ILLEGIBLE: revenue_raw — SALES REVENUE column obscured by D&amp;B live-chat widget overlay; CONFLICT: province=British Columbia|BC (chat-example-detail-newmont-01.png); key_principal_title blank — no title printed next to Key Principal. Revenue on this page is behind a lock icon (paywalled), as expected. industry_tags: first three are links, 'Gold bullion production' is printed as plain text. Detail page prints province as 'BC'; listing prints 'British Columbia'.</t>
         </is>
@@ -672,22 +684,22 @@
           <t>1.877.759.6226 (toll-free Canada/US); 604.699.4257 (outside Canada/US)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.teck.com/investors/contact-us/</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>ILLEGIBLE: revenue_raw — SALES REVENUE column obscured by D&amp;B live-chat widget overlay; ILLEGIBLE: street_address — Vancouver HQ address not present in static HTML (site footer renders address via JavaScript, not fetched).</t>
         </is>
@@ -747,22 +759,22 @@
           <t>+1 416 361 6400 (International); +1 877 961 6400 (Toll Free)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.first-quantum.com/contact/</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>ILLEGIBLE: revenue_raw — value partially covered by the floating phone-number button; only a trailing fragment is visible and partial numbers are not transcribed; CONFLICT: province=British Columbia|BC (https://www.first-quantum.com/contact/); ILLEGIBLE: contact_email for Bonita To — no personal email published on official contact page; only phone. General website inquiries: website@fqml.com.</t>
         </is>
@@ -832,22 +844,22 @@
           <t>www.lundinmining.com</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://www.lundinmining.com/about/contact/</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.lundinmining.com/about/contact/)</t>
         </is>
@@ -882,17 +894,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>listing_only</t>
         </is>
@@ -952,22 +964,22 @@
           <t>+1 (604) 806-3191 (direct); +1 (604) 684-1175 (general office)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://panamericansilver.com/about/contact/</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://panamericansilver.com/about/contact/); ILLEGIBLE: contact_email — page uses email obfuscation (renders as '*protected email*' in fetched HTML rather than an address); not decoded.</t>
         </is>
@@ -1002,22 +1014,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; yamana.com (not fetched)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>REVIEW: yamana.com's TLS certificate has expired — declined to connect (no TLS bypass attempted). Yamana Gold was acquired jointly by Pan American Silver and Agnico Eagle in 2023; this entity may no longer be an independently operating company. Recommend manual verification of current status before treating as an active prospect.</t>
         </is>
@@ -1067,22 +1079,22 @@
           <t>604-684-8894 (general); 866-684-8894 (toll-free)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://capstonecopper.com/contact-us/</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://capstonecopper.com/contact-us/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder in fetched HTML); not decoded. No named contact published on this page.</t>
         </is>
@@ -1117,22 +1129,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://www.wheatonpm.com/contact/ (blocked)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>ILLEGIBLE: contact_email, contact_phone — wheatonpm.com contact page returned an active Cloudflare bot-challenge (cf-mitigated: challenge); not bypassed.</t>
         </is>
@@ -1202,22 +1214,22 @@
           <t>www.equinoxgold.com</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://www.equinoxgold.com/contact/</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.equinoxgold.com/contact/); General public email also available: info@equinoxgold.com.</t>
         </is>
@@ -1287,22 +1299,22 @@
           <t>www.eldoradogold.com</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker)); Live fetch of eldoradogold.com/contact-us returned 403; this data comes from a search-engine snippet of that same official page, not an independent third-party source. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -1362,22 +1374,22 @@
           <t>www.oceanagold.com</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://oceanagold.com/contact-us</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://oceanagold.com/contact-us); General public IR email/phone used; no named individual confirmed on the official contact page itself (named contacts surfaced only in unverified search snippets, not used).</t>
         </is>
@@ -1427,22 +1439,22 @@
           <t>www.evr.com</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://www.glencore.ca/en/evr</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>EVR Operations (Elk Valley Resources) is a Glencore subsidiary. Site describes a new Vancouver headquarters but does not publish a street address on this page; ILLEGIBLE: street_address.</t>
         </is>
@@ -1502,22 +1514,22 @@
           <t>www.lundingold.com</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-01.png; https://lundingold.com/contact/</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://lundingold.com/contact/); General public email/phone used; a named VP Investor Relations (Brendan Creaney) appeared in search results but was not present on the official contact or corporate-information pages checked, so not recorded.</t>
         </is>
@@ -1577,22 +1589,22 @@
           <t>www.fortunamining.com</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -1627,22 +1639,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; SEC 6-K filing + secondary sources (not fetched directly)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>REVIEW: Atlatsa underwent a 'going private' restructuring in 2018-2019 and is now headquartered in Sandton, South Africa per available records; the Vancouver address in the D&amp;B listing may be a stale registered/agent address rather than an active operating office. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
@@ -1702,22 +1714,22 @@
           <t>www.ero.com</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.ero.com/contact-us/</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.ero.com/contact-us/); No named IR contact published on the official contact page.</t>
         </is>
@@ -1772,22 +1784,22 @@
           <t>www.chinagoldintl.com</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.chinagoldintl.com/contact/</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.chinagoldintl.com/contact/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
         </is>
@@ -1842,22 +1854,22 @@
           <t>www.international-petroleum.com</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.international-petroleum.com/contact-us</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.international-petroleum.com/contact-us); No email or named contact published on the official contact page; phone only.</t>
         </is>
@@ -1912,22 +1924,22 @@
           <t>www.artemisgoldinc.com</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.artemisgoldinc.com/contact/contact-details/</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.artemisgoldinc.com/contact/contact-details/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
         </is>
@@ -1972,22 +1984,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as acquirer Newmont Corporation (acquired Goldcorp in 2019). Not independently verified as this entity's own filed address.</t>
         </is>
@@ -2022,22 +2034,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.calibremining.com/ (301 redirect)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>REVIEW: calibremining.com now 301-redirects to equinoxgold.com — Calibre Mining has merged into Equinox Gold Corp, which is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.</t>
         </is>
@@ -2097,22 +2109,22 @@
           <t>www.mereninc.com</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://mereninc.com/contact-us/</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://mereninc.com/contact-us/); General public email used; no named individual confirmed on the official contact page itself. Phone number is a UK line — no Canadian direct line published.</t>
         </is>
@@ -2172,22 +2184,22 @@
           <t>www.firstmajestic.com</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://www.firstmajestic.com/contact/contact-details/</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.firstmajestic.com/contact/contact-details/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
@@ -2242,22 +2254,22 @@
           <t>www.aris-mining.com</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://aris-mining.com/contact-us/</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://aris-mining.com/contact-us/); General public email used; no Vancouver phone number published on the official contact page (only a Colombia office phone). No named individual confirmed.</t>
         </is>
@@ -2317,22 +2329,22 @@
           <t>imperialmetals.com</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; https://imperialmetals.com/contact/</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://imperialmetals.com/contact/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
@@ -2397,22 +2409,22 @@
           <t>www.edrsilver.com</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403 (generic WAF deny, not a robots/ToS block); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -2447,22 +2459,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-02.png; secondary sources (AuRico Gold acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>REVIEW: Northgate Minerals was acquired by and amalgamated into AuRico Gold in October 2011 (a historical transaction); AuRico itself later merged with Alamos Gold in 2015. This entity has not existed independently for over a decade — the D&amp;B listing entry is almost certainly stale/historical, not a current Vancouver prospect.</t>
         </is>
@@ -2522,22 +2534,22 @@
           <t>www.asantegold.com</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://asantegold.com/contact</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://asantegold.com/contact); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
@@ -2597,22 +2609,22 @@
           <t>www.trekormetals.com</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.trekormetals.com/contact/); Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.</t>
         </is>
@@ -2647,22 +2659,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (National Observer, SEC filings — not fetched directly)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>REVIEW: Petaquilla Minerals was delisted from the TSX in 2015, abandoned its only mine (Molejon, Panama) the same year, and by public reporting its listed phone/email were already disconnected years ago. Treat this D&amp;B listing entry as stale/inactive, not a current Vancouver prospect.</t>
         </is>
@@ -2732,22 +2744,22 @@
           <t>www.k92mining.com</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://k92mining.com/contact/</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://k92mining.com/contact/)</t>
         </is>
@@ -2782,22 +2794,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (merger press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>REVIEW: Leagold Mining merged into Equinox Gold Corp in March 2020 and was delisted; Equinox Gold is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.</t>
         </is>
@@ -2857,22 +2869,22 @@
           <t>www.orlamining.com</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)); Live fetch of the contact page 404'd (URL structure differs from what search results implied); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -2917,22 +2929,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly); derived from First Majestic Silver Corp's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from First Majestic Silver Corp's verified address (already a row in this workbook)); Same registered office as acquirer First Majestic Silver Corp (acquired Silvermex in 2012). Not independently verified as this entity's own filed address.</t>
         </is>
@@ -2982,22 +2994,22 @@
           <t>250.523.2443</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (teck.com project pages, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>CONFLICT: city=Vancouver|Logan Lake (secondary sources (teck.com project pages, not fetched directly)); CONFLICT: province=British Columbia|BC (secondary sources (teck.com project pages, not fetched directly)); REVIEW: this is a Teck Resources operating partnership for the Highland Valley Copper mine near Logan Lake, BC — not a Vancouver office, and not separately contactable from Teck Resources Limited (already a row in this workbook). The D&amp;B listing's Vancouver location likely reflects Teck's corporate HQ, not this operation's actual site address.</t>
         </is>
@@ -3032,22 +3044,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (Zijin Mining acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>REVIEW: Nevsun Resources was fully acquired by Zijin Mining in a compulsory acquisition completed March 2019 and delisted; it has been a wholly-owned Zijin subsidiary for years. The D&amp;B listing entry is almost certainly stale, not a current independent Vancouver prospect.</t>
         </is>
@@ -3107,22 +3119,22 @@
           <t>www.silvercorpmetals.com</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://silvercorpmetals.com/contact-details/</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://silvercorpmetals.com/contact-details/); General public email used; no named individual confirmed on the official contact page itself.</t>
         </is>
@@ -3157,22 +3169,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; opengovca.com Vancouver business licence listing (not the company's own site; no official site located)</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>REVIEW: could not locate an active official company website. Secondary sources describe it as formerly 'Leicester Diamond Mines' and reference an acquisition/merger. Likely an inactive shell or renamed entity; recommend manual verification before treating as a live prospect.</t>
         </is>
@@ -3232,22 +3244,22 @@
           <t>www.orezone.com</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://orezone.com/contact/</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://orezone.com/contact/); General public email used; no named individual confirmed on the official contact page itself (a Kevin MacKenzie, VP Corporate Development and IR, appeared in older search results but was not present on the current official contact page, so not recorded).</t>
         </is>
@@ -3317,22 +3329,22 @@
           <t>www.santacruzsilver.com</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; https://santacruzsilver.com/contact/contact-information/</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://santacruzsilver.com/contact/contact-information/); The CEO's contact block on the official page lists a Mexico phone number and the general info@ email rather than a personal address/direct Vancouver line — recorded as published, not inferred further.</t>
         </is>
@@ -3377,22 +3389,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; secondary sources (Fasken/Aris Mining corporate history, not fetched directly); derived from Aris Mining Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>REVIEW: Aris Mining Holdings Corp is a wholly-owned subsidiary formed in the 2022 Aris Gold/GCM Mining amalgamation; the parent, Aris Mining Corporation, is already a separate row in this workbook (same Vancouver office). Recommend treating this as the same entity rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Aris Mining Corporation's verified address (already a row in this workbook)); Same registered office as parent Aris Mining Corporation. Not independently verified as this entity's own filed address.</t>
         </is>
@@ -3462,22 +3474,22 @@
           <t>www.steppegold.com</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-03.png; steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)); Live fetch of the contact page did not surface an address/phone block (possibly rendered via JS); data sourced from a search-engine snippet referencing the company's own site. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -3522,22 +3534,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; secondary sources (Newmont/Goldcorp merger reporting, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>REVIEW: Newmont Canada Corporation appears to be the same Vancouver office/entity as Newmont Corporation (already a separate row in this workbook, verified with a Vancouver address and contact information), reflecting Newmont's Canadian corporate structure post-Goldcorp merger rather than a distinct company. Recommend treating as the same physical office as Newmont Corporation.; CONFLICT: city=North Vancouver|Vancouver (derived from Newmont Corporation's verified address (already a row in this workbook)); CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as Newmont Corporation — reflects Newmont's Canadian corporate structure, not a distinct physical office.</t>
         </is>
@@ -3572,22 +3584,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; secondary sources (mine closure reporting, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>REVIEW: the Bullmoose coal mine near Tumbler Ridge, BC closed in 2000. This entity has had no active operations for a quarter century; the D&amp;B listing entry is stale. Any current contact would route through Teck Resources Limited (already a row in this workbook).</t>
         </is>
@@ -3632,22 +3644,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; secondary sources (Imperial Metals operational updates, not fetched directly); derived from Imperial Metals Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>REVIEW: Huckleberry Mines Ltd is a wholly-owned Imperial Metals Corporation subsidiary; the Huckleberry mine has been on care-and-maintenance (inactive) since August 2016. Imperial Metals Corporation is already a separate row in this workbook with the same Vancouver office — recommend treating this as the same entity rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Imperial Metals Corporation's verified address (already a row in this workbook)); Same registered office as parent Imperial Metals Corporation. Not independently verified as this entity's own filed address.</t>
         </is>
@@ -3682,22 +3694,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; secondary sources (Jinchuan Group acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>REVIEW: Continental Minerals Corporation was acquired by Jinchuan Group in April 2011 and delisted. This entity has not existed independently for over a decade; the D&amp;B listing entry is stale.</t>
         </is>
@@ -3732,22 +3744,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; no active official website located</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>REVIEW: no current official website could be located; search results returned only an unrelated Australia-based 'Azure Minerals' and generic mining directory listings. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
@@ -3782,22 +3794,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; cacheexploration.com (domain no longer belongs to the company)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>REVIEW: cacheexploration.com has been taken over/squatted — it now serves unrelated online-casino affiliate content (7Bit, Bitstarz, Jackbit, etc.), not the mining company. Did not use this domain for anything. No current verified official site located; recommend manual verification.</t>
         </is>
@@ -3852,22 +3864,22 @@
           <t>www.galianogold.com</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-04.png; galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -3902,22 +3914,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; cfcanada.fticonsulting.com/trevali (court-appointed receiver's case site, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>REVIEW: Trevali entered CCAA insolvency proceedings in August 2022 and its Caribou Mine assets went into receivership under FTI Consulting in 2023, with sale agreements finalized in 2024. This is not a going-concern Vancouver prospect.</t>
         </is>
@@ -3982,22 +3994,22 @@
           <t>www.amerigoresources.com</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://www.amerigoresources.com/company/contact/</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.amerigoresources.com/company/contact/); ILLEGIBLE: contact_email — both the general and CEO email addresses render as obfuscated placeholders in the fetched HTML; not decoded.</t>
         </is>
@@ -4032,22 +4044,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://www.aurcana.com/ (fetched directly; data quality concerns noted below)</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>REVIEW: aurcana.com's contact page shows a stale 2016 copyright footer and a Victoria, BC address, conflicting with third-party sources citing a Vancouver address — and the homepage's most recent news item is from November 2022 (director/officer resignation, TSX-V tier downgrade). Site appears dormant. Declined to record an address/phone that may be years out of date; recommend manual verification.</t>
         </is>
@@ -4117,22 +4129,22 @@
           <t>www.osinoresources.com</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://osinoresources.com/contact-3/</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://osinoresources.com/contact-3/)</t>
         </is>
@@ -4187,22 +4199,22 @@
           <t>www.thorexpl.com</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://thorexpl.com/contact-us/</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://thorexpl.com/contact-us/); No email published on the official contact page (IR handled externally by Fig House Communications per other pages, not a company-owned address). No named individual confirmed on this page.</t>
         </is>
@@ -4262,22 +4274,22 @@
           <t>www.srk.com</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; srk.com/en/contact-us/vancouver (live fetch returned a page whose address block renders via JavaScript; sourced from a search-engine snippet of the same official page)</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (srk.com/en/contact-us/vancouver (live fetch returned a page whose address block renders via JavaScript; sourced from a search-engine snippet of the same official page)); Live fetch succeeded (200) but the address/phone block is client-side rendered and not present in the static HTML; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -4312,22 +4324,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; secondary sources (NovaCopper/Trilogy Metals acquisition news, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>REVIEW: Sunward Resources became a wholly-owned subsidiary of NovaCopper Inc. (now Trilogy Metals) via a 2015 plan of arrangement. Not an independently operating Vancouver prospect.</t>
         </is>
@@ -4397,22 +4409,22 @@
           <t>www.bearcreekmining.com</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://bearcreekmining.com/investors/contact/contact-us/</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://bearcreekmining.com/investors/contact/contact-us/)</t>
         </is>
@@ -4447,22 +4459,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; no official site or public record located</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>REVIEW: this is a generic federal numbered company (Canada Business Corporations Act); no official website, news coverage, or public registry detail was located under this number. Numbered companies are frequently shell/holding entities without a public presence. Recommend manual verification via Corporations Canada before treating as a live prospect.</t>
         </is>
@@ -4497,22 +4509,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; no verified official site located</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>REVIEW: no evidence found connecting this name to a mining company — search results returned only unrelated Vancouver freight-forwarding/logistics listings. The name and business type suggest this D&amp;B listing entry may be a logistics/customs-forwarding company misclassified under the mining NAICS code, not an actual mining prospect. Recommend manual verification.</t>
         </is>
@@ -4572,22 +4584,22 @@
           <t>www.lucaradiamond.com</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://lucaradiamond.com/contact/contact-info/</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://lucaradiamond.com/contact/contact-info/); General public email used for both general and Investor Relations inquiries on the official page; no distinct personal contact confirmed there.</t>
         </is>
@@ -4622,22 +4634,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; secondary sources (SEC filings, BNamericas — not fetched directly, no official standalone site located)</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>REVIEW: sources conflict on ownership (one describes this as an SSR Mining venture, others associate it with Pan American Silver's Argentina operations). No standalone official website was located. Recommend manual verification of current ownership/contact before treating as an independent prospect.</t>
         </is>
@@ -4672,22 +4684,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; secondary sources (Newcrest acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>REVIEW: Pretium Resources (Brucejack mine) was fully acquired by Newcrest Mining in March 2022 and delisted; Newcrest itself was subsequently acquired by Newmont in 2023. Newmont Corporation is already a separate row in this workbook. Not an independent Vancouver prospect.</t>
         </is>
@@ -4722,22 +4734,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; secondary sources (Yahoo Finance, Northern Miner — not fetched directly)</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>REVIEW: available sources describe this company as headquartered in Brisbane, Australia, not Vancouver, with its most recent located news dating to 2013. The D&amp;B listing's Vancouver location could not be corroborated; likely stale or a registered-agent address only. Recommend manual verification.</t>
         </is>
@@ -4787,22 +4799,22 @@
           <t>queensrdcapital.com</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; https://queensrdcapital.com/contact/offices/</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>CONFLICT: city=Vancouver|Hong Kong (https://queensrdcapital.com/contact/offices/); CONFLICT: country=Canada|Hong Kong (https://queensrdcapital.com/contact/offices/); REVIEW: the company's own official 'Offices' page lists only a Hong Kong address — no Vancouver office is published anywhere on the site. This directly conflicts with the D&amp;B listing's Vancouver location. Recorded the verified Hong Kong address rather than inferring a Canadian one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
         </is>
@@ -4837,22 +4849,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-05-05.png; secondary sources (acquisition history, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>REVIEW: Rockgate Capital Corp was acquired by Denison Mines in 2013 and no longer exists as an independent entity. The D&amp;B listing entry is stale, over a decade old.</t>
         </is>
@@ -4922,22 +4934,22 @@
           <t>www.tridentresourcescorp.com</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; https://www.tridentresourcescorp.com/corporate/overview/</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.tridentresourcescorp.com/corporate/overview/); Recently rebranded from Rockridge/MAS Gold/Eros three-way consolidation (2025); currently active Saskatchewan gold exploration company.</t>
         </is>
@@ -4972,22 +4984,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; magellanminerals.com (domain redirects to a parking-page lander)</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>REVIEW: magellanminerals.com now redirects to a generic domain-parking lander page, indicating the company's official web presence has lapsed. Search results conflict — one 2016 report describes an acquisition by Anfield Nickel Corp, while other secondary sources reference 2026 news activity — but no live official site could be verified. Recommend manual verification before treating as a live Vancouver prospect.</t>
         </is>
@@ -5047,22 +5059,22 @@
           <t>www.hivedigitaltechnologies.com</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; https://www.hivedigitaltechnologies.com/contact (email/phone fetched directly; street address sourced from a search-engine snippet of the same official site, not present on the contact page itself)</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.hivedigitaltechnologies.com/contact (email/phone fetched directly; street address sourced from a search-engine snippet of the same official site, not present on the contact page itself)); Email and phone confirmed via direct fetch. Address not shown on the fetched contact page; sourced from search snippet instead. Recommend re-verifying the address directly if precision matters.</t>
         </is>
@@ -5107,22 +5119,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; secondary sources (Foran Mining / Eldorado Gold acquisition reporting, not fetched directly); derived from Eldorado Gold Corporation's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>REVIEW: McIlvenna Bay is a copper project operated by Foran Mining Corporation, which was itself acquired by Eldorado Gold in April 2026 (Eldorado Gold is already a separate row in this workbook). This is a mine-site operating entity, not an independent Vancouver corporate office.; CONFLICT: province=British Columbia|BC (derived from Eldorado Gold Corporation's verified address (already a row in this workbook)); Same registered office as parent Eldorado Gold Corporation (via its 2026 acquisition of Foran Mining, which held McIlvenna Bay). Not independently verified as this entity's own filed address.</t>
         </is>
@@ -5157,22 +5169,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; secondary sources (SEC filings, acquisition history, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>REVIEW: Queenstake Resources was acquired by Veris Gold in 2007; Veris Gold itself filed for bankruptcy in 2014 and is now inactive. This entity has been defunct for close to two decades — the D&amp;B listing entry is stale.</t>
         </is>
@@ -5232,22 +5244,22 @@
           <t>www.shamaranpetroleum.com</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; https://shamaranpetroleum.com/contact/contact-info/</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>CONFLICT: company_name=Shamaran Petroleum Corp|ShaMaran Petroleum Corp (https://shamaranpetroleum.com/contact/contact-info/); CONFLICT: province=British Columbia|BC (https://shamaranpetroleum.com/contact/contact-info/); The only named Investor Relations contact published (Robert Eriksson) is based in Sweden, not Vancouver, so a Canadian general email/phone was used instead. Shares the same Vancouver registered-office building (1055 Dunsmuir Street) as several other Lundin-family companies already in this workbook — a known registered-agent-suite pattern, not an error.</t>
         </is>
@@ -5297,22 +5309,22 @@
           <t>www.cumtn.com</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; cumtn.com/investors/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (cumtn.com/investors/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; address sourced from a search-engine snippet of the same official domain, no email/phone surfaced in that snippet. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -5347,22 +5359,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; secondary sources (SEC/bankruptcy court filings, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>REVIEW: Veris Gold filed for Chapter 15 bankruptcy in 2014; its Jerritt Canyon assets were sold off in 2015 and the bankruptcy case formally closed in 2018. This is an inactive BC corporation with no current operations.</t>
         </is>
@@ -5422,22 +5434,22 @@
           <t>www.lucamining.com</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; https://lucamining.com/contact/</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://lucamining.com/contact/)</t>
         </is>
@@ -5472,22 +5484,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; secondary sources (Hecla Mining acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>REVIEW: Klondex Mines was acquired by Hecla Mining in July 2018 (Nevada assets); its Canadian operations were spun off separately into Havilah Mining Corp, which is not in this workbook. Klondex has not existed independently since 2018.</t>
         </is>
@@ -5547,22 +5559,22 @@
           <t>www.monumentmining.com</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; https://monumentmining.com/contact/</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://monumentmining.com/contact/); General public email used; a named IR contact (Richard Cushing) appeared in search results but was not present on the official contact page itself, so not recorded.</t>
         </is>
@@ -5597,22 +5609,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; secondary sources (Newcrest acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>REVIEW: same entity/history already flagged for 'Pretium Exploration Inc' in an earlier batch — Pretium Resources (Brucejack mine) was acquired by Newcrest Mining in March 2022 and delisted; Newcrest itself was acquired by Newmont in 2023 (Newmont Corporation is already a row in this workbook). Not an independent Vancouver prospect.</t>
         </is>
@@ -5662,22 +5674,22 @@
           <t>www.makomining.com</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-04.png; makomining.com/contact/ (live fetch 403'd; address sourced from a search-engine snippet of the company's own official site)</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (makomining.com/contact/ (live fetch 403'd; address sourced from a search-engine snippet of the company's own official site)); Live fetch returned 403; no email/phone surfaced in the available search snippet. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -5712,22 +5724,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; secondary sources (federalcorporation.ca, OSC records — not fetched directly)</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>REVIEW: this entity's status is recorded as 'Inactive - Amalgamated,' its registered office is in Toronto (not Vancouver), and it voluntarily surrendered its BC reporting-issuer status back in 2009. The D&amp;B listing's Vancouver location does not reflect current reality; this is not a live prospect.</t>
         </is>
@@ -5797,22 +5809,22 @@
           <t>www.energold.com</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://energold.com/contact/</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://energold.com/contact/); Company now operates under the 'Energold Group' brand at this domain.</t>
         </is>
@@ -5857,22 +5869,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; secondary sources (Capstone Copper/Orion joint-venture press releases, not fetched directly); derived from Capstone Copper Corp's verified address (already a row in this workbook)</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>REVIEW: this is a wholly-owned Capstone Copper Corp subsidiary (the 'JVCo' vehicle for the Santo Domingo project, in which Capstone sold a 25% interest to Orion in 2025). Capstone Copper Corp is already a verified row in this workbook with the same Vancouver office. Not an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Capstone Copper Corp's verified address (already a row in this workbook)); Same registered office as parent Capstone Copper Corp (this entity is Capstone's 'JVCo' vehicle for the Santo Domingo project). Not independently verified as this entity's own filed address.</t>
         </is>
@@ -5907,22 +5919,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; secondary sources (St Barbara Limited acquisition press releases, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>REVIEW: Atlantic Gold was fully acquired by St Barbara Limited (Australia) in July 2019, delisted from the TSX-V, and ceased to be a reporting issuer. It is now a wholly-owned Australian subsidiary operating the Moose River Consolidated project in Nova Scotia — not an independent Vancouver prospect.</t>
         </is>
@@ -5977,22 +5989,22 @@
           <t>www.gsilver.com</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://www.gsilver.com/contact</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.gsilver.com/contact); ILLEGIBLE: contact_email — page uses JavaScript-based spambot protection instead of a plain-text address; not decoded.</t>
         </is>
@@ -6042,22 +6054,22 @@
           <t>www.titanminingcorp.com</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://www.titanminingcorp.com/contact/contact-details/</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.titanminingcorp.com/contact/contact-details/); ILLEGIBLE: street_address — the fetched contact page only lists the company's US mine-site address (Gouverneur, NY) alongside a Canadian phone/email; the Vancouver street address (999 Canada Place, per third-party sources) was not present on this official page, so not recorded to avoid mixing sourced and unsourced data.</t>
         </is>
@@ -6117,22 +6129,22 @@
           <t>www.hemisphereenergy.ca</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://www.hemisphereenergy.ca/contact</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.hemisphereenergy.ca/contact); The official contact page publishes only department-specific addresses (Accounts Payable, Surface and Mineral Land inquiries) rather than a general info@ address; recorded the land/surface-inquiries address as the closest general-purpose contact. No named individual confirmed.</t>
         </is>
@@ -6167,22 +6179,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; taatglobal.com (checked; not a mining company)</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>REVIEW: TAAT Global Alternatives makes tobacco-free/nicotine-free cigarette alternatives — a consumer products company, not a mining company. This D&amp;B listing entry appears to be misclassified under the mining NAICS code, similar to Ridgetop Forwarding flagged earlier. Not a mining prospect.</t>
         </is>
@@ -6247,22 +6259,22 @@
           <t>www.aticomining.com</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://aticomining.com/contact-us/contact-information/</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://aticomining.com/contact-us/contact-information/); ILLEGIBLE: contact_email — no email published alongside the named Corporate Development contact on the official page.</t>
         </is>
@@ -6317,22 +6329,22 @@
           <t>www.uraniumenergy.com</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://www.uraniumenergy.com/contact</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://www.uraniumenergy.com/contact); This is UEC's Vancouver office; the company's actual corporate headquarters is in Corpus Christi, Texas. No email published for the Vancouver office specifically.</t>
         </is>
@@ -6367,22 +6379,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; secondary sources (BC Securities Commission reporting-issuer list, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>REVIEW: the BC Securities Commission lists this company as 'In Default' as of September 3, 2024. Recommend manual verification of current operating status before treating as a live prospect.</t>
         </is>
@@ -6452,22 +6464,22 @@
           <t>www.avino.com</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; https://avino.com/contact</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://avino.com/contact)</t>
         </is>
@@ -6527,22 +6539,22 @@
           <t>www.minesense.com</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; minesense.com/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official site)</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (minesense.com/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official site)); Live fetch returned 403; data sourced from a search-engine snippet of the same official domain. Recommend re-verifying directly if precision matters.</t>
         </is>
@@ -6577,22 +6589,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-01.png; secondary sources (SEC filings, Mergr ownership records, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>REVIEW: Oromin Explorations was acquired by Teranga Gold Corporation in 2013 (its Sabodala/OJVG assets in Senegal). Not an independent Vancouver prospect for well over a decade.</t>
         </is>
@@ -6627,22 +6639,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>chat-listing-2026-08-06-02.png; secondary sources (BC Environmental Assessment Office filings, Skeena Resources SEC filings, not fetched directly)</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>REVIEW: this is a wholly-owned, permit-holding subsidiary of Skeena Resources Ltd (which holds the Eskay Creek gold-silver project in the Golden Triangle). Skeena Resources itself is not currently a row in this workbook. This entity is a project vehicle, not an independent Vancouver corporate office — recommend adding Skeena Resources Ltd as the actual contactable entity if this project is of interest.</t>
         </is>
@@ -6704,22 +6716,32 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png; https://www.eastplats.com/contacts/</t>
+          <t>capital raise: secured additional credit facility, total credit available up to C$4,000,000 across three facilities; expansion/new project: targeting Zandfontein underground ramp-up to 70,000 tonnes ROM ore/month by end of 2026, per 2025 annual results and 2026 targets</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
+          <t>https://www.eastplats.com/investors/news-releases/2026/eastern-platinum-limited-secures-additional-credit-facility/; https://www.eastplats.com/investors/news-releases/2026/eastern-platinum-limited-reports-annual-results-for-2025-and-provides-its-targets-for-2026/</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; https://www.eastplats.com/contacts/; stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.eastplats.com/contacts/)</t>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.eastplats.com/contacts/); Company also disclosed a working capital deficit of $56.9 million as at Dec 31, 2025 (up from $38.7 million a year earlier) in the same annual results release — a financial-health signal worth noting even though it's not one of the fixed categories.</t>
         </is>
       </c>
     </row>
@@ -6777,24 +6799,24 @@
           <t>www.somagoldcorp.com</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>chat-listing-2026-08-06-02.png; https://somagoldcorp.com/contact/</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; https://somagoldcorp.com/contact/; stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>CONFLICT: province=British Columbia|BC (https://somagoldcorp.com/contact/)</t>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://somagoldcorp.com/contact/); Search results referenced a 'CI Jade' merger/acquisition (Sept 9, 2025) and a mid-2026 capital raise, but no primary press release or citable source URL could be located for either claim on somagoldcorp.com/news/ or elsewhere — not recorded per the no-fabrication rule. Recommend a direct check of somagoldcorp.com's news archive pagination if this matters.</t>
         </is>
       </c>
     </row>
@@ -6829,22 +6851,32 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png; secondary sources (acquisition/delisting press releases, not fetched directly)</t>
+          <t>expansion/new project: Phase 3 exploration drilling (8,100 metres total) at the Golden Queen mine intersected encouraging mineralized intervals supporting potential mine-life extension, update issued October 2025</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
+          <t>https://www.newsfilecorp.com/release/270605/Andean-Precious-Metals-Provides-Update-on-2025-Exploration-Results-at-Golden-Queen-and-San-Bartolome</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (acquisition/delisting press releases, not fetched directly); stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>REVIEW: Golden Queen Mining delisted from the TSX in 2019 and was acquired by Falco Resources in March 2020, becoming a private company. Not an independent, publicly-contactable Vancouver prospect.</t>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>REVIEW: Golden Queen Mining delisted from the TSX in 2019 and was acquired by Falco Resources in March 2020, becoming a private company. Not an independent, publicly-contactable Vancouver prospect.; CORRECTION to earlier REVIEW note: current owner is Andean Precious Metals Corp, which acquired Golden Queen Mining Company, LLC from Auvergne Umbrella LLC for $66.6 million on November 24, 2023 (per canadianlawyermag.com/cl-plus/deals/1269) — not Falco Resources as previously stated. The entity remains a private/acquired asset, not an independent Vancouver prospect, but ownership chain is now corrected.</t>
         </is>
       </c>
     </row>
@@ -6879,22 +6911,32 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png; secondary sources (CCAA insolvency records, not fetched directly)</t>
+          <t>insolvency/receivership: remains under CCAA creditor protection with the Cantung mine on care and maintenance; most recent Monitor's Report filed April 10, 2026</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.alvarezandmarsal.com/north-american-tungsten-corporation-ltd/monitors-reports; </t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (CCAA insolvency records, not fetched directly); stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>REVIEW: this company entered CCAA creditor protection in 2015 and its head office closed effective December 31, 2015, with all inquiries redirected to court-appointed monitor Alvarez &amp; Marsal Canada. The Cantung Mine remains on care and maintenance. Not an active Vancouver office.</t>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>REVIEW: this company entered CCAA creditor protection in 2015 and its head office closed effective December 31, 2015, with all inquiries redirected to court-appointed monitor Alvarez &amp; Marsal Canada. The Cantung Mine remains on care and maintenance. Not an active Vancouver office.; Confirms the CCAA proceeding (already flagged REVIEW, entered 2015) is still active as of April 2026, not resolved.</t>
         </is>
       </c>
     </row>
@@ -6929,22 +6971,32 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-02.png; hemlomining.com (site loaded but is a JavaScript single-page app; no static contact page found at common paths)</t>
+          <t>IPO/listing change: commenced trading on the TSX Venture Exchange under symbol HMMC at market-open, December 2, 2025; expansion/new project: launched a 130,000-metre 2026 exploration drilling program and $30M+ investment in 21 new pieces of mobile equipment as part of an owner-operator transition</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
+          <t>https://markets.financialcontent.com/pennwell.pennenergy/article/accwirecq-2025-12-1-hemlo-mining-corp-announces-commencement-of-trading-on-the-tsxv-at-market-open-on-tuesday-december-2-2025; https://www.hemlomining.com/news/hemlo-mining-corp-reports-first-quarter-2026-financial-and-operating-results</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; hemlomining.com (site loaded but is a JavaScript single-page app; no static contact page found at common paths); stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>REVIEW: this is a very recently renamed entity (formerly Carcetti Capital Corp, which completed its Hemlo gold mine acquisition from Barrick on November 26, 2025). Sources conflict on head office location (Vancouver vs. Toronto), and the live site's contact page could not be located via static fetch. Recommend manual verification given how new this entity is.</t>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a very recently renamed entity (formerly Carcetti Capital Corp, which completed its Hemlo gold mine acquisition from Barrick on November 26, 2025). Sources conflict on head office location (Vancouver vs. Toronto), and the live site's contact page could not be located via static fetch. Recommend manual verification given how new this entity is.; This confirms Hemlo Mining Corp is a genuinely active, newly-listed company (formerly Carcetti Capital Corp, closed its Hemlo gold mine acquisition from Barrick November 26, 2025) rather than uncertain as previously flagged — recommend downgrading the earlier REVIEW status now that real operations are confirmed, though the Vancouver-vs-Toronto head office question from the earlier note is still unresolved.</t>
         </is>
       </c>
     </row>
@@ -6987,24 +7039,24 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>chat-listing-2026-08-06-02.png; secondary sources (Equinox Gold formation press releases, not fetched directly); derived from Equinox Gold Corp's verified address (already a row in this workbook)</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-02.png; secondary sources (Equinox Gold formation press releases, not fetched directly); derived from Equinox Gold Corp's verified address (already a row in this workbook); stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>REVIEW: Newcastle Gold merged with Trek Mining and Anfield Gold in December 2017 to form Equinox Gold Corp, and was delisted. Equinox Gold Corp is already a verified row in this workbook. Not an independent entity.; CONFLICT: province=British Columbia|BC (derived from Equinox Gold Corp's verified address (already a row in this workbook)); Same registered office as Equinox Gold Corp, formed from the 2017 merger of Newcastle Gold, Anfield Gold, and Trek Mining. Not independently verified as this entity's own filed address.</t>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>REVIEW: Newcastle Gold merged with Trek Mining and Anfield Gold in December 2017 to form Equinox Gold Corp, and was delisted. Equinox Gold Corp is already a verified row in this workbook. Not an independent entity.; CONFLICT: province=British Columbia|BC (derived from Equinox Gold Corp's verified address (already a row in this workbook)); Same registered office as Equinox Gold Corp, formed from the 2017 merger of Newcastle Gold, Anfield Gold, and Trek Mining. Not independently verified as this entity's own filed address.; No material 12-month corporate-action news found. A search result claimed a 'November 2025' NewCastle Gold/Catalyst Copper merger, but this was verified against primary sources to actually be the 2016 Catalyst Copper merger, misdated by the search summary — not treated as real 2025-2026 news. Entity remains defunct/merged into Equinox Gold since December 2017 (already flagged REVIEW).</t>
         </is>
       </c>
     </row>
@@ -7037,24 +7089,24 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>chat-listing-2026-08-06-03.png; secondary sources (Argonaut Gold merger press releases, not fetched directly)</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png; secondary sources (Argonaut Gold merger press releases, not fetched directly); stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="T102" t="inlineStr">
         <is>
           <t>detail_only</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>REVIEW: Alio Gold merged into Argonaut Gold in July 2020 and was delisted from both the TSX and NYSE American. Not an independent entity for six years.</t>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>REVIEW: Alio Gold merged into Argonaut Gold in July 2020 and was delisted from both the TSX and NYSE American. Not an independent entity for six years.; No material 12-month corporate-action news found — consistent with the entity having been defunct/merged into Argonaut Gold since July 2020 (already flagged REVIEW).</t>
         </is>
       </c>
     </row>
@@ -7099,22 +7151,32 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png; https://www.ngenergyintl.com/contact/contact-details/</t>
+          <t>acquisition/merger: closed sale of a 40% operating working interest in the Sinu-9 Block to Etablissements Maurel &amp; Prom for US$150 million cash, plus acquisition of a collective 28% working interest from minority partners, leaving NGE with a 39% non-operating interest</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
+          <t>https://www.newswire.ca/news-releases/ng-energy-announces-closing-of-sinu-9-transactions-822740107.html</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png; https://www.ngenergyintl.com/contact/contact-details/; stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>CONFLICT: city=Vancouver|Calgary (https://www.ngenergyintl.com/contact/contact-details/); CONFLICT: province=British Columbia|AB (https://www.ngenergyintl.com/contact/contact-details/); REVIEW: the company's own official contact page lists its Canadian office in Calgary, Alberta — not Vancouver — directly conflicting with the D&amp;B listing. Email on this page is obfuscated. Recorded the verified Calgary address rather than a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Calgary (https://www.ngenergyintl.com/contact/contact-details/); CONFLICT: province=British Columbia|AB (https://www.ngenergyintl.com/contact/contact-details/); REVIEW: the company's own official contact page lists its Canadian office in Calgary, Alberta — not Vancouver — directly conflicting with the D&amp;B listing. Email on this page is obfuscated. Recorded the verified Calgary address rather than a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.; Exact transaction date not stated in the source beyond 2025-2026 context. Reminder: this company's own site lists a Calgary, AB Canadian office (see earlier REVIEW note), not Vancouver.</t>
         </is>
       </c>
     </row>
@@ -7169,22 +7231,32 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png; https://encoreuranium.com/corporate/corporate-directory/</t>
+          <t>capital raise: closed $115M USD senior unsecured convertible notes offering, August 22, 2025; expansion/new project: acquired the 5,900-acre Tacubaya land parcel (70/30 JV with Boss Energy) to extend the Alta Mesa uranium project, October 2025</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
+          <t>https://www.ainvest.com/news/encore-energy-corp-strategic-115m-capital-raise-catalyst-green-energy-growth-shareholder-2508/; https://www.ainvest.com/news/encore-energy-corp-strategic-115m-capital-raise-catalyst-green-energy-growth-shareholder-2508/</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png; https://encoreuranium.com/corporate/corporate-directory/; stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>CONFLICT: city=Vancouver|Dallas (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: province=British Columbia|TX (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: country=Canada|United States (https://encoreuranium.com/corporate/corporate-directory/); REVIEW: the company's own official corporate directory lists its head office in Dallas, Texas. The only Vancouver address on the page (510 Burrard Street) belongs to Computershare, enCore's third-party transfer agent — not an enCore office. Recorded the verified Dallas head office rather than inferring a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.</t>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Dallas (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: province=British Columbia|TX (https://encoreuranium.com/corporate/corporate-directory/); CONFLICT: country=Canada|United States (https://encoreuranium.com/corporate/corporate-directory/); REVIEW: the company's own official corporate directory lists its head office in Dallas, Texas. The only Vancouver address on the page (510 Burrard Street) belongs to Computershare, enCore's third-party transfer agent — not an enCore office. Recorded the verified Dallas head office rather than inferring a Vancouver one; recommend treating this as NOT a Vancouver prospect unless independently confirmed otherwise.; Reminder: this company's own site lists Dallas, TX as head office (see earlier REVIEW note) — Vancouver is only its transfer agent's address.</t>
         </is>
       </c>
     </row>
@@ -7244,27 +7316,37 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-06-03.png; https://liononemetals.com/contact/contact-info/</t>
+          <t>capital raise: closed upsized LIFE offering for gross proceeds of C$18.7 million (2025); management change: CEO Ian Berzins departed effective late December 2025; management change: Ian Berzins reappointed President, CEO and Director effective June 16, 2026</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
+          <t>https://liononemetals.com/news/news-releases/lion-one-announces-closing-of-upsized-life-offering-for-gross-proceeds-of-18.7-million/; https://liononemetals.com/news/news-releases/lion-one-announces-departure-of-ceo/; https://www.newsfilecorp.com/release/301600/Lion-One-Appoints-Ian-Berzins-as-President-CEO-and-Director</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-06-03.png; https://liononemetals.com/contact/contact-info/; stage-3 news check</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>CONFLICT: province=British Columbia|BC (https://liononemetals.com/contact/contact-info/); A newly appointed VP Corporate Development and Investor Relations (Ronan Geoghegan, per search results, appointed July 2026) was not present on the official contact page itself, so not recorded.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S105"/>
+  <autoFilter ref="A1:U105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:U141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7345,8 +7345,1628 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Afton Operating Corporation</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>$38.37M</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Heliostar Metals Ltd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>$36.57M</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BioHarvest Sciences Inc</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>$34.51M</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Integra Resources Corp</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>$30.35M</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Leef Brands Inc</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>$28.5M</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EMX Royalty Corporation</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>$27.45M</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Pacific Rim Mining Corp</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>$27.03M</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Core Gold Inc</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>$26.7M</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Red Lake Madsen Mine Ltd</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>$24.92M</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Starcore International Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>$23.69M</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Battery Mineral Resources Corp</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>$23.24M</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IMPACT Silver Corp</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>$22.74M</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Silver X Mining Corp</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>$21.85M</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Goldgroup Mining Inc</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>$20.37M</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-02.png</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Canaf Investments Inc</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>$19.86M</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Hunter Dickinson Inc</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>$17.51M</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Cathedra Bitcoin Inc</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>$16.5M</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Elemental Royalty Corporation</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>$16.32M</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Polaris Materials Corporation</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>$15.67M</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Renaissance Oil Corp</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>$14.36M</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>K+S Canada Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>$13.58M</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Hillsborough Resources Limited</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>$13.51M</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sixth Wave Innovations Inc</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>$12.1M</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Metalla Royalty &amp; Streaming Ltd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>$11.74M</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Ledcor CMI Ltd</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Golden Lake Exploration Inc</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Lida Resources Inc</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Peace River Coal Inc</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-03.png</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AndeanGold Ltd</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Virginia Energy Resources Inc</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>$11.67M</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Uranium Royalty Corp</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>$11.49M</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cambria Gold Mines Inc</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>$10.97M</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Gunnison Copper Corp</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>$10.89M</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Quintette Coal Limited</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>$10.81M</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NEOS Canada Services ULC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>$10.3M</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Gold Royalty Corp</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>$10.1M</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-07-01.png</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U105"/>
+  <autoFilter ref="A1:U141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -7374,9 +7374,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>info.newafton@newgold.com</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>250 377-2700</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>newafton.newgold.com</t>
+        </is>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://newafton.newgold.com/engage-with-us/get-in-touch/</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -7386,7 +7401,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>REVIEW: this is the operating entity for the New Afton mine, located near Kamloops (~350km from Vancouver), not a Vancouver office. Owner New Gold Inc was itself acquired by Coeur Mining Inc, completed March 20, 2026. Not an independent Vancouver corporate prospect.</t>
         </is>
       </c>
     </row>
@@ -7404,6 +7424,11 @@
       <c r="C107" t="n">
         <v>36.57</v>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>595 Burrard Street, Suite 1723</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7414,14 +7439,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>V7X 1J1</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Rob Grey</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>info@heliostarmetals.com</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>+1 778 357 1313 (IR direct); +1 844-753-0045 (general/toll-free)</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>www.heliostarmetals.com</t>
+        </is>
+      </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://www.heliostarmetals.com/contact/contact-us/</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -7431,7 +7486,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.heliostarmetals.com/contact/contact-us/); ILLEGIBLE: Rob Grey's personal email — obfuscated on the official page; general email used instead.</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7526,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; bioharvest.com (checked; not a mining company)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -7476,7 +7536,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>REVIEW: BioHarvest Sciences is a biotechnology company (plant-based molecule synthesis for nutraceuticals/pharmaceuticals), not a mining company. Likely a NAICS misclassification, similar to TAAT Global Alternatives and Ridgetop Forwarding flagged earlier. Not a mining prospect.</t>
         </is>
       </c>
     </row>
@@ -7494,6 +7559,11 @@
       <c r="C109" t="n">
         <v>30.35</v>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>400 Burrard Street, Suite 1050</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7504,14 +7574,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>V6C 3A6</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>info@integraresources.com</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>604-416-0576</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>www.integraresources.com</t>
+        </is>
+      </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://integraresources.com/contact/contact/</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -7521,7 +7611,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://integraresources.com/contact/contact/); General public email used; a named VP Corporate Development &amp; IR (Jason Banducci) appeared in search results but was not present on the official contact page itself, so not recorded.</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7651,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; leefbrands.com (checked; ambiguous/not a mining company)</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -7566,7 +7661,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>REVIEW: search results returned conflicting descriptions — a CSE-listed 'global wellness enterprise' making botanically-based consumable products, and a separately-branded 'California cannabis manufacturer' at the same domain. Either way this is a consumer products company, not mining. Likely a NAICS misclassification; not a mining prospect.</t>
         </is>
       </c>
     </row>
@@ -7584,6 +7684,11 @@
       <c r="C111" t="n">
         <v>27.45</v>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>543 Granville Street, Suite 501</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7594,14 +7699,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>V6C 1X8</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Corporate@emxroyalty.com</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>+1 (604) 688-6390</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>www.emxroyalty.com</t>
+        </is>
+      </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; secondary sources (merger press releases; general contact info corroborated across multiple search results)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -7611,7 +7736,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (merger press releases; general contact info corroborated across multiple search results)); REVIEW: EMX Royalty Corporation merged with Elemental Altus Royalties Corp on November 13, 2025, with the combined entity renamed Elemental Royalty Corporation (a separate row in this workbook, at a different Vancouver address). EMX no longer exists as an independent entity — recommend treating this row as historical, cross-referenced to Elemental Royalty Corporation.</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7776,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; secondary sources (OceanaGold acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -7656,7 +7786,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>REVIEW: Pacific Rim Mining was acquired by OceanaGold Corporation in 2013 (OceanaGold is already a row in this workbook). Not independently operating for over a decade.</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7826,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; secondary sources (Titan Minerals acquisition records, not fetched directly)</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -7701,7 +7836,12 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>REVIEW: Core Gold was acquired by Titan Minerals (ASX-listed) on May 13, 2020. Not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -7719,6 +7859,11 @@
       <c r="C114" t="n">
         <v>24.92</v>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Suite 3123, 595 Burrard Street, Three Bentall Centre</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7729,14 +7874,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>V7X 1J1</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>investors@wrlgold.com</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>1-604-569-5559</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>www.westredlakegold.com</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; search-engine snippet of westredlakegold.com (the actual operating company; not fetched directly)</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -7746,7 +7911,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet of westredlakegold.com (the actual operating company; not fetched directly)); REVIEW: 'Red Lake Madsen Mine' is the Madsen Mine project name; the actual corporate entity operating it is West Red Lake Gold Mines Ltd. Recorded that company's contact info here since the D&amp;B listing entry appears to refer to the project, not a separately incorporated company. Recommend treating this as the same entity as West Red Lake Gold Mines Ltd.</t>
         </is>
       </c>
     </row>
@@ -7764,6 +7934,11 @@
       <c r="C115" t="n">
         <v>23.69</v>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>580 Hornby Street, Suite 750, Box 113</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7774,14 +7949,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>V6C 3B6</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Robert Eadie</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>President/CEO</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>investor@starcore.com</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>+1 604-602-4935</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>www.starcore.com</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://starcore.com/en/contact/contact-us/</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -7791,7 +7996,12 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://starcore.com/en/contact/contact-us/); No personal email published for Robert Eadie; general Investor Relations email used.</t>
         </is>
       </c>
     </row>
@@ -7809,6 +8019,11 @@
       <c r="C116" t="n">
         <v>23.24</v>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1111 West Hastings Street, 15th Floor</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7819,14 +8034,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>V6E 2J3</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>info@bmrcorp.com</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>www.bmrcorp.com</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; bmrcorp.com/contact/contact-info/ (live fetch succeeded but the address block wasn't in the static content; sourced from search-engine snippet of the same official page)</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -7836,7 +8066,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (bmrcorp.com/contact/contact-info/ (live fetch succeeded but the address block wasn't in the static content; sourced from search-engine snippet of the same official page)); Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -7854,6 +8089,11 @@
       <c r="C117" t="n">
         <v>22.74</v>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>543 Granville Street, Suite 303</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7864,14 +8104,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>V6C 1X8</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Jerry Huang</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>VP Finance &amp; Investor Relations</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>inquiries@impactsilver.com</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>604 664-7707</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>www.impactsilver.com</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://impactsilver.com/contact/contact-info/</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -7881,7 +8151,12 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://impactsilver.com/contact/contact-info/)</t>
         </is>
       </c>
     </row>
@@ -7899,6 +8174,11 @@
       <c r="C118" t="n">
         <v>21.85</v>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>409 Granville Street, Suite 1500</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7909,14 +8189,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>V6C 1T2</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Paola Ricardo</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>ir@silverxmining.com</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>+1 647 259 6901</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>www.silverxmining.com</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://www.silverxmining.com/contact/</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -7926,7 +8236,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.silverxmining.com/contact/); The official contact page lists two different Vancouver addresses (this one, and a second at 620-1111 Melville St.) with two different named IR contacts (Paola Ricardo and Kaitlin Taylor) — likely a template/content duplication on their own site rather than two real offices. Recorded the block with the more complete contact information; flagging the discrepancy rather than silently picking one.</t>
         </is>
       </c>
     </row>
@@ -7944,6 +8259,11 @@
       <c r="C119" t="n">
         <v>20.37</v>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1111 Melville St., Suite 410</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7954,14 +8274,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>V6E 3V6</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Sophia Shane</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>sshane@goldgroupmining.com</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>1.604.306.6867</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>www.goldgroupmining.com</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-02.png</t>
+          <t>chat-listing-2026-08-07-02.png; https://www.goldgroupmining.com/contact</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -7971,7 +8321,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.goldgroupmining.com/contact)</t>
         </is>
       </c>
     </row>
@@ -7989,6 +8344,11 @@
       <c r="C120" t="n">
         <v>19.86</v>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1111 Melville Street, Suite 1100</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -7999,14 +8359,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>V6E 3V6</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>info@canafinvestments.com</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>+1 604 283 6110</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>www.canafinvestments.com</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; https://www.canafinvestments.com/contact</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -8016,7 +8396,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.canafinvestments.com/contact); No named individual confirmed on the official contact page.</t>
         </is>
       </c>
     </row>
@@ -8034,6 +8419,11 @@
       <c r="C121" t="n">
         <v>17.51</v>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1040 West Georgia Street, 15th Floor</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8044,14 +8434,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>V6E 4H8</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>www.hdimining.com</t>
+        </is>
+      </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; search-engine snippet of hdimining.com (not fetched directly)</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -8061,7 +8461,12 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet of hdimining.com (not fetched directly)); Hunter Dickinson Inc is a private management/technical-services group serving a portfolio of mineral companies, not itself a mine operator. No email/phone surfaced in the available snippet.</t>
         </is>
       </c>
     </row>
@@ -8079,6 +8484,11 @@
       <c r="C122" t="n">
         <v>16.5</v>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>422 Richards Street, Unit 170</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8089,14 +8499,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>V6B 2Z4</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Joel Block</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>ir@cathedra.com</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>+1 (604) 259-0607</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>www.cathedra.com</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; https://cathedra.com/contact/</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -8106,7 +8546,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://cathedra.com/contact/); Note: this is a bitcoin/digital-infrastructure company ('dispatchable compute'), not a mineral mining company — the word 'mining' here refers to cryptocurrency mining. Flagging for awareness rather than as a misclassification, since crypto mining can plausibly fall under a mining-adjacent NAICS code; recommend a judgment call on relevance.</t>
         </is>
       </c>
     </row>
@@ -8124,6 +8569,11 @@
       <c r="C123" t="n">
         <v>16.32</v>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>815 W. Hastings St., Suite 905</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8134,14 +8584,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>V6C 1B4</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>corporate@elementalroyalty.com</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>+1 (604) 688-6390</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>www.elementalroyalty.com</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; elementalroyalty.com/contact/ (live fetch 404'd on the path tried; sourced from search-engine snippet of the same official domain)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -8151,7 +8621,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (elementalroyalty.com/contact/ (live fetch 404'd on the path tried; sourced from search-engine snippet of the same official domain)); Formed November 13, 2025 from the merger of Elemental Altus Royalties Corp and EMX Royalty Corporation (EMX flagged REVIEW as a separate row, cross-referenced here). Recommend re-verifying the contact page directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8661,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (Vulcan Materials Company acquisition records, not fetched directly)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -8196,7 +8671,12 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>REVIEW: Polaris Materials is a wholly-owned private subsidiary of Vulcan Materials Company (a US public company) and has no independent public investor relations presence. Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8711,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (not fetched directly; address in search results appeared to combine two different addresses inconsistently)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -8241,7 +8721,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>REVIEW: as of November 10, 2023 this company operates as a subsidiary of Chame Energy Corporation. The address returned by search results appeared to be a garbled composite of two different addresses ('1500-999 West Hastings Street Suite 3123, 595 Burrard Street') — not recorded rather than guessing which is correct. Recommend direct verification if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -8259,6 +8744,11 @@
       <c r="C126" t="n">
         <v>13.58</v>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>750 West Pender Street, Suite 1212</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8269,14 +8759,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1-306-385-8057</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ks-potashcanada.com</t>
+        </is>
+      </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; search-engine snippet of ks-potashcanada.com (not fetched directly)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -8286,7 +8791,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet of ks-potashcanada.com (not fetched directly)); This Vancouver office serves as logistics/operations coordination for the Pacific Coast Terminals potash facility in Port Moody; the company's main headquarters is in Saskatoon, SK. No email surfaced in the available snippet.</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8831,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (Fasken CCAA records, Wikipedia, not fetched directly)</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -8331,7 +8841,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>REVIEW: this company went through CCAA restructuring (approved 2006), was acquired by a Vitol Group unit in 2009, and closed its only operating mine (Quinsam) in 2016. No current independent operations found. Not a live Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8881,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; sixthwave.com (checked; not a mining company)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -8376,7 +8891,12 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>REVIEW: Sixth Wave Innovations develops nanotechnology-based molecular extraction/detection technology (agriculture safety, virus detection) — not a mining company. Likely a NAICS misclassification; not a mining prospect.</t>
         </is>
       </c>
     </row>
@@ -8394,6 +8914,11 @@
       <c r="C129" t="n">
         <v>11.74</v>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>543 Granville St, Suite 501</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8404,14 +8929,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>V6C 1X8</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>info@metallaroyalty.com</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>604-696-0741</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>www.metallaroyalty.com</t>
+        </is>
+      </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; https://www.metallaroyalty.com/contact/details/</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -8421,7 +8966,12 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.metallaroyalty.com/contact/details/); Shares the same Suite 501, 543 Granville St address as EMX Royalty Corporation (also a row in this workbook) — a known registered-agent-suite pattern among Vancouver royalty companies, not an error.</t>
         </is>
       </c>
     </row>
@@ -8439,6 +8989,11 @@
       <c r="C130" t="n">
         <v>11.67</v>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1066 West Hastings Street</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8449,14 +9004,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>604-681-7500</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>www.ledcor.com</t>
+        </is>
+      </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; search-engine snippet of ledcor.com and 411directoryassistance.ca (not fetched directly)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -8466,7 +9036,12 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet of ledcor.com and 411directoryassistance.ca (not fetched directly)); Ledcor CMI is the mining-services division of Ledcor Group of Companies, a private construction/engineering conglomerate — a services provider to the mining industry, not a mine owner-operator itself. No email surfaced in available sources.</t>
         </is>
       </c>
     </row>
@@ -8501,7 +9076,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (securityholder meeting circular, not fetched directly)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -8511,7 +9086,12 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>REVIEW: as of February 2026, Golden Lake Exploration is in the process of being acquired by McEwen Inc, with a securityholder vote held March 18, 2026 to approve the transaction. Recommend verifying current status before treating as an independent prospect — it may have already closed by the time this is reviewed.</t>
         </is>
       </c>
     </row>
@@ -8544,9 +9124,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Len De Melt</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>President and CEO</t>
+        </is>
+      </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (CSE listing, newswire press releases; no official company website located)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -8556,7 +9146,12 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (CSE listing, newswire press releases; no official company website located)); ILLEGIBLE: street_address, contact_email, contact_phone, website — no official company site could be located distinct from third-party listings (CSE, BNamericas, TradingView). Company has a Vancouver corporate HQ and Lima, Peru administrative HQ per secondary sources; recommend a direct BC Registry or SEDAR+ search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -8591,7 +9186,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-03.png</t>
+          <t>chat-listing-2026-08-07-03.png; secondary sources (Anglo American/Conuma Resources sale press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -8601,7 +9196,12 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>REVIEW: Anglo American completed the sale of Peace River Coal to Conuma Resources Limited on February 11, 2025. The asset has been on care and maintenance since 2014 with no announced timeline for resuming production. Not an independent Vancouver corporate prospect.</t>
         </is>
       </c>
     </row>
@@ -8619,6 +9219,11 @@
       <c r="C134" t="n">
         <v>11.67</v>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>701 West Georgia Street, Suite 1500</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8629,14 +9234,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>V7Y 1C6</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Anthony F. Ciali</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>1 604 601-5610</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>www.andeangoldltd.com</t>
+        </is>
+      </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; search-engine snippet (site itself could not be reached — connection error, not a policy block); the search results explicitly flagged this data as dating to 2015 or earlier</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -8646,7 +9271,12 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (site itself could not be reached — connection error, not a policy block); the search results explicitly flagged this data as dating to 2015 or earlier); This contact information is stale (pre-2015 per the search tool's own caveat) and could not be independently re-verified due to a connection failure on andeangoldltd.com. Recommend treating as unconfirmed rather than current.</t>
         </is>
       </c>
     </row>
@@ -8664,6 +9294,11 @@
       <c r="C135" t="n">
         <v>11.67</v>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>675 West Hastings Street, Suite 611</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8674,14 +9309,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>V6B 1N2</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Tony Perri</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Investor Relations Manager</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>virginiaenergyresources.com</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; search-engine snippet (direct fetch returned 403; underlying site appears to use old .asp pages dated 2019-2021)</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -8691,7 +9346,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (direct fetch returned 403; underlying site appears to use old .asp pages dated 2019-2021)); Site content referenced in search results looks dated (2019-2021 news pages); could not independently confirm this is still current. Recommend verifying directly before treating as confirmed-active.</t>
         </is>
       </c>
     </row>
@@ -8709,6 +9369,11 @@
       <c r="C136" t="n">
         <v>11.49</v>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1188 West Georgia Street, Suite 1830</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8719,14 +9384,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>V6E 4A2</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>604.396.8222; toll free 1.855.396.8222</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>www.uraniumroyalty.com</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; https://www.uraniumroyalty.com/contact/</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -8736,7 +9416,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.uraniumroyalty.com/contact/); Shares the same 1188 West Georgia Street, Suite 1830 address as Gold Royalty Corp and Uranium Energy Corp's Vancouver office (both already rows in this workbook) — a known registered-agent-suite cluster, not an error. ILLEGIBLE: contact_email — obfuscated on the official page. The company's own news feed shows a 'Sweetwater Transaction' completed and a shareholder-approved 'Arrangement' both in July 2026 — a material recent corporate action worth a stage-3 news check if this company is of interest.</t>
         </is>
       </c>
     </row>
@@ -8769,9 +9454,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>cambriagold.com</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; cambriagold.com/contact/ (blocked by an active bot-challenge/CAPTCHA redirect; not bypassed)</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -8781,7 +9471,12 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Live fetch of the contact page was redirected to an active CAPTCHA challenge page, consistent with the hard rule against bypassing active bot defenses. No address/contact recorded. Company itself is confirmed active (formerly Ascot Resources, renamed; developing the Premier and Red Mountain gold projects near Stewart, BC) per secondary sources.</t>
         </is>
       </c>
     </row>
@@ -8799,6 +9494,11 @@
       <c r="C138" t="n">
         <v>10.89</v>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2999 North 44th Street, Suite 300, Concord Place</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8814,9 +9514,29 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Melissa Mackie</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Vice President, Investor Relations and Communications</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>647-533-4536</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>www.gunnisoncopper.com</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; https://gunnisoncopper.com/contact/contact-us</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -8826,7 +9546,12 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Phoenix (https://gunnisoncopper.com/contact/contact-us); CONFLICT: province=British Columbia|AZ (https://gunnisoncopper.com/contact/contact-us); CONFLICT: country=Canada|United States (https://gunnisoncopper.com/contact/contact-us); REVIEW: the company's own official contact page lists its head office in Phoenix, Arizona — not Vancouver — directly conflicting with the D&amp;B listing. Recorded the verified Phoenix address rather than inferring a Vancouver one. ILLEGIBLE: contact_email — obfuscated on the official page.</t>
         </is>
       </c>
     </row>
@@ -8861,7 +9586,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; secondary sources (Teck/Conuma Resources sale press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -8871,7 +9596,12 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>REVIEW: Teck Resources sold the Quintette mine and related assets to a Conuma Resources subsidiary for $120 million, completed February 2023; the mine had been on care and maintenance since 2000 and restarted under Conuma's ownership in September 2024. Quintette Coal Limited itself is not an independently operating Vancouver entity.</t>
         </is>
       </c>
     </row>
@@ -8906,7 +9636,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; no official site or public record located</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -8916,7 +9646,12 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>REVIEW: could not locate an official website or clear public record for this entity distinct from several unrelated companies with similar names (Neos Group, National Energy Equipment). Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -8934,6 +9669,11 @@
       <c r="C141" t="n">
         <v>10.1</v>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1188 West Georgia Street, Suite 1830</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -8944,14 +9684,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>V6E 4A2</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Peter Behncke</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Director, Corporate Development &amp; Investor Relations</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>+1 (604) 396 3066; toll free 1 (833) 396-3066</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>www.GoldRoyalty.com</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-07-01.png</t>
+          <t>chat-listing-2026-08-07-01.png; https://www.goldroyalty.com/contact/contact-details/</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -8961,7 +9726,12 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.goldroyalty.com/contact/contact-details/); ILLEGIBLE: contact_email — obfuscated on the official page. Same building/suite as Uranium Royalty Corp and Uranium Energy Corp's Vancouver office (registered-agent-suite cluster). A separate 'Registered and Records Office' is listed at 1000 Cathedral Place, 925 West Georgia Street — a law-firm-style address, likely legal counsel rather than an operating office.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -619,9 +619,19 @@
           <t>Newmont Corporation is a gold producer and also engaged in the production of copper, silver, lead and zinc. The Company's world-class portfolio of assets, prospects and talent is anchored in favorable mining jurisdictions in Africa, Australia, Latin America &amp; Caribbean, North America, and Papua New Guinea.</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>capital raise: announced enhanced capital allocation framework including a $6 billion share repurchase program and $1.1 billion annual dividend payout, alongside FY2025 results and 2026 guidance; management change: appointed Brian Tabolt as CFO, Mark Rodgers as COO, and David Thornton as CTO, effective July 1, 2026</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://www.newmont.com/investors/news-release/news-details/2026/Newmont-Reports-Fourth-Quarter-and-Full-Year-2025-Results-Provides-2026-Guidance-and-Announces-Enhanced-Capital-Allocation-Framework/default.aspx; https://www.businesswire.com/news/home/20260615487768/en/Newmont-Announces-Key-Executive-Appointments-for-the-Next-Phase-of-Delivery</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png; chat-listing-2026-08-05-01.png</t>
+          <t>chat-example-listing-01.png; chat-example-detail-newmont-01.png; chat-listing-2026-08-05-01.png; stage-3 news check</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -684,9 +694,19 @@
           <t>1.877.759.6226 (toll-free Canada/US); 604.699.4257 (outside Canada/US)</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>expansion/new project: board approved construction of the Highland Valley Copper Mine Life Extension, a US$2.1-2.4 billion investment extending the mine's life to 2046, construction began August 2025; hiring/expansion signal: the Highland Valley Copper Mine Life Extension project is expected to generate approximately 2,900 jobs during the construction phase</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://www.teck.com/news/news-releases/2025/teck-announces-construction-of-highland-valley-copper-mine-life-extension-to-proceed; https://www.teck.com/news/news-releases/2025/teck-announces-construction-of-highland-valley-copper-mine-life-extension-to-proceed</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.teck.com/investors/contact-us/</t>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.teck.com/investors/contact-us/; stage-3 news check</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -759,9 +779,19 @@
           <t>+1 416 361 6400 (International); +1 877 961 6400 (Toll Free)</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>expansion/new project: achieved commercial production of the Kansanshi S3 Expansion (Zambia) at the end of 2025; hiring/expansion signal: adding approximately 1,000 jobs as the Cobre Panama mine restart nears, with stockpile processing and hiring underway</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://www.first-quantum.com/news/first-quantum-minerals-announces-2025-preliminary-production-and-2026-2028-guidance/; https://www.mining.com/first-quantum-adds-1000-jobs-as-cobre-panama-restart-nears/</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.first-quantum.com/contact/</t>
+          <t>chat-example-listing-01.png; chat-listing-2026-08-05-01.png; https://www.first-quantum.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -844,9 +874,19 @@
           <t>www.lundinmining.com</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>capital raise: expanded its committed credit facility from US$1.75 billion to US$4.5 billion (a 157% increase), backed by an international banking syndicate; expansion/new project: published the Vicuna Project technical report (Feb 16, 2026) describing a potential top-five global copper/gold/silver mine, with $395 million in 2026 capex forecast (50% basis) ahead of a year-end sanctioning decision</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://simplywall.st/stocks/ca/materials/tsx-lun/lundin-mining-shares/news/lundin-mining-refines-identity-and-credit-to-back-vicua-copp; https://www.lundinmining.com/news/2026/lundin-mining-capital-markets-day-highlights-strategic-vision-for-leading-growth-and-shareholder-returns</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://www.lundinmining.com/about/contact/</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.lundinmining.com/about/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -894,9 +934,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>expansion/new project: achieved commercial production at the Goose Mine in Nunavut, early October 2025 (B2Gold's first Canadian gold-producing mine); expansion/new project: approved a development decision on the Antelope underground deposit at the Otjikoto Mine (Namibia), announced September 15, 2025, to extend mine life</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://www.b2gold.com/news-media/news-releases/news-details/2025/B2Gold-Reports-Q3-2025-Results/default.aspx; https://www.miningnewsnorth.com/story/2026/01/15/mining-explorers-2025/b2gold-opens-golden-goose-mine-in-nunavut/9451.html</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png</t>
+          <t>chat-listing-2026-08-05-01.png; stage-3 news check</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -906,7 +956,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Contact page remains blocked by an active Cloudflare bot-challenge (per earlier batch); this news check used general search results, not a direct b2gold.com fetch.</t>
         </is>
       </c>
     </row>
@@ -964,9 +1019,19 @@
           <t>+1 (604) 806-3191 (direct); +1 (604) 684-1175 (general office)</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>acquisition/merger: acquired the Juanicipio mine (Mexico), completed September 2025, since producing 2.5 million ounces of silver and generating a $44 million dividend in December; expansion/new project: advancing a conceptual plan for phased development of new mineral resources at the Timmins operation to extend mine life</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://panamericansilver.com/news/pan-american-silver-achieves-2025-production-guidance-and-provides-guidance-for-2026/; https://panamericansilver.com/news/pan-american-silver-achieves-2025-production-guidance-and-provides-guidance-for-2026/</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://panamericansilver.com/about/contact/</t>
+          <t>chat-listing-2026-08-05-01.png; https://panamericansilver.com/about/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1079,9 +1144,19 @@
           <t>604-684-8894 (general); 866-684-8894 (toll-free)</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>capital raise: Orion investment of up to $360 million for a 25% interest in the Santo Domingo project; expansion/new project: Mantoverde Optimized Project construction underway (sanctioned August 2025); Santo Domingo final investment decision expected H2 2026</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://capstonecopper.com/news/capstone-copper-announces-up-to-360-million-investment-from-orion-for-25-interest-in-santo-domingo/; https://capstonecopper.com/news/capstone-copper-announces-2026-guidance/; </t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://capstonecopper.com/contact-us/</t>
+          <t>chat-listing-2026-08-05-01.png; https://capstonecopper.com/contact-us/; stage-3 news check</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1129,9 +1204,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>acquisition/merger: acquired an additional silver stream on the Antamina mine (Peru) through a new partnership with BHP, valued at US$4.3 billion, Q1 2026; acquisition/merger: acquired a gold and silver stream on the Jervois Project (Australia) with KGL Resources, announced April 1, 2026 — Wheaton's first Australian streaming deal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://www.wheatonpm.com/news/news-details/2026/Wheaton-Precious-Metals-Announces-Acquisition-of-Additional-Silver-Stream-on-Antamina-Through-New-Partnership-with-BHP/default.aspx; https://www.wheatonpm.com/news/news-details/2026/Wheaton-Precious-Metals-Announces-Acquisition-of-a-Gold-and-Silver-Stream-on-the-Jervois-Project-Through-a-Partnership-with-KGL-Resources/default.aspx</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://www.wheatonpm.com/contact/ (blocked)</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.wheatonpm.com/contact/ (blocked); stage-3 news check</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1146,7 +1231,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>ILLEGIBLE: contact_email, contact_phone — wheatonpm.com contact page returned an active Cloudflare bot-challenge (cf-mitigated: challenge); not bypassed.</t>
+          <t>ILLEGIBLE: contact_email, contact_phone — wheatonpm.com contact page returned an active Cloudflare bot-challenge (cf-mitigated: challenge); not bypassed.; Note: wheatonpm.com/news/ pages loaded fine for this check even though /contact/ remains behind an active Cloudflare challenge — the block appears path-specific, not site-wide.</t>
         </is>
       </c>
     </row>
@@ -1214,9 +1299,19 @@
           <t>www.equinoxgold.com</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>acquisition/merger: completed merger with Orla Mining Ltd, July 31, 2026, creating a combined ~700,000 oz/year Canadian gold producer; expansion/new project: Valentine Phase 2 expansion starting Q4 2026; South Railroad (Nevada) permits/start expected Q3 2026; Castle Mountain Phase 2 (California) federal Record of Decision expected December 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.equinoxgold.com/news/equinox-and-orla-mining-combine-to-create-north-americas-new-senior-gold-producer-built-to-grow-built-to-last/; https://www.equinoxgold.com/news/equinox-gold-delivers-strong-second-quarter-results-increases-2026-production-guidance-following-successful-completion-of-the-orla-mining-merger-quarterly-dividend-increased-by-50/; ; </t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://www.equinoxgold.com/contact/</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.equinoxgold.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1231,7 +1326,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.equinoxgold.com/contact/); General public email also available: info@equinoxgold.com.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://www.equinoxgold.com/contact/); General public email also available: info@equinoxgold.com.; This confirms Orla Mining Ltd (a separate row in this workbook) merged into Equinox Gold effective July 31, 2026 — see the corresponding REVIEW update on that row.</t>
         </is>
       </c>
     </row>
@@ -1299,9 +1394,19 @@
           <t>www.eldoradogold.com</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>expansion/new project: Skouries project (Greece) construction ~90% complete overall (78% for phase 2) as of Dec 31, 2025; first concentrate now expected Q3 2026, commercial production Q4 2026; capital cost estimate $1.16 billion; mill expansion to 650 ktpa underway as part of 2026 growth capital plan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.eldoradogold.com/investors/news-releases/eldorado-gold-transformational-growth-greece-2026; ; ; </t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker)</t>
+          <t>chat-listing-2026-08-05-01.png; eldoradogold.com/contact-us (live fetch 403'd; sourced from search-engine snippet of the company's own official page, not a data broker); stage-3 news check</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2869,9 +2974,19 @@
           <t>www.orlamining.com</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>acquisition/merger: merged into Equinox Gold Corp, completed July 31, 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://www.equinoxgold.com/news/equinox-and-orla-mining-combine-to-create-north-americas-new-senior-gold-producer-built-to-grow-built-to-last/</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)</t>
+          <t>chat-listing-2026-08-05-03.png; orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page); stage-3 news check</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -2886,7 +3001,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)); Live fetch of the contact page 404'd (URL structure differs from what search results implied); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
+          <t>CONFLICT: province=British Columbia|BC (orlamining.com contact page (live fetch 404'd on the paths tried; sourced from search-engine snippet of the company's own official page)); Live fetch of the contact page 404'd (URL structure differs from what search results implied); data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.; REVIEW: Orla Mining merged into Equinox Gold Corp (already a verified row in this workbook) effective July 31, 2026, and is no longer an independent entity. This was caught while researching Equinox Gold's own stage-3 news — an example of the stage-3/REVIEW-flag overlap documented in CLAUDE.md.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -1479,9 +1479,19 @@
           <t>www.oceanagold.com</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>expansion/new project: planning ~$280 million in 2026 growth capital, including ~$150 million toward the Waihi North project (New Zealand); expansion/new project: Haile mine (South Carolina) expected to produce ~35% more gold in 2026 with a completed waste-removal program opening access to higher-grade ore; capital raise: increased 2025 share buyback program by 75% to $175 million</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://www.kitco.com/opinion/investment-trends/2026-03-16/oceanagold-targets-2026-growth-haile-expansion-and-nyse; https://www.kitco.com/opinion/investment-trends/2026-03-16/oceanagold-targets-2026-growth-haile-expansion-and-nyse; https://www.kitco.com/opinion/investment-trends/2026-03-16/oceanagold-targets-2026-growth-haile-expansion-and-nyse</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://oceanagold.com/contact-us</t>
+          <t>chat-listing-2026-08-05-01.png; https://oceanagold.com/contact-us; stage-3 news check</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1544,9 +1554,19 @@
           <t>www.evr.com</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>acquisition/merger: Glencore received final regulatory approval for its acquisition of a 77% interest in Elk Valley Resources (EVR) for US$6.93 billion, now operating EVR as a joint venture with Nippon Steel (20%) and POSCO (3%)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://www.glencore.com/media-and-insights/news/glencore-receives-final-regulatory-approval-for-the-acquisition-of-elk-valley-resources</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://www.glencore.ca/en/evr</t>
+          <t>chat-listing-2026-08-05-01.png; https://www.glencore.ca/en/evr; stage-3 news check</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1561,7 +1581,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>EVR Operations (Elk Valley Resources) is a Glencore subsidiary. Site describes a new Vancouver headquarters but does not publish a street address on this page; ILLEGIBLE: street_address.</t>
+          <t>EVR Operations (Elk Valley Resources) is a Glencore subsidiary. Site describes a new Vancouver headquarters but does not publish a street address on this page; ILLEGIBLE: street_address.; REVIEW-adjacent: EVR is now majority-owned and operated by Glencore, a company not otherwise in this workbook. Not flagging as REVIEW since EVR still operates under its own name with its own Vancouver office (already verified in an earlier batch), but worth knowing outreach may now need to account for Glencore's ownership. EVR operates four steelmaking coal mines in the Elk Valley employing ~5,500 people — a large regional workforce, though this is existing headcount, not a new hiring signal.</t>
         </is>
       </c>
     </row>
@@ -1619,9 +1639,19 @@
           <t>www.lundingold.com</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>expansion/new project: evaluating expanding Fruta del Norte mine/mill capacity beyond 5,500 t/d, with an investment decision targeted for H2 2026; expansion/new project: launched its largest-ever US$85 million exploration program (133,000 metres of drilling) to extend mine life and evaluate the Fruta del Norte South deposit, development decision expected H1 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://lundingold.com/news/lundin-gold-provides-2026-guidance-and-strategic-t-122826/; https://lundingold.com/news/lundin-gold-provides-2026-guidance-and-strategic-t-122826/</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; https://lundingold.com/contact/</t>
+          <t>chat-listing-2026-08-05-01.png; https://lundingold.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1636,7 +1666,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://lundingold.com/contact/); General public email/phone used; a named VP Investor Relations (Brendan Creaney) appeared in search results but was not present on the official contact or corporate-information pages checked, so not recorded.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://lundingold.com/contact/); General public email/phone used; a named VP Investor Relations (Brendan Creaney) appeared in search results but was not present on the official contact or corporate-information pages checked, so not recorded.; Company explicitly stated these expansions are funded from operating cash flow, no capital raise announced.</t>
         </is>
       </c>
     </row>
@@ -1694,9 +1724,19 @@
           <t>www.fortunamining.com</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>expansion/new project: approved a 30% capacity expansion of the Seguela Gold Mine (Cote d'Ivoire), $109 million construction capital, funded from operating cash flow; construction begins H2 2026, underground mining (Sunbird) starts Q2 2027, full ramp-up H2 2028; capital raise: returned $80.2 million to shareholders via share repurchases in Q2 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.globenewswire.com/news-release/2026/07/30/3335699/0/en/Fortuna-Approves-30-Capacity-Expansion-of-the-S%C3%A9gu%C3%A9la-Gold-Mine-in-C%C3%B4te-d-Ivoire.html; https://investingnews.com/fortuna-reports-second-quarter-2026-production-of-72217-gold-equivalent-ounces-and-advances-key-growth-initiatives/; </t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
+          <t>chat-listing-2026-08-05-02.png; fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page); stage-3 news check</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1711,7 +1751,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.</t>
+          <t>CONFLICT: province=British Columbia|BC (fortunamining.com/contact/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)); Live fetch returned 403; data sourced from a search-engine snippet of the same official page. Recommend re-verifying directly if precision matters.; The Seguela expansion (30% capacity increase, ~10 years of 200,000+ oz/year production) is a strong hiring/expansion signal, though no specific job-count figure was published.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1786,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; SEC 6-K filing + secondary sources (not fetched directly)</t>
+          <t>chat-listing-2026-08-05-02.png; SEC 6-K filing + secondary sources (not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1761,7 +1801,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>REVIEW: Atlatsa underwent a 'going private' restructuring in 2018-2019 and is now headquartered in Sandton, South Africa per available records; the Vancouver address in the D&amp;B listing may be a stale registered/agent address rather than an active operating office. Recommend manual verification before treating as a live Vancouver prospect.</t>
+          <t>REVIEW: Atlatsa underwent a 'going private' restructuring in 2018-2019 and is now headquartered in Sandton, South Africa per available records; the Vancouver address in the D&amp;B listing may be a stale registered/agent address rather than an active operating office. Recommend manual verification before treating as a live Vancouver prospect.; Skipped dedicated news search — already flagged REVIEW (went private, HQ relocated to Sandton, South Africa in 2018-19). No indication this status has changed.</t>
         </is>
       </c>
     </row>
@@ -1819,9 +1859,19 @@
           <t>www.ero.com</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>expansion/new project: achieved commercial production at the Tucuma mine (Brazil), Q3 2025, now expected to contribute ~40% of 2026 revenue; capital raise: amended Senior Credit Facility to increase the limit from $150M to $200M and extend maturity to December 2028 (January 2025); capital raise: received $50 million upfront cash under streaming agreements, bringing total streaming proceeds to $160 million</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://www.ainvest.com/news/ero-copper-tucuma-project-track-h1-2025-commercial-production-2505/; https://www.investing.com/news/stock-market-news/ero-copper-upgraded-to-b-by-fitch-on-tucuma-rampup-93CH-4418181; https://www.investing.com/news/stock-market-news/ero-copper-upgraded-to-b-by-fitch-on-tucuma-rampup-93CH-4418181</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://www.ero.com/contact-us/</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.ero.com/contact-us/; stage-3 news check</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1889,9 +1939,19 @@
           <t>www.chinagoldintl.com</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>expansion/new project: completed a mineral resource/reserve update and NI 43-101 technical report for the Jiama Copper-Gold Polymetallic Project (Tibet), June 30, 2026, showing a 51% rise in total reserves and a strategic shift toward underground mining</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://simplywall.st/stocks/ca/materials/tsx-cgg/china-gold-international-resources-shares/news/should-jiamas-underground-reserve-surge-reshape-the-long-ter/amp</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://www.chinagoldintl.com/contact/</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.chinagoldintl.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1906,7 +1966,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.chinagoldintl.com/contact/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://www.chinagoldintl.com/contact/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.; A 2026 shareholder vote on capital mandates and 'key China National Gold deals' was mentioned in search results without further detail; not recorded as a specific item since no primary source with details was found.</t>
         </is>
       </c>
     </row>
@@ -1959,9 +2019,19 @@
           <t>www.international-petroleum.com</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>expansion/new project: achieved first steam injection at the Blackrod Phase 1 project, December 2025, first oil now expected Q3 2026 (a quarter ahead of original guidance); capital raise: increased Canadian revolving credit facility to CAD 348.5 million and extended maturity to May 2028, April 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/02/10/3235015/0/en/International-Petroleum-Corporation-Announces-2025-Year-End-Financial-and-Operational-Results-and-2026-Budget-Reserves-and-Guidance.html; https://www.international-petroleum.com/post/ipc-announces-2025-year-end-financial-and-operational-results-and-2026-budget-reserves-and-guidance</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://www.international-petroleum.com/contact-us</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.international-petroleum.com/contact-us; stage-3 news check</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2029,9 +2099,19 @@
           <t>www.artemisgoldinc.com</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>expansion/new project: Phase 1A Blackwater mill expansion (33% capacity increase, 6 to 8 Mtpa) 57% complete as of Q2 2026, on schedule for Q4 2026 commissioning, cost raised to $120 million; expansion/new project: Expanded Phase 2 (EP2) project targeting 21 Mtpa throughput and 500,000+ oz/year gold production by end of 2028, $1.44 billion cost; capital raise: issued $450 million of five-year senior unsecured notes to repay revolving credit facility, ending 2025 with $852.7 million pro-forma available liquidity</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/artemis-gold-posts-strong-2025-results-and-accelerates-blackwater-expansion; https://www.artemisgoldinc.com/news/media-releases/2025/artemis-gold-announces-33-increase-to-phase-1-processing-plant-capacity-at-blackwater-mine-and-places-order-for-long-lead-equipment-for-phase-2-expansion; https://www.tipranks.com/news/company-announcements/artemis-gold-posts-strong-2025-results-and-accelerates-blackwater-expansion</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://www.artemisgoldinc.com/contact/contact-details/</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.artemisgoldinc.com/contact/contact-details/; stage-3 news check</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2046,7 +2126,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.artemisgoldinc.com/contact/contact-details/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://www.artemisgoldinc.com/contact/contact-details/); ILLEGIBLE: contact_email — page uses email obfuscation ('[email protected]' placeholder); not decoded.; The EP2 expansion (targeting production growth to 500,000+ oz/year) is a major hiring/expansion signal for the Blackwater site, though no specific headcount figure was published.</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2171,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook)</t>
+          <t>chat-listing-2026-08-05-02.png; SEC/newmont.com merger announcement (secondary sources, not fetched directly); derived from Newmont Corporation's verified address (already a row in this workbook); stage-3 news check</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2106,7 +2186,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as acquirer Newmont Corporation (acquired Goldcorp in 2019). Not independently verified as this entity's own filed address.</t>
+          <t>REVIEW: Goldcorp was acquired by Newmont in April 2019 and is now a wholly-owned Newmont subsidiary; the Vancouver office folded into Newmont's North America regional office (Newmont Corporation is already a separate row in this workbook). Recommend treating this as the same physical office as Newmont rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from Newmont Corporation's verified address (already a row in this workbook)); Same registered office as acquirer Newmont Corporation (acquired Goldcorp in 2019). Not independently verified as this entity's own filed address.; Skipped dedicated news search — already flagged REVIEW (folded into Newmont Corporation after the 2019 merger; any current news would appear under Newmont Corporation's own stage-3 entry, already checked in batch 1).</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -2294,9 +2294,19 @@
           <t>www.mereninc.com</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>expansion/new project: preparing 2026 drilling campaigns across Nigerian producing hubs (Agbami, Akija, Aegina, Akpo), rigs contracted; capital raise: refinanced its reserves-based lending facility, strengthening liquidity (Q1 2026)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://www.directorstalkinterviews.com/meren-energy-sets-out-growth-priorities-after-first-quarter-update/4121255340; https://www.directorstalkinterviews.com/meren-energy-highlights-strong-earnings-liquidity-and-african-market-positioning/4121255787</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://mereninc.com/contact-us/</t>
+          <t>chat-listing-2026-08-05-02.png; https://mereninc.com/contact-us/; stage-3 news check</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2369,9 +2379,19 @@
           <t>www.firstmajestic.com</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>expansion/new project: increased 2026 capex budget to $318-344 million (from $213-236 million), primarily for the Jerritt Canyon restart (Nevada, $75 million) and Santa Elena plant expansion to 3,500 tpd; acquisition/merger: sold the San Martin Silver Mine for US$90 million (agreement, July 2026) and the Del Toro Silver Mine to Sierra Madre Gold and Silver (completed 2026, announced Dec 2025)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/first-majestic-silver-lifts-2026-guidance-on-strong-q2-output-and-mexican-mine-expansion; https://www.tipranks.com/news/company-announcements/first-majestic-silver-lifts-2026-guidance-on-strong-q2-output-and-mexican-mine-expansion</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://www.firstmajestic.com/contact/contact-details/</t>
+          <t>chat-listing-2026-08-05-02.png; https://www.firstmajestic.com/contact/contact-details/; stage-3 news check</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2386,7 +2406,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.firstmajestic.com/contact/contact-details/); General public email used; no named individual confirmed on the official contact page itself.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://www.firstmajestic.com/contact/contact-details/); General public email used; no named individual confirmed on the official contact page itself.; The Jerritt Canyon restart is a hiring/expansion signal (new underground equipment, 12,800+ metres of exploration drilling) though no specific headcount figure was published.</t>
         </is>
       </c>
     </row>
@@ -2439,9 +2459,19 @@
           <t>www.aris-mining.com</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>expansion/new project: advancing the Marmato bulk mine and CIP plant expansion (Colombia), first gold expected Q4 2026, Lower Mine expanded 25% to 5,000 tpd, total project cost risen to ~$400 million; expansion/new project: Segovia and Marmato expansions together targeting ~500,000 oz/year gold production</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/aris-mining-posts-strong-q2-2026-results-and-advances-marmato-expansion; https://www.tipranks.com/news/company-announcements/aris-mining-posts-strong-q2-2026-results-and-advances-marmato-expansion</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://aris-mining.com/contact-us/</t>
+          <t>chat-listing-2026-08-05-02.png; https://aris-mining.com/contact-us/; stage-3 news check</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2456,7 +2486,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://aris-mining.com/contact-us/); General public email used; no Vancouver phone number published on the official contact page (only a Colombia office phone). No named individual confirmed.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://aris-mining.com/contact-us/); General public email used; no Vancouver phone number published on the official contact page (only a Colombia office phone). No named individual confirmed.; Company stated no equity financing since Feb 2021 and no current plans to issue securities, funding growth from operating cash flow.</t>
         </is>
       </c>
     </row>
@@ -2514,9 +2544,19 @@
           <t>imperialmetals.com</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>expansion/new project: advancing a feasibility study for the Red Chris Block Cave underground expansion project, with completion and possible joint-venture approval expected H2 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/02/19/3241640/0/en/Imperial-Provides-Update-on-Red-Chris-2025-Production-and-Production-Guidance-for-2026.html</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; https://imperialmetals.com/contact/</t>
+          <t>chat-listing-2026-08-05-02.png; https://imperialmetals.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2531,7 +2571,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://imperialmetals.com/contact/); General public email used; no named individual confirmed on the official contact page itself.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://imperialmetals.com/contact/); General public email used; no named individual confirmed on the official contact page itself.; Red Chris is majority-owned/operated by Newmont (already a row in this workbook); Imperial holds a 30% interest. Mount Polley 2026 guidance also confirmed active operations.</t>
         </is>
       </c>
     </row>
@@ -2594,9 +2634,19 @@
           <t>www.edrsilver.com</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>expansion/new project: Terronera mine (Mexico) commenced commercial production October 1, 2025, ramping toward 30% production growth in 2026 (2,000 t/d plant throughput); capital raise/expansion: increased 2026 capex guidance to $181 million (from $157 million), including $48 million for Pitarrilla and $18 million for Kolpa infrastructure; acquisition/merger: sold the Bolanitos mine, January 2026, as part of asset rebalancing</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/news/company-news/endeavour-silver-july-2026-slides-30-production-growth-targets-93CH-4825967; https://www.tipranks.com/news/company-announcements/endeavour-silver-boosts-q2-2026-output-as-terronera-and-kolpa-ramp-up; https://www.tipranks.com/news/company-announcements/endeavour-silver-boosts-q2-2026-output-as-terronera-and-kolpa-ramp-up</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
+          <t>chat-listing-2026-08-05-02.png; edrsilver.com/contact-us/contact-us/ (live fetch 403'd; sourced from search-engine snippet of the company's own official page); stage-3 news check</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2646,7 +2696,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-02.png; secondary sources (AuRico Gold acquisition press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-02.png; secondary sources (AuRico Gold acquisition press releases, not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2661,7 +2711,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>REVIEW: Northgate Minerals was acquired by and amalgamated into AuRico Gold in October 2011 (a historical transaction); AuRico itself later merged with Alamos Gold in 2015. This entity has not existed independently for over a decade — the D&amp;B listing entry is almost certainly stale/historical, not a current Vancouver prospect.</t>
+          <t>REVIEW: Northgate Minerals was acquired by and amalgamated into AuRico Gold in October 2011 (a historical transaction); AuRico itself later merged with Alamos Gold in 2015. This entity has not existed independently for over a decade — the D&amp;B listing entry is almost certainly stale/historical, not a current Vancouver prospect.; Skipped dedicated news search — already flagged REVIEW (absorbed into AuRico Gold in 2011, over a decade defunct). No indication this status has changed.</t>
         </is>
       </c>
     </row>
@@ -2719,9 +2769,19 @@
           <t>www.asantegold.com</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>capital raise: completed a $500 million financing package by August 2025 to fund Bibiani ramp-up, including a $175 million commitment from Appian Capital Advisory and a $170 million facility from Rand Merchant Bank, plus a $30 million accordion from GCB Bank; expansion/new project: commissioned the Bibiani sulphide treatment plant, gold recovery improved from 60% to over 90% following oxygen plant installation (December 2025), targeting ~450,000 oz in 2026 from Bibiani and Chirano combined</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://www.ecofinagency.com/news/1906-47334-asante-gold-seeks-470-million-to-scale-up-production-in-ghana; https://www.ainvest.com/news/asante-gold-operational-turnaround-growth-potential-2026-2512/</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://asantegold.com/contact</t>
+          <t>chat-listing-2026-08-05-03.png; https://asantegold.com/contact; stage-3 news check</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2794,9 +2854,19 @@
           <t>www.trekormetals.com</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>IPO/listing change: shareholders approved renaming Taseko Mines Limited to Trekor Metals Limited at the AGM held June 24, 2026 in Vancouver; expansion/new project: Florence Copper (Arizona) SX/EW plant began operations February 2026, first cathodes produced early March, 5.2 million lbs copper produced in Q2 2026; expansion/new project: Yellowhead Project (south-central BC) advancing, positioned as a potential future leading North American copper asset</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mining.com/taseko-seeks-rebrands-as-trekor-to-reflect-growth/; https://www.juniorminingnetwork.com/junior-miner-news/press-releases/738-tsx/tko/207318-trekor-announces-36-million-pounds-of-copper-production-from-gibraltar-and-florence-copper-in-the-second-quarter.html; </t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/</t>
+          <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2811,7 +2881,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://www.trekormetals.com/contact/); Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://www.trekormetals.com/contact/); Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.; This confirms and dates the Taseko-to-Trekor rename already noted in an earlier contact-verification batch.</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2916,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (National Observer, SEC filings — not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (National Observer, SEC filings — not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -2861,7 +2931,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>REVIEW: Petaquilla Minerals was delisted from the TSX in 2015, abandoned its only mine (Molejon, Panama) the same year, and by public reporting its listed phone/email were already disconnected years ago. Treat this D&amp;B listing entry as stale/inactive, not a current Vancouver prospect.</t>
+          <t>REVIEW: Petaquilla Minerals was delisted from the TSX in 2015, abandoned its only mine (Molejon, Panama) the same year, and by public reporting its listed phone/email were already disconnected years ago. Treat this D&amp;B listing entry as stale/inactive, not a current Vancouver prospect.; Skipped dedicated news search — already flagged REVIEW (delisted 2015, mine abandoned same year). No indication this status has changed.</t>
         </is>
       </c>
     </row>
@@ -2929,9 +2999,19 @@
           <t>www.k92mining.com</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>expansion/new project: Stage 3 process plant construction/commissioning completed under budget, first production October 2025, record 2025 annual production of 174 koz AuEq; expansion/new project: advancing the fully-funded Stage 4 expansion targeting 400,000+ oz/year by late 2027 (~200% throughput increase from 2025 levels, 1.8 Mtpa); expansion/new project: increasing 2026 exploration budget by 50%+ to US$31-35 million, up to 14 drill rigs active</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://pngmining.com/k92-posts-record-quarter-as-kainantu-development-surges/; https://www.mining.com/k92-minings-kainantu-expansion-pours-first-gold; https://www.k92mining.com/news/k92-mining-announces-2025-q4-and-annual-financial-13421/</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://k92mining.com/contact/</t>
+          <t>chat-listing-2026-08-05-03.png; https://k92mining.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -2946,7 +3026,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://k92mining.com/contact/)</t>
+          <t>CONFLICT: province=British Columbia|BC (https://k92mining.com/contact/); Stage 4 expansion (200% throughput increase) is a major hiring/expansion signal for the Kainantu operation, though no specific headcount figure was published for the Vancouver corporate office.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -3061,7 +3061,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (merger press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (merger press releases, not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>REVIEW: Leagold Mining merged into Equinox Gold Corp in March 2020 and was delisted; Equinox Gold is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.</t>
+          <t>REVIEW: Leagold Mining merged into Equinox Gold Corp in March 2020 and was delisted; Equinox Gold is already a separate row in this workbook. Recommend treating this as the same entity as Equinox Gold rather than an independent prospect.; Skipped dedicated news search — already flagged REVIEW (merged into Equinox Gold Corp, 2020).</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly); derived from First Majestic Silver Corp's verified address (already a row in this workbook)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (First Majestic acquisition press releases, not fetched directly); derived from First Majestic Silver Corp's verified address (already a row in this workbook); stage-3 news check</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from First Majestic Silver Corp's verified address (already a row in this workbook)); Same registered office as acquirer First Majestic Silver Corp (acquired Silvermex in 2012). Not independently verified as this entity's own filed address.</t>
+          <t>REVIEW: Silvermex Resources was acquired by First Majestic Silver Corp in July 2012 and delisted; First Majestic is already a separate row in this workbook. Recommend treating this as the same entity as First Majestic rather than an independent prospect.; CONFLICT: province=British Columbia|BC (derived from First Majestic Silver Corp's verified address (already a row in this workbook)); Same registered office as acquirer First Majestic Silver Corp (acquired Silvermex in 2012). Not independently verified as this entity's own filed address.; Skipped dedicated news search — already flagged REVIEW (acquired by First Majestic Silver, 2012).</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (teck.com project pages, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (teck.com project pages, not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>CONFLICT: city=Vancouver|Logan Lake (secondary sources (teck.com project pages, not fetched directly)); CONFLICT: province=British Columbia|BC (secondary sources (teck.com project pages, not fetched directly)); REVIEW: this is a Teck Resources operating partnership for the Highland Valley Copper mine near Logan Lake, BC — not a Vancouver office, and not separately contactable from Teck Resources Limited (already a row in this workbook). The D&amp;B listing's Vancouver location likely reflects Teck's corporate HQ, not this operation's actual site address.</t>
+          <t>CONFLICT: city=Vancouver|Logan Lake (secondary sources (teck.com project pages, not fetched directly)); CONFLICT: province=British Columbia|BC (secondary sources (teck.com project pages, not fetched directly)); REVIEW: this is a Teck Resources operating partnership for the Highland Valley Copper mine near Logan Lake, BC — not a Vancouver office, and not separately contactable from Teck Resources Limited (already a row in this workbook). The D&amp;B listing's Vancouver location likely reflects Teck's corporate HQ, not this operation's actual site address.; Skipped dedicated news search — the relevant news (Highland Valley Copper Mine Life Extension) was already captured under Teck Resources Limited's stage-3 entry in batch 1, since this is a Teck operating partnership, not a separate Vancouver office.</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; secondary sources (Zijin Mining acquisition press releases, not fetched directly)</t>
+          <t>chat-listing-2026-08-05-03.png; secondary sources (Zijin Mining acquisition press releases, not fetched directly); stage-3 news check</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>REVIEW: Nevsun Resources was fully acquired by Zijin Mining in a compulsory acquisition completed March 2019 and delisted; it has been a wholly-owned Zijin subsidiary for years. The D&amp;B listing entry is almost certainly stale, not a current independent Vancouver prospect.</t>
+          <t>REVIEW: Nevsun Resources was fully acquired by Zijin Mining in a compulsory acquisition completed March 2019 and delisted; it has been a wholly-owned Zijin subsidiary for years. The D&amp;B listing entry is almost certainly stale, not a current independent Vancouver prospect.; Skipped dedicated news search — already flagged REVIEW (wholly-owned Zijin Mining subsidiary since 2019).</t>
         </is>
       </c>
     </row>
@@ -3394,9 +3394,19 @@
           <t>www.silvercorpmetals.com</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>acquisition/merger: expanded into South America and Central Asia via acquisitions of Adventus Mining Corporation and Chaarat Gold Holdings, diversifying into copper and gold across three continents; capital raise: completed a $150 million convertible senior notes offering (Nov 2024) and launched a share buyback program (NCIB, up to ~4% of shares, starting Sept 19, 2025); expansion/new project: completed a 1,500 tpd mill expansion at the Ying Mine (China), operational by January 2025, boosting capacity to 4,000 tpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/silvercorp-metals-reports-strong-fiscal-2025-results-and-strategic-expansion; https://silvercorpmetals.com/silvercorp-renews-share-repurchase-program-2/; https://www.tipranks.com/news/company-announcements/silvercorp-metals-reports-strong-fiscal-2025-results-and-strategic-expansion</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://silvercorpmetals.com/contact-details/</t>
+          <t>chat-listing-2026-08-05-03.png; https://silvercorpmetals.com/contact-details/; stage-3 news check</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3446,7 +3456,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; opengovca.com Vancouver business licence listing (not the company's own site; no official site located)</t>
+          <t>chat-listing-2026-08-05-03.png; opengovca.com Vancouver business licence listing (not the company's own site; no official site located); stage-3 news check</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3461,7 +3471,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>REVIEW: could not locate an active official company website. Secondary sources describe it as formerly 'Leicester Diamond Mines' and reference an acquisition/merger. Likely an inactive shell or renamed entity; recommend manual verification before treating as a live prospect.</t>
+          <t>REVIEW: could not locate an active official company website. Secondary sources describe it as formerly 'Leicester Diamond Mines' and reference an acquisition/merger. Likely an inactive shell or renamed entity; recommend manual verification before treating as a live prospect.; Skipped dedicated news search — already flagged REVIEW (no verifiable official site located).</t>
         </is>
       </c>
     </row>
@@ -3519,9 +3529,19 @@
           <t>www.orezone.com</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>expansion/new project: Bomboré hard rock expansion (Burkina Faso) commissioned in 2025, first gold poured Dec 15, 2025, commercial production declared Jan 16, 2026, raising 2026 production guidance 45% to 170,000-185,000 oz; expansion/new project: advancing Bomboré Stage 2 hard rock expansion, targeting 220,000-250,000 oz/year, estimated cost $90-95 million; capital raise: closed a $24 million offering to fund Stage 2 and exploration; acquisition/merger: completed acquisition of the Casa Berardi gold mine from Hecla Mining Company</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/bombor-expansion-near-completion-production-131020997.html; https://www.mining-technology.com/news/orezone-bombore-gold-mine/; https://www.mining-technology.com/news/orezone-bombore-gold-mine/; https://www.globenewswire.com/news-release/2026/03/25/3262583/0/en/Orezone-Gold-Reports-Fourth-Quarter-2025-Results-and-Provides-2026-Guidance.html</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://orezone.com/contact/</t>
+          <t>chat-listing-2026-08-05-03.png; https://orezone.com/contact/; stage-3 news check</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3536,7 +3556,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://orezone.com/contact/); General public email used; no named individual confirmed on the official contact page itself (a Kevin MacKenzie, VP Corporate Development and IR, appeared in older search results but was not present on the current official contact page, so not recorded).</t>
+          <t>CONFLICT: province=British Columbia|BC (https://orezone.com/contact/); General public email used; no named individual confirmed on the official contact page itself (a Kevin MacKenzie, VP Corporate Development and IR, appeared in older search results but was not present on the current official contact page, so not recorded).; IPO/listing change: also planning a secondary ASX listing targeted for mid-2025, per the same source.</t>
         </is>
       </c>
     </row>
@@ -3604,9 +3624,19 @@
           <t>www.santacruzsilver.com</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>capital raise: Bolivian subsidiary San Lucas S.A. raised a total of 140 million Bolivian Bolivianos across two promissory-note offerings (Feb and Aug 2025); capital raise: eliminated all Glencore debt by January 2026, ending with ~$80 million treasury; IPO/listing change: achieved a dual NASDAQ listing, January 2026; expansion/new project: finalized a preliminary mine plan and is pursuing production permitting at the Soracaya Project (Bolivia), October 2025</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://discoveryalert.com.au/strategic-capital-markets-silver-mining-2026/; https://discoveryalert.com.au/strategic-capital-markets-silver-mining-2026/; https://finance.yahoo.com/news/santacruz-silver-mining-tsxv-scz-211052346.html; </t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://santacruzsilver.com/contact/contact-information/</t>
+          <t>chat-listing-2026-08-05-03.png; https://santacruzsilver.com/contact/contact-information/; stage-3 news check</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3621,7 +3651,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (https://santacruzsilver.com/contact/contact-information/); The CEO's contact block on the official page lists a Mexico phone number and the general info@ email rather than a personal address/direct Vancouver line — recorded as published, not inferred further.</t>
+          <t>CONFLICT: province=British Columbia|BC (https://santacruzsilver.com/contact/contact-information/); The CEO's contact block on the official page lists a Mexico phone number and the general info@ email rather than a personal address/direct Vancouver line — recorded as published, not inferred further.; Correction/clarification: the company sold its Zacatecas, Mexico property in 2020 and current operations are centered on Bolivia — not related to the 'Vancouver' contact-page address confirmed in an earlier batch, just noting the company's operational focus has shifted geographically.</t>
         </is>
       </c>
     </row>
@@ -3749,9 +3779,19 @@
           <t>www.steppegold.com</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>expansion/new project: ATO Phase 2 expansion (Mongolia) fully funded via a $150 million financing deal with the Trade and Development Bank of Mongolia; revised feasibility study expected H2 2026; total gold production expected to rise to ~160,000 oz/year in 2026 as Phase 2 comes onstream</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://kalkine.ca/news/mining/why-is-steppe-gold-stock-rising-today-investors-focus-on-mongolia-growth-story-and-expansion-plans; ; </t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)</t>
+          <t>chat-listing-2026-08-05-03.png; steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain); stage-3 news check</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -3766,7 +3806,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)); Live fetch of the contact page did not surface an address/phone block (possibly rendered via JS); data sourced from a search-engine snippet referencing the company's own site. Recommend re-verifying directly if precision matters.</t>
+          <t>CONFLICT: province=British Columbia|BC (steppegold.com/contact/ (live fetch returned a page without the contact block; data sourced from a search-engine snippet of the same official domain)); Live fetch of the contact page did not surface an address/phone block (possibly rendered via JS); data sourced from a search-engine snippet referencing the company's own site. Recommend re-verifying directly if precision matters.; Note: company reported very low cash ($68,295) and working capital ($107,336) as of Dec 31, 2025 in the same source — a financial-health signal worth flagging even though it's not one of the fixed categories.</t>
         </is>
       </c>
     </row>
@@ -4139,9 +4179,19 @@
           <t>www.galianogold.com</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>acquisition/merger: consolidated ownership of the Asanko Gold Mine (Ghana) by acquiring Gold Fields' 45% interest, boosting Galiano's stake to 90% (2024, ongoing payments through 2026); expansion/new project: 2025-2026 development capital of $60-65 million primarily for Nkran Cut 3 waste stripping, secondary crushing circuit completion, and a tailings facility expansion</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://www.streetinsider.com/PRNewswire/GALIANO+GOLD+CONSOLIDATES+OWNERSHIP+OF+THE+ASANKO+GOLD+MINE+IN+TRANSFORMATIONAL+TRANSACTION/22553720.html; https://www.prnewswire.com/news-releases/galiano-gold-announces-2025-guidance-and-provides-mineral-reserve-and-mineral-resource-update-302362570.html</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-04.png; galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page)</t>
+          <t>chat-listing-2026-08-05-04.png; galianogold.com/contact/contact-us/default.aspx (live fetch 403'd; sourced from search-engine snippet of the company's own official page); stage-3 news check</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U141"/>
+  <dimension ref="A1:U205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10060,8 +10060,2888 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Design Maintenance Systems Inc</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>$4.26M</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CapitalEnergy Corporation</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Voyageur Oil And Gas Corporation</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Donnybrook Energy Inc</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Golden Predator Mining Corp</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Latin Explore Inc</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>$4.18M</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Anglo American Exploration (Canada) Ltd</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Gatos Silver Canada Corp</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Teck Namibia Ltd.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>NatBridge Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Golden Shield Resources Inc</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Lannister Mining Corp</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>South32 Canada Inc</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tiger Gold Corp</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Garson Gold Corp</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>$4.08M</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-01.png</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>VMS Ventures Inc</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-02.png</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Select Sands Corp</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-02.png</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Precision Sampling Inc</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Lac Gold (Rouyn) Inc</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Hunter Dickinson Acquisition Inc</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Gold Line Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Southwestern Resources Corp</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Triex Minerals Corporation</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>XXL Energy Corp</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>$3.29M</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Yellowhead Mining Inc</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>$3.27M</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Euro Manganese Inc</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>$3.18M</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Woodfibre LNG Limited Partnership</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>$3.15M</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Fox Exploration Limited</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>$3.15M</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Fuse Advisors Inc</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>$3.09M</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Atrum Coal Groundhog Inc</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Thesis Gold (Holdings) Inc</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>North Atlantic Titanium Corp</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Quebec Innovative Materials Corp</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-03.png</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Canamex Gold Corp</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ashmont Resources Corp</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>$3.06M</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>EMC Metals Corp</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>$3.03M</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ivanhoe Electric Inc</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>$2.9M</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BM&amp;H Oilfield Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>$2.86M</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Irwin Resources Inc</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>$2.86M</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Pacific Geophysical Ltd</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>$2.86M</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Northern Prince Lng Inc.</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>$2.86M</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>eCobalt Solutions Inc</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>$2.81M</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Rapier Gold Inc</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>$2.8M</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>International Northair Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>$2.8M</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Miata Metals Corp.</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>$2.8M</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Gemdale Gold Inc.</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>$2.8M</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Pediment Gold Corp</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>$2.8M</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Pulse Oil Corp</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>$2.68M</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-04.png</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Offsetters Clean Technology Inc</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>$2.58M</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Esrey Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>$2.57M</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Kaizen Discovery Inc</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>$2.57M</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Mason Resources Corp</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>$2.57M</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Geoscience BC Society</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>$2.52M</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Adroit Resources Inc</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>$2.45M</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Snipgold Corp</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Alpha Minerals Inc</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Aurea Mining Inc</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Anglo Coal Canada Inc</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Golden Predator Exploration Ltd</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>JKR Gold Resources Inc</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Coral Gold Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Bearing Lithium Corp</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Goldsource Mines Inc</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Continuum Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-05.png</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U141"/>
+  <autoFilter ref="A1:U205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10271,7 +10271,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; secondary sources (Sabre Gold/Victoria Gold transaction and receivership records, not fetched directly)</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -10281,7 +10281,12 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>REVIEW: sold by Sabre Gold to Victoria Gold Corp in September 2023 ($13.5 million). Victoria Gold itself was placed into receivership on August 14, 2024 (PwC appointed receiver) following the June 2024 Eagle Gold Mine heap leach failure in Yukon. Not an independent, going-concern Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -10344,6 +10349,11 @@
       <c r="C148" t="n">
         <v>4.08</v>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>700 W Pender Street, Suite 800</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10354,14 +10364,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Ed Yarrow</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Vice President Exploration, North America</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>eyarrow@angloamerican.ca</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>604-696-3500</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>www.angloamerican.com</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; search-engine snippets of yellowpages.ca/allbiz.ca listings (not the company's own site directly; two different Vancouver addresses appeared in results, this one matched the more complete contact record)</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -10371,7 +10411,12 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets of yellowpages.ca/allbiz.ca listings (not the company's own site directly; two different Vancouver addresses appeared in results, this one matched the more complete contact record)); Anglo American Exploration Canada is a wholly-owned exploration subsidiary of Anglo American plc — a legitimate, independently-contactable Vancouver office, not flagged REVIEW. Recommend re-verifying directly if precision matters, since the source was a directory listing rather than angloamerican.com itself.</t>
         </is>
       </c>
     </row>
@@ -10389,6 +10434,11 @@
       <c r="C149" t="n">
         <v>4.08</v>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>925 West Georgia Street, Suite 910</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10399,14 +10449,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>V6C 3L2</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>604-424-0984</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; secondary sources (First Majestic Silver acquisition press release, not fetched directly)</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -10416,7 +10476,12 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (First Majestic Silver acquisition press release, not fetched directly)); REVIEW: Gatos Silver Inc. was acquired by First Majestic Silver Corp (already a verified row in this workbook). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10516,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; not researched directly</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -10461,7 +10526,12 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a Teck Resources Limited subsidiary/exploration entity (already a verified row in this workbook, same Vancouver corporate structure). Not a separate independent office.</t>
         </is>
       </c>
     </row>
@@ -10479,6 +10549,11 @@
       <c r="C151" t="n">
         <v>4.08</v>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3292 Production Way, Suite 501</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10489,14 +10564,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>V5A 4R4</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>IR@NatBridgeResources.com</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>+1 (778) 372-9062</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>www.natbridgeresources.com</t>
+        </is>
+      </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; https://www.natbridgeresources.com/contact-us/</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -10506,7 +10601,12 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Burnaby (https://www.natbridgeresources.com/contact-us/); CONFLICT: province=British Columbia|BC (https://www.natbridgeresources.com/contact-us/); REVIEW: registered office is in Burnaby, not Vancouver proper — flagging the discrepancy from the D&amp;B listing's 'Vancouver' location rather than silently treating Burnaby as Vancouver. Metro Vancouver, so may still be relevant depending on how strictly 'Vancouver' is being scoped.</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10641,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; search-engine snippets (Bloomberg, Yahoo Finance, LinkedIn — no official company website located)</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -10551,7 +10651,12 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Confirmed active (CSE: GSRI), Vancouver-based, focused on the Marudi Mountain gold project in Guyana; led by Chairman Leo Hathaway and CEO Hilbert Shields. Could not locate an official company website distinct from financial-data aggregators; ILLEGIBLE: street_address, contact_email, contact_phone. Recommend a direct SEDAR+/CSE search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10691,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; no public record located</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -10596,7 +10701,12 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -10614,6 +10724,11 @@
       <c r="C154" t="n">
         <v>4.08</v>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1066 West Hastings Street, Suite 1780</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10624,14 +10739,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>www.south32.net</t>
+        </is>
+      </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; south32.net/contact-us (live fetch 403'd; address sourced from search-engine snippet of the company's own official site)</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -10641,7 +10766,12 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (south32.net/contact-us (live fetch 403'd; address sourced from search-engine snippet of the company's own official site)); This is South32's North America regional office; the parent (South32 Limited) is headquartered in Perth, Australia and dual-listed on ASX/LSE/JSE. No email/phone surfaced in the available snippet.</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10806,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; no public record located distinct from unrelated 'Tiger International Resources'</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -10686,7 +10816,12 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>REVIEW: search results only surfaced an unrelated company (Tiger International Resources, Philippines-focused). No official site or record located for 'Tiger Gold Corp' specifically. Recommend manual verification via BC Registry.</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10856,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; no public record located</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -10731,7 +10866,12 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -11199,6 +11339,11 @@
       <c r="C167" t="n">
         <v>3.18</v>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>700 West Pender Street, #709</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11209,14 +11354,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>V6C 1G8</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>info@mn25.ca</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>+1 (604) 681-1010</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>www.mn25.ca</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; https://www.mn25.ca/contact</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -11226,7 +11391,12 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.mn25.ca/contact)</t>
         </is>
       </c>
     </row>
@@ -11694,6 +11864,11 @@
       <c r="C178" t="n">
         <v>2.9</v>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>450 E Rio Salado Parkway, Suite 130</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11709,9 +11884,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>www.ivanhoeelectric.com</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; secondary sources (Kaizen Discovery acquisition press release, not fetched directly)</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -11721,7 +11901,12 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Tempe (secondary sources (Kaizen Discovery acquisition press release, not fetched directly)); CONFLICT: province=British Columbia|AZ (secondary sources (Kaizen Discovery acquisition press release, not fetched directly)); CONFLICT: country=Canada|United States (secondary sources (Kaizen Discovery acquisition press release, not fetched directly)); REVIEW: the company's own head office is in Tempe, Arizona, not Vancouver — directly conflicting with the D&amp;B listing. Recorded the verified Tempe address rather than inferring a Vancouver one.</t>
         </is>
       </c>
     </row>
@@ -12324,6 +12509,11 @@
       <c r="C192" t="n">
         <v>2.57</v>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>999 Canada Place, 606</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12334,14 +12524,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>V6C 3E1</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>www.kaizendiscovery.com</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; secondary sources (Ivanhoe Electric acquisition press release, not fetched directly)</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -12351,7 +12551,12 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (Ivanhoe Electric acquisition press release, not fetched directly)); REVIEW: fully acquired by Ivanhoe Electric Inc. (completed arrangement), now a wholly-owned subsidiary. Not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$244</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U205"/>
+  <dimension ref="A1:U244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13145,8 +13145,1763 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Rochester Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>$9.6M</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Barrick Gold Inc</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>$9.57M</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Avanti Kitsault Mine Ltd</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>$9.34M</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Western Magnesium Corporation</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>$9.34M</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>HighGold Mining Inc.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>$9.1M</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Pamicon Developments Ltd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>$8.5M</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Patagonia Gold Corp.</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>$8.22M</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1911 Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>$7.68M</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NEMI Northern Energy &amp; Mining Inc</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>$7.47M</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sunoil Ltd.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>$7.35M</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-07.png</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Orca Sand &amp; Gravel Limited Partnership</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>7</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Valhalla Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>7</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Rio Tinto Exploration Canada Inc</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>7</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Foran Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>7</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Trillion Energy International Inc</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>7</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Alderon Iron Ore Corp</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>$6.77M</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sierra Madre Gold and Silver Ltd</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>$6.47M</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Craigmont Mines (A Joint Venture)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>$6.12M</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Iberdrola Energy Projects Canada Corporation</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>$6.07M</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>WellteQ Digital Health Inc</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>$6.07M</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>International Enexco Limited</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>$6.07M</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Vicuña Corp</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>$5.84M</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>First Coal Corporation</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>$5.14M</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Chubu Electric Power Cordova Gas LTD</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>$4.8M</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-08.png</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Arlac Transamerican Oilfield Services Inc</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>$4.8M</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Bucking Horse Energy Inc</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>$4.8M</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Arizona Mining Inc</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>MGX Minerals Inc</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Kaminak Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Prodigy Gold Inc</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>BMC Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Terraco Gold Corp</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Woulfe Mining Corp</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Bellhaven Copper &amp; Gold Inc</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>GB Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Constantine Metal Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Waroona Energy Inc</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>$4.67M</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Nevada Copper Corp</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>$4.57M</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Xrapplied Technologies Inc</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>$4.44M</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-06.png</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U205"/>
+  <autoFilter ref="A1:U244"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -13176,7 +13176,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippets (PitchBook, not an official company site)</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
@@ -13186,7 +13186,12 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Confirmed active Vancouver-based gold mining company (CSE: RCT, ~3 employees) but no official website, address, or contact could be located. Recommend a direct CSE/SEDAR+ search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -13204,6 +13209,11 @@
       <c r="C207" t="n">
         <v>9.57</v>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>925 West Georgia Street, Suite 1600</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13214,14 +13224,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>V6C 3L2</t>
+        </is>
+      </c>
       <c r="H207" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>investor@barrick.com</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>www.barrick.com</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippets (yellowpages.ca listing for a separate Barrick Technology Centre at 323 Alexander St; barrick.com contact page for general IR email; not fetched directly)</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -13231,7 +13256,12 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (yellowpages.ca listing for a separate Barrick Technology Centre at 323 Alexander St; barrick.com contact page for general IR email; not fetched directly)); REVIEW: Barrick's main corporate headquarters is in Toronto (Barrick Mining Corporation, formerly Barrick Gold Corporation). This appears to be a Vancouver operating/technology office rather than a standalone entity's own headquarters. Recommend treating outreach here as reaching a regional office of the Toronto-headquartered parent, not an independent Vancouver company.</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13296,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; secondary sources (BC Environmental Assessment Office records, not fetched directly)</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
@@ -13276,7 +13306,12 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>REVIEW: the Kitsault molybdenum mine has been dormant since 1982 (low prices forced shutdown); a 2014 restart attempt stalled, and as of July 2026 the project is in a dispute-resolution process between the BC Environmental Assessment Office and West Moberly First Nations. No active operations or independent contact information found. Not a live prospect in its current state.</t>
         </is>
       </c>
     </row>
@@ -13309,9 +13344,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>www.westernmagnesium.com</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; westernmagnesium.com (live fetch succeeded but the contact page renders via JavaScript; no address/contact found in static HTML)</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -13321,7 +13361,12 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Confirmed active, Vancouver-headquartered (magnesium production technology). ILLEGIBLE: street_address, contact_email, contact_phone — not present in static HTML. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -13339,6 +13384,11 @@
       <c r="C210" t="n">
         <v>9.1</v>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>375 Water Street, Suite 405</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13349,14 +13399,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>V6B 5C6</t>
+        </is>
+      </c>
       <c r="H210" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Darwin Green</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>+1 604.629.1165; toll free +1 855.629.1165</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>www.highgoldmining.com</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; https://highgoldmining.com/contact/</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -13366,7 +13441,12 @@
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://highgoldmining.com/contact/); ILLEGIBLE: contact_email — official page displays it in reversed character order (a JS-deobfuscation trick), not decoded. Nicole Hoeller, VP Communications, is the named Investor/Corporate Development contact, same phone.</t>
         </is>
       </c>
     </row>
@@ -13384,6 +13464,11 @@
       <c r="C211" t="n">
         <v>8.5</v>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>675 West Hastings Street, Suite 611</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13401,7 +13486,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippets (yellowpages.ca/Kompass directory listings, not an official company site)</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
@@ -13411,7 +13496,12 @@
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (yellowpages.ca/Kompass directory listings, not an official company site)); No official company website located; no phone/email surfaced. Recommend a direct BC Registry search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -13444,9 +13534,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>www.patagoniagoldcorp.com</t>
+        </is>
+      </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippets (globenewswire filing index; live site fetch failed with a connection error, not a policy block)</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -13456,7 +13551,12 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Confirmed active (TSXV: PGDC), Vancouver-headquartered, Argentina-focused gold/silver explorer. ILLEGIBLE: street_address, contact_email, contact_phone — site fetch failed on this attempt. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -13474,6 +13574,11 @@
       <c r="C213" t="n">
         <v>7.68</v>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>400 Burrard Street, Suite 1050</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13484,14 +13589,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>V6C 3A6</t>
+        </is>
+      </c>
       <c r="H213" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Suzette Ramcharan</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>ir@1911gold.com</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>(647) 284-5315; general office (604) 900-5620</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>www.1911gold.com</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; https://www.1911gold.com/contact/</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -13501,7 +13636,12 @@
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.1911gold.com/contact/)</t>
         </is>
       </c>
     </row>
@@ -13519,6 +13659,11 @@
       <c r="C214" t="n">
         <v>7.47</v>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>700 West Georgia Street, 25th Floor</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13529,14 +13674,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>V7Y 1B3</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>(415) 339-8825</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippet (resourceconnector.ca directory listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
@@ -13546,7 +13701,12 @@
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (resourceconnector.ca directory listing, not the company's own site)); Operates as a merchant bank investing in small/micro-cap public companies (CSE-listed), not a mine operator itself. Phone number has a California area code despite the Vancouver address — recorded as found, not altered.</t>
         </is>
       </c>
     </row>
@@ -13564,6 +13724,11 @@
       <c r="C215" t="n">
         <v>7.35</v>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>999 West Hastings Street, Suite 550</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13581,7 +13746,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-07.png</t>
+          <t>chat-listing-2026-08-10-07.png; search-engine snippets (yellowpages.ca directory listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
@@ -13591,7 +13756,12 @@
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (yellowpages.ca directory listing, not the company's own site)); Formerly Blackstream Energy Corporation / Stealth Energy Inc.; a producing oil &amp; gas company with a Montana field office. No phone/email surfaced in available sources.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -13779,6 +13779,11 @@
       <c r="C216" t="n">
         <v>7</v>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>6505 Island Highway</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13789,6 +13794,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>V0N 2R0</t>
+        </is>
+      </c>
       <c r="H216" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -13796,7 +13806,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; secondary sources (Vulcan Materials, Natural Resources Canada, not fetched directly)</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -13806,7 +13816,12 @@
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Port McNeill (secondary sources (Vulcan Materials, Natural Resources Canada, not fetched directly)); CONFLICT: province=British Columbia|BC (secondary sources (Vulcan Materials, Natural Resources Canada, not fetched directly)); REVIEW: this is the operating quarry (Orca Quarry), majority-owned (88%) by Polaris Minerals Corporation / Vulcan Materials Company, with 'Namgis First Nation holding 12%. Polaris Materials Corporation is already flagged REVIEW in this workbook as a Vulcan Materials subsidiary. Not a separate Vancouver corporate office — the physical address is the Port McNeill quarry site, not Vancouver.</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13856,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; no public record located</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -13851,7 +13866,12 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -13884,9 +13904,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>www.riotinto.com</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; riotinto.com (general Canada operations pages checked; no Vancouver-specific exploration office contact located)</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
@@ -13896,7 +13921,12 @@
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>This is a Rio Tinto plc exploration subsidiary; Rio Tinto's Canadian operations are primarily centered on Iron Ore Company of Canada (Quebec/Labrador) and Rio Tinto Fer et Titane (Quebec) rather than a distinct Vancouver office. ILLEGIBLE: street_address, contact_email, contact_phone. Recommend direct verification if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13961,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; secondary sources (Eldorado Gold acquisition press releases, already documented for the related McIlvenna Bay Operating Ltd row, not re-fetched)</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -13941,7 +13971,12 @@
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>REVIEW: Foran Mining was acquired by Eldorado Gold Corporation, completed April 2026 (Eldorado Gold is already a verified row in this workbook). This is the same acquisition already flagged on the McIlvenna Bay Operating Ltd row (Foran's McIlvenna Bay project). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -13959,6 +13994,11 @@
       <c r="C220" t="n">
         <v>7</v>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>838 West Hastings St., Suite 700</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13969,14 +14009,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>V6C 0A6</t>
+        </is>
+      </c>
       <c r="H220" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>info@trillionenergy.com</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>1-778-819-1585</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>www.trillionenergy.com</t>
+        </is>
+      </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; https://trillionenergy.com/contact/</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
@@ -13986,7 +14046,12 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://trillionenergy.com/contact/); Oil exploration &amp; development company focused on southeast Turkiye, not a mining company per se, but energy-sector aligned with the D&amp;B directory's broader NAICS grouping.</t>
         </is>
       </c>
     </row>
@@ -14019,9 +14084,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>info@alderonironore.com</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>604-681-8030</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>alderonironore.com</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; search-engine snippet (SEC filing; the live domain failed to load with a TLS handshake error, not an expired-cert rejection but a broken/unreachable server — not connected to insecurely)</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
@@ -14031,7 +14111,12 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>REVIEW: Alderon Iron Ore filed for CCAA creditor protection in 2018 after financing for its Kami iron ore project in Labrador collapsed; the company's own domain appears to be down/unreachable now, consistent with a defunct entity. Recorded the old contact info found in a 2013 SEC filing with a clear caveat rather than treating it as current.</t>
         </is>
       </c>
     </row>
@@ -14049,6 +14134,11 @@
       <c r="C222" t="n">
         <v>6.47</v>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1455 Bellevue Ave.</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>West Vancouver</t>
@@ -14059,14 +14149,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>V7T 1C3</t>
+        </is>
+      </c>
       <c r="H222" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>investor@sierramadregoldandsilver.com</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>(604) 765-1604</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>www.sierramadregoldandsilver.com</t>
+        </is>
+      </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; search-engine snippet of the company's own official site (not fetched directly)</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -14076,7 +14186,12 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet of the company's own official site (not fetched directly)); Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -14109,9 +14224,29 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Peter Espig</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>info@nicolamining.com</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>(778) 385-1213</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>www.nicolamining.com</t>
+        </is>
+      </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; secondary sources (Nicola Mining Inc. press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
@@ -14121,7 +14256,12 @@
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>REVIEW: the historical Craigmont Mines (copper, near Merritt, BC) closed in 1982. The 'New Craigmont' property is now held and operated by Nicola Mining Inc., adjacent to Teck's Highland Valley Copper mine — recorded Nicola Mining's contact as the likely current operator, but this is a inference based on project-name continuity, not a confirmed identical legal entity. Recommend manual verification before treating as the same entity.</t>
         </is>
       </c>
     </row>
@@ -14154,9 +14294,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>www.iberdrola.com</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; not researched in depth — parent company confirmed (Iberdrola S.A., Spain), no Vancouver-specific office contact located</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
@@ -14166,7 +14311,12 @@
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>This is a Canadian project-development subsidiary of Iberdrola S.A. (Spanish multinational utility). ILLEGIBLE: street_address, contact_email, contact_phone. Not a mining company — energy/utility sector. Recommend direct verification if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14351,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; wellteq.co (checked; connection timed out — not fetched)</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
@@ -14211,7 +14361,12 @@
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>REVIEW: WellteQ Digital Health is a corporate wellness/digital health technology company (CSE-listed), not a mining company. Likely a NAICS misclassification, similar to BioHarvest Sciences and Sixth Wave Innovations flagged in earlier batches. Not a mining prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$263</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U244"/>
+  <dimension ref="A1:U263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15225,8 +15225,863 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Newstrike Capital Inc</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>$2.25M</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Basin Uranium Corp</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>$2.25M</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Altima Energy Inc</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>$2.18M</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ZL EOR Chemicals Ltd</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>$2.11M</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Canada Stewart Energy Group Limited</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Western LNG ULC</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Maxim Resources Inc</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Northiana Energy Solutions Inc</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Berkley Renewables Inc</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>$2.1M</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Gold'n Futures Mineral Corp</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Beta Energy Corp</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Colombian Mines Corporation</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Dynasty Metals &amp; Mining Inc.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Cypress West Development Corporation</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Marathon Gold NI Corp.</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1560706 B.C. Ltd</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-09.png</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Redhawk Resources Inc</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-10.png</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Maxy Gold Corp</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-10.png</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Balmoral Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>$2.33M</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-10.png</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U244"/>
+  <autoFilter ref="A1:U263"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -15301,7 +15301,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippet (barchart.com private-placement announcement, Dec 2024; not the company's own site)</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -15311,7 +15311,12 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Confirmed active as of Dec 2024 (CSE-listed, Vancouver-based). ILLEGIBLE: street_address, contact_email, contact_phone, website — no official site located distinct from financial-news aggregators. Recommend a direct CSE/SEDAR+ search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -15479,9 +15484,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>info@westernlng.com</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>www.westernlng.com</t>
+        </is>
+      </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; https://www.westernlng.com/contact</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
@@ -15491,7 +15506,12 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>REVIEW: the company's own official contact page lists its headquarters as 11 Greenway Plaza, Suite 545, Houston, Texas — not Vancouver. This is a BC unlimited-liability company (ULC), a common structure for a US parent to hold Canadian project assets (the Ksi Lisims LNG project). Recorded the verified Houston contact rather than inferring a Vancouver office; recommend treating this as NOT an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15771,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippet (Northern Miner company profile, not the company's own site)</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -15761,7 +15781,12 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Confirmed as a Vancouver-based Colombia-focused gold/copper explorer, but no official website, address, or contact was located in available sources. Recommend a direct search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -15794,9 +15819,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>info@dynastymining.com</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>604-687-7810</t>
+        </is>
+      </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippets (2016-dated press releases referencing a 'Special Committee' financial-advisor engagement and corporate update — a common precursor to a wind-down or going-private transaction)</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -15806,7 +15841,12 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>REVIEW: the most recent information located for this company dates to 2016, alongside language suggesting a possible going-private or restructuring process at that time. No confirmation of current active status found. Recommend manual verification before treating as a live prospect; contact info recorded is a decade old and may be stale.</t>
         </is>
       </c>
     </row>
@@ -15869,6 +15909,11 @@
       <c r="C259" t="n">
         <v>2.09</v>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>320 Granville Street, Suite 660</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -15879,6 +15924,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>V6C 1S9</t>
+        </is>
+      </c>
       <c r="H259" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -15886,7 +15936,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippet (tmgcorporation.com, not the company's own site)</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
@@ -15896,7 +15946,12 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (tmgcorporation.com, not the company's own site)); REVIEW: 'NI' likely denotes a specific subsidiary of Marathon Gold Corporation, whose main headquarters is in Toronto (Valentine Gold Project, Newfoundland). This Vancouver address is described as a 'West Coast Office,' not the company's primary headquarters. Recommend treating outreach here as reaching a satellite office of a Toronto-headquartered company.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -15351,7 +15351,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippets (Yahoo Finance, PitchBook, Newsfile — not the company's own site)</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
@@ -15361,7 +15361,12 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Confirmed active (TSXV: ARH), Vancouver-headquartered, oil &amp; gas exploration; renamed from Altima Resources Ltd in December 2024. ILLEGIBLE: street_address, contact_email, contact_phone, website. Recommend a direct search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15401,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippets (RocketReach/LinkedIn aggregator profiles only — not used for contact data per the hard rule against data brokers)</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -15406,7 +15411,12 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Confirmed active, Vancouver-headquartered polyacrylamide manufacturer for oil &amp; gas chemical-enhanced-oil-recovery applications, ~37 employees. No official company website located; the only contact-adjacent sources found were data-broker aggregators, which were not used per this project's hard rules.</t>
         </is>
       </c>
     </row>
@@ -15441,7 +15451,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -15451,7 +15461,12 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity despite repeated searches. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15561,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located distinct from an unrelated historical 'Maxim Power Corp'</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -15556,7 +15571,12 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website or clear record located for this specific entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15611,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -15601,7 +15621,12 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15634,9 +15659,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>berkleyrenewables.com</t>
+        </is>
+      </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; berkleyrenewables.com (site returned a 503 Service Unavailable from its own server — not a network/policy block)</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -15646,7 +15676,12 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Confirmed to exist (renewable energy/life sciences/oil &amp; gas venture firm, BC-based) but the official site is currently down. Recommend retrying later if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15716,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; search-engine snippets (Newsfile, BCSC reporting-issuer list — not the company's own site)</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -15691,7 +15726,12 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Confirmed active (CSE: FUTR), Vancouver-headquartered, exploring the Hercules-Elmhirst uranium/precious/base-metals project near Thunder Bay, Ontario. No official website or direct contact located.</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15766,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located distinct from an unrelated US-based 'Beta Energy'</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -15736,7 +15776,12 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website or clear record located for this specific Vancouver entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15926,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -15891,7 +15936,12 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15986,7 +16036,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; no public record located</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
@@ -15996,7 +16046,12 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>REVIEW: this is a generic BC numbered company; no official website, news coverage, or public registry detail located beyond the number itself. Numbered companies are frequently shell/holding entities without a public presence, consistent with 0908113 B.C. Ltd and 17411979 Canada Inc flagged in earlier batches.</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16086,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-10.png</t>
+          <t>chat-listing-2026-08-10-10.png; no public record located</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -16041,7 +16096,12 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16076,7 +16136,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-10.png</t>
+          <t>chat-listing-2026-08-10-10.png; no public record located</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -16086,7 +16146,12 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located for this entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16186,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-10.png</t>
+          <t>chat-listing-2026-08-10-10.png; search-engine snippet (Facebook page only, not an official company website)</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -16131,7 +16196,12 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>REVIEW: only a Facebook presence was located; no official website, news coverage, or financial-database listing found. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$312</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U263"/>
+  <dimension ref="A1:U312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16205,8 +16205,2213 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Global Cobalt Corporation</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Red Chris Development Company Ltd</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Kazax Minerals Inc</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Intrusion Precious Metals Corp</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sniper Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Riva Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Great Michael Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Norzan Enterprises Ltd</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Salmon River Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Uec Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Niocorp Developments Ltd</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>HD Mining International Ltd</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Intigold Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Kobex Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Pape Salter Teillet LLP</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-11.png</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Red Dragon Resources Corp</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Pembrook Copper Corp</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Charlotte Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Cariboo Copper Corp</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>$2.09M</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>East West Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Hecla Canada Ltd</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>International Bethlehem Mining Corp</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Palo Duro Energy Inc</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Viscount Mining Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>RB Energy Inc</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>International Barytex Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>K+S Legacy GP Inc</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Torrent Gold Inc</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Newcrest Red Chris Mining Limited</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Goldcorp Inc</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-12.png</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Great Bear Royalties Corp</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>StrategX Elements Corp</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Pegmatite One Lithium and Gold Corp</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Coronation Mines Ltd</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Lumina Metals Corp</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Rare Element Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Deakin Equipment Ltd.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Canadian De Hua International Trading Ltd</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Magnus International Resources Inc</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>B C &amp; Yukon Chamber of Mines</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CanXGold Mining Corp</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Norra Metals Corp</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Xemplar Energy Corp</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>B2Gold Logistics Corp</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>XCite Resources Inc</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Africo Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-13.png</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Valory Resources Inc.</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-14.png</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Contango Mining Canada, Inc</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-14.png</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Adonis Minerals Corp</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-14.png</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U263"/>
+  <autoFilter ref="A1:U312"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -919,6 +919,11 @@
       <c r="C6" t="n">
         <v>3061.24</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Park Place, Suite 3400, 666 Burrard Street</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -929,11 +934,31 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>V6C 2X8</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>info@b2gold.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+1 604 681 8371; toll free +1 800 316 8855</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>www.b2gold.com</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>expansion/new project: achieved commercial production at the Goose Mine in Nunavut, early October 2025 (B2Gold's first Canadian gold-producing mine); expansion/new project: approved a development decision on the Antelope underground deposit at the Otjikoto Mine (Namibia), announced September 15, 2025, to extend mine life</t>
@@ -946,7 +971,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-01.png; stage-3 news check</t>
+          <t>chat-listing-2026-08-05-01.png; stage-3 news check; b2gold.com/contact/contact-us/ (live fetch still returns an active Cloudflare bot-challenge, unchanged from earlier batches; address sourced from a search-engine snippet of the company's own official page instead)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -956,12 +981,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Contact page remains blocked by an active Cloudflare bot-challenge (per earlier batch); this news check used general search results, not a direct b2gold.com fetch.</t>
+          <t>Contact page remains blocked by an active Cloudflare bot-challenge (per earlier batch); this news check used general search results, not a direct b2gold.com fetch.; CONFLICT: province=British Columbia|BC (b2gold.com/contact/contact-us/ (live fetch still returns an active Cloudflare bot-challenge, unchanged from earlier batches; address sourced from a search-engine snippet of the company's own official page instead)); Resolves the long-standing gap on this row — B2Gold's contact page has been Cloudflare-blocked since the first contact-enrichment batch of this project. This address/phone/email come from a search snippet of the official b2gold.com page, not a direct fetch (still blocked). Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -16281,7 +16306,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; secondary sources (Newmont operations page, not fetched directly)</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
@@ -16291,7 +16316,12 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>REVIEW: Red Chris mine is now a Newmont Corporation operation (via the 2023 Newcrest acquisition; Newmont is already a verified row in this workbook). Not an independent Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16356,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; search-engine snippets (LinkedIn/Bloomberg, described as 'recently re-capitalised' but no date given)</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -16336,7 +16366,12 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>CONFLICT: company_name=Kazax Minerals Inc|KazaX Minerals Inc (search-engine snippets (LinkedIn/Bloomberg, described as 'recently re-capitalised' but no date given)); Vancouver-based, holds an interest in the Lomonosovskoye iron ore deposit in Kazakhstan. No official website or direct contact located; recency of the 're-capitalised' description is unclear.</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16631,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; secondary sources (mining.com, 2012-dated, not fetched directly)</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
@@ -16606,7 +16641,12 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>REVIEW: most recent located activity is a 2012 debt-settlement arrangement. No evidence of activity since. Recommend treating as likely dormant.</t>
         </is>
       </c>
     </row>
@@ -16669,6 +16709,11 @@
       <c r="C274" t="n">
         <v>2.04</v>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>7000 S. Yosemite Street, Suite 115</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -16679,14 +16724,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>80112</t>
+        </is>
+      </c>
       <c r="H274" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Jim Sims</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Corporate Communications Officer</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>jim.sims@niocorp.com</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>(720) 334-7066; general office 720-639-4647</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>www.niocorp.com</t>
+        </is>
+      </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; https://www.niocorp.com/contact-us/ (verified via search snippet of the official page)</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -16696,7 +16771,12 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>CONFLICT: company_name=Niocorp Developments Ltd|NioCorp Developments Ltd (https://www.niocorp.com/contact-us/ (verified via search snippet of the official page)); CONFLICT: city=Vancouver|Centennial (https://www.niocorp.com/contact-us/ (verified via search snippet of the official page)); CONFLICT: province=British Columbia|CO (https://www.niocorp.com/contact-us/ (verified via search snippet of the official page)); CONFLICT: country=Canada|United States (https://www.niocorp.com/contact-us/ (verified via search snippet of the official page)); REVIEW: the company's own official contact page lists its head office in Centennial, Colorado — not Vancouver. Recorded the verified Colorado address rather than inferring a Vancouver one.</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16856,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; search-engine snippets (TSXV listing only, current status unclear)</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
@@ -16786,7 +16866,12 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>TSX Venture-listed (IGD.V) but no official website or current-status confirmation located. Recommend a direct SEDAR+/TSXV search if this entity matters.</t>
         </is>
       </c>
     </row>
@@ -16821,7 +16906,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; secondary sources (PitchBook, not fetched directly)</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -16831,7 +16916,12 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired September 30, 2009 by GreenFirst Forest Products. Not an independent prospect for over 15 years.</t>
         </is>
       </c>
     </row>
@@ -16849,6 +16939,11 @@
       <c r="C278" t="n">
         <v>2.04</v>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>595 Burrard Street, P.O. Box 48146, Bentall</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -16859,14 +16954,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>V7Z 1N8</t>
+        </is>
+      </c>
       <c r="H278" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>604 681 3002</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>pstlaw.ca</t>
+        </is>
+      </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; https://pstlaw.ca/contact/</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -16876,7 +16986,12 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://pstlaw.ca/contact/); This is an Indigenous-rights law firm (also has a Toronto office), not a mining company. Likely a NAICS misclassification, but a real, confirmed-active Vancouver organization.</t>
         </is>
       </c>
     </row>
@@ -17119,6 +17234,11 @@
       <c r="C284" t="n">
         <v>2.04</v>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>800 West Pender Street, Suite 970</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -17129,14 +17249,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>V6C 2V6</t>
+        </is>
+      </c>
       <c r="H284" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>+1 604.682.6201</t>
+        </is>
+      </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; search-engine snippet (D&amp;B directory listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -17146,7 +17276,12 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (D&amp;B directory listing, not the company's own site)); This is a Canadian subsidiary office of Hecla Mining Company (headquartered in Coeur d'Alene, Idaho, USA) — a real, independently-contactable Vancouver office, not flagged REVIEW. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -17479,6 +17614,11 @@
       <c r="C292" t="n">
         <v>2.04</v>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>1066 West Hastings St, Suite 800</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -17489,6 +17629,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H292" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -17496,7 +17641,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; search-engine snippet (D&amp;B directory listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -17506,7 +17651,12 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (D&amp;B directory listing, not the company's own site)); REVIEW: same Red Chris/Newcrest/Newmont chain as Red Chris Development Company Ltd above. Newmont Corporation is already a verified row in this workbook. Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17691,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; not researched separately</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
@@ -17551,7 +17701,12 @@
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>REVIEW: distinct D&amp;B entry from 'Goldcorp Canada Ltd' (already flagged REVIEW in an earlier batch) but almost certainly part of the same corporate family, folded into Newmont Corporation after the 2019 merger (already a verified row in this workbook). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17741,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; secondary sources (Royal Gold acquisition press release, not fetched directly)</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -17596,7 +17751,12 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Royal Gold Corporation (per 'Royal Gold Completes Acquisition of Great Bear Royalties' press release). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -17809,9 +17969,19 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>(720) 278-2460</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>www.rareelementresources.com</t>
+        </is>
+      </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; search-engine snippets (SEC filings, company FAQ page, not fetched directly)</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -17821,7 +17991,12 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>CONFLICT: city=Vancouver|Littleton (search-engine snippets (SEC filings, company FAQ page, not fetched directly)); CONFLICT: province=British Columbia|CO (search-engine snippets (SEC filings, company FAQ page, not fetched directly)); CONFLICT: country=Canada|United States (search-engine snippets (SEC filings, company FAQ page, not fetched directly)); REVIEW: headquartered in Colorado, not Vancouver; now a subsidiary of General Atomic Technologies Corporation, developing the Bear Lodge rare-earth project in Wyoming. Recorded the verified Colorado information rather than a Vancouver address.</t>
         </is>
       </c>
     </row>
@@ -17839,6 +18014,11 @@
       <c r="C300" t="n">
         <v>2.04</v>
       </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1361 Powell Street</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -17849,14 +18029,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>V5L 1G8</t>
+        </is>
+      </c>
       <c r="H300" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>(604) 253-2685</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>deakin.com</t>
+        </is>
+      </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; search-engine snippets (Yelp listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -17866,7 +18061,12 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (Yelp listing, not the company's own site)); Confirmed active — a survey/outdoor/mining-supply equipment retailer, locally owned and operated in Vancouver. Not a mining company itself but a real, active local business serving the sector.</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18371,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; not researched separately</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
@@ -18181,7 +18381,12 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>REVIEW: almost certainly a logistics subsidiary of B2Gold Corp (already a row in this workbook, Park Place, Suite 3400 - 666 Burrard Street, Vancouver BC V6C 2X8). Same corporate office presumed. Not an independent prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -16451,7 +16451,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; no public record located</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -16461,7 +16461,12 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16501,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; not researched in depth</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -16506,7 +16511,12 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch.</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16551,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; no public record located</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -16551,7 +16561,12 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16601,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; no public record located</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -16596,7 +16611,12 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16701,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; no public record located distinct from unrelated 'UEC' (Uranium Energy Corp, already a row) ticker collisions</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -16691,7 +16711,12 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website distinct from Uranium Energy Corp (already a row in this workbook, unrelated entity) could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -16811,7 +16836,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; secondary sources (Wikipedia — HD Mining International, Murray River coal project)</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
@@ -16821,7 +16846,12 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>REVIEW: known for a controversial temporary foreign worker permit dispute around 2012-2013 involving its Murray River coal project; no confirmation of current active status found. Recommend manual verification before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17056,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -17036,7 +17066,12 @@
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17069,9 +17104,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>pembrookmining.com</t>
+        </is>
+      </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; search-engine snippet (pembrookmining.com is an old-style site; no confirmation of recent activity)</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -17081,7 +17121,12 @@
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Peru-focused copper/gold/silver exploration company, Vancouver-headquartered per company description, but the official site appears dated and no recent (post-2020) activity could be confirmed. Recommend manual verification of current status before treating as active.</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17161,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -17126,7 +17171,12 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17211,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; opengovca.com Vancouver business licence listing (not the company's own site)</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -17171,7 +17221,12 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>REVIEW: business licence on file was issued December 2011 and expired December 31, 2012. No evidence of activity since. Recommend treating as dormant.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17261,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; search-engine snippets (Simply Wall St, MarketScreener)</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -17216,7 +17271,12 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Confirmed active — an oil and gas company (Canada/New Zealand/Romania), recently renamed to 'East West Minerals Ltd' as of October 2025 (previously a different name, per naming-change reference). No official website, address, or contact located.</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17376,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -17326,7 +17386,12 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17426,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; directory listing only, no official site located</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -17371,7 +17436,12 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>REVIEW: appears in a general energy-company directory listing but no official website, address, or contact could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17406,7 +17476,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; not researched separately</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -17416,7 +17486,12 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch. Note: distinct from 'Viscount Mining Corp' (a different, US-focused silver company) — possible naming confusion to watch for.</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17526,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located distinct from an unrelated historical Quebec lithium company of the same name (RB Energy / Canada Lithium, ceased operations 2015)</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -17461,7 +17536,12 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>REVIEW: an unrelated historical company named RB Energy Inc (Quebec lithium, entered CCAA in 2014-2015) surfaced in search results, but no confirmation this is the same entity as the Vancouver company in this listing. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17576,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -17506,7 +17586,12 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17626,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; not researched separately</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -17551,7 +17636,12 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>REVIEW: almost certainly a related general-partner entity to K+S Canada Holdings Ltd (already a row in this workbook, part of K+S Potash Canada's Legacy project). Same corporate family, likely same registered office; not independently verified.</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17676,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png</t>
+          <t>chat-listing-2026-08-10-12.png; no public record located</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -17596,7 +17686,12 @@
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -16501,7 +16501,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png; not researched in depth</t>
+          <t>chat-listing-2026-08-10-11.png; not researched in depth; no public record located</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch.</t>
+          <t>Not yet researched due to time constraints on this batch.; REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-12.png; not researched separately</t>
+          <t>chat-listing-2026-08-10-12.png; not researched separately; no public record located distinct from unrelated 'Viscount Mining Corp' (US-focused silver company)</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch. Note: distinct from 'Viscount Mining Corp' (a different, US-focused silver company) — possible naming confusion to watch for.</t>
+          <t>Not yet researched due to time constraints on this batch. Note: distinct from 'Viscount Mining Corp' (a different, US-focused silver company) — possible naming confusion to watch for.; REVIEW: no official website or clear record located for this specific North Vancouver entity, distinct from the similarly-named US-focused Viscount Mining Corp. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -17869,6 +17869,11 @@
       <c r="C295" t="n">
         <v>2.04</v>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>409 Granville Street, Unit 1500</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -17879,14 +17884,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>V6C 1T2</t>
+        </is>
+      </c>
       <c r="H295" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>info@strategxcorp.com</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>778-231-2767</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>www.strategxcorp.com</t>
+        </is>
+      </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; https://www.strategxcorp.com/contact</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -17896,7 +17921,12 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://www.strategxcorp.com/contact)</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17961,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; not researched in depth</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -17941,7 +17971,12 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints.</t>
         </is>
       </c>
     </row>
@@ -17976,7 +18011,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -17986,7 +18021,12 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18019,9 +18059,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>www.luminametals.com</t>
+        </is>
+      </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; luminametals.com (site loads but contact page returned an error on this attempt; not a policy block)</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -18031,7 +18076,12 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Confirmed very active — a Ross Beaty-led company advancing multiple copper-silver projects in Poland; completed a C$406.2 million Toronto IPO. Not to be confused with the separate, related company Lumina Gold Corp (Vancouver, Ecuador-focused; contact Scott Hicks, shicks@luminagold.com, +1 604 646 1890, per search results — recorded for reference but not verified directly). ILLEGIBLE: street_address, contact_email, contact_phone for Lumina Metals specifically. Recommend re-verifying directly if precision matters.</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18246,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -18206,7 +18256,12 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Name suggests an import/export trading company rather than a mining operator; possible NAICS misclassification. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18296,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -18251,7 +18306,12 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18269,6 +18329,11 @@
       <c r="C303" t="n">
         <v>2.04</v>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>889 West Pender Street, Suite 800</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -18279,14 +18344,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>V6C 3B2</t>
+        </is>
+      </c>
       <c r="H303" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>604-689-5271</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>amebc.ca</t>
+        </is>
+      </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; https://amebc.ca/contact/</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -18296,7 +18376,12 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (https://amebc.ca/contact/); This organization renamed itself the Association for Mineral Exploration British Columbia (AME BC) in 2005 — this is the current name and site, still Vancouver-based. Verified this is distinct from the similarly-named 'Yukon Chamber of Mines' (Whitehorse, YT), which some search results conflated it with. Not a mining company itself but the region's lead mineral-exploration industry association — a real, active, contactable organization. ILLEGIBLE: contact_email — obfuscated on the official page.</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18416,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; secondary sources (PwC insolvency records, Grand Forks Gazette receivership notice, not fetched directly)</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -18341,7 +18426,12 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>REVIEW: a receiver (PwC) was appointed November 20, 2023; the receiver subsequently agreed to sell all company assets to Phoenix Copper Company Inc. (formerly known as Golden Dawn Minerals Inc. / Kettle River Resources Ltd.). Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -18376,7 +18466,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -18386,7 +18476,12 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18516,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -18431,7 +18526,12 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18616,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; no public record located distinct from unrelated 'Xcite Energy'</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -18526,7 +18626,12 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website or clear record located for this specific entity. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18666,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-13.png</t>
+          <t>chat-listing-2026-08-10-13.png; secondary sources (Wikipedia, not fetched directly)</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -18571,7 +18676,12 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>REVIEW: majority ownership acquired by Camrose Resources Limited in 2016. Not an independent Vancouver prospect for close to a decade.</t>
         </is>
       </c>
     </row>
@@ -18589,6 +18699,11 @@
       <c r="C310" t="n">
         <v>2.04</v>
       </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1111 West Hastings St., Suite 905</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -18606,7 +18721,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-14.png</t>
+          <t>chat-listing-2026-08-10-14.png; search-engine snippet (D&amp;B directory listing, not the company's own site)</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -18616,7 +18731,12 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (D&amp;B directory listing, not the company's own site)); Coal mining industry per available description. No official website, email, or phone located.</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18771,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-14.png</t>
+          <t>chat-listing-2026-08-10-14.png; no public record located distinct from unrelated 'Contango ORE' (Alaska)</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -18661,7 +18781,12 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website or clear record located for this specific Canadian entity, distinct from the similarly-named US company Contango ORE. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18821,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-14.png</t>
+          <t>chat-listing-2026-08-10-14.png; no public record located</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -18706,7 +18831,12 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -14409,6 +14409,11 @@
       <c r="C226" t="n">
         <v>6.07</v>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>700 West Georgia Street, Suite 1450</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -14419,6 +14424,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>V7Y 1K8</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -14426,7 +14436,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; secondary sources (Denison Mines information circular, not fetched directly)</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
@@ -14436,7 +14446,12 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (Denison Mines information circular, not fetched directly)); REVIEW: acquired by Denison Mines, completed June 6, 2014. Not an independent Vancouver prospect for over a decade.</t>
         </is>
       </c>
     </row>
@@ -14454,6 +14469,11 @@
       <c r="C227" t="n">
         <v>5.84</v>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1133 Melville Street, Suite 3030</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -14464,14 +14484,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>V6E 4E5</t>
+        </is>
+      </c>
       <c r="H227" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Ron Hochstein</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>604 636 7090</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>vicuna.com</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; search-engine snippets (lundinmining.com press release, vicuna.com/en/contacto/ referenced but not fetched directly)</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
@@ -14481,7 +14526,12 @@
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (lundinmining.com press release, vicuna.com/en/contacto/ referenced but not fetched directly)); Confirmed very active — a newly-formed 50/50 joint venture between Lundin Mining and BHP holding the Filo del Sol and Josemaria copper projects (Vicuña district, Argentina/Chile). Stephen Williams (Lundin Mining's VP Investor Relations, already recorded on that row) is also listed as an IR contact here, +1 604 806 3074, confirming shared corporate infrastructure. Not flagged REVIEW — this is a real, well-funded, independently significant entity.</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14566,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; no public record located</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -14526,7 +14576,12 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14661,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -14616,7 +14671,12 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch.</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14711,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -14661,7 +14721,12 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch.</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14761,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; secondary sources (PitchBook, not fetched directly)</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -14706,7 +14771,12 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by South32 (already a row in this workbook), completed August 10, 2018. Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -14739,9 +14809,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>www.mgxminerals.com</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; mgxminerals.com (site displays 'Site Under Construction'; description sourced from search snippets)</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -14751,7 +14826,12 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Confirmed active — led by CEO/Founder Jared Lazerson, advancing the Fran Gold Project near Fort St. James, BC (~$18-20 million invested, 104+ drill holes). Official website is currently non-functional ('Site Under Construction'). ILLEGIBLE: street_address, contact_email, contact_phone. Recommend re-verifying if the site comes back online.</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14866,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; secondary sources (Northern Miner, not fetched directly)</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
@@ -14796,7 +14876,12 @@
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Goldcorp via a $520 million all-share bid (2016) for the Coffee gold project. Goldcorp itself later merged into Newmont Corporation (already a verified row in this workbook). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -14831,7 +14916,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -14841,7 +14926,12 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch. Note: there is an unrelated 'Prodigy Gold NL' in Australia — watch for naming confusion.</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14966,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; not yet researched in depth</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -14886,7 +14976,12 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch.</t>
         </is>
       </c>
     </row>
@@ -14921,7 +15016,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; search-engine snippet (mentioned as CSE: TEN in a general list, not the company's own site)</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
@@ -14931,7 +15026,12 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Confirmed to exist (CSE: TEN) but no address, email, or phone located in available sources.</t>
         </is>
       </c>
     </row>
@@ -14966,7 +15066,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; no public record located</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -14976,7 +15076,12 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15116,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; secondary sources (GoldMining Inc. acquisition press releases, not fetched directly)</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -15021,7 +15126,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by GoldMining Inc., agreement announced April 2017, for its Colombian gold-copper project. Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -15056,7 +15166,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; no public record located</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -15066,7 +15176,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15084,6 +15199,11 @@
       <c r="C241" t="n">
         <v>4.67</v>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>800 West Pender Street, Suite 320</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -15094,6 +15214,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>V6C 2V6</t>
+        </is>
+      </c>
       <c r="H241" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -15101,7 +15226,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; search-engine snippets (yellowpages.ca, not the company's own site)</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -15111,7 +15236,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (yellowpages.ca, not the company's own site)); REVIEW: acquired by American Pacific Mining Corp via a completed plan of arrangement, November 2022. Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15276,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; no public record located</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
@@ -15156,7 +15286,12 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15326,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; secondary sources (GlobalData, not fetched directly)</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
@@ -15201,7 +15336,12 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired, completed September 24, 2025 (Pumpkin Hollow copper project near Yerington, Nevada). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -15236,7 +15376,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
@@ -15246,7 +15386,12 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Not yet researched due to time constraints on this batch.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -14661,7 +14661,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth; no public record located</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch.</t>
+          <t>Not yet researched due to time constraints on this batch.; REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth; no public record located</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch.</t>
+          <t>Not yet researched due to time constraints on this batch.; REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth; search-engine snippets (Cambridge House, energy-oil-gas.com — dated, current status unclear)</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch. Note: there is an unrelated 'Prodigy Gold NL' in Australia — watch for naming confusion.</t>
+          <t>Not yet researched due to time constraints on this batch. Note: there is an unrelated 'Prodigy Gold NL' in Australia — watch for naming confusion.; Formed from a merger of Kodiak Exploration and Golden Goose Resources, led by President/CEO Brian Maher, per older sources. No confirmation of current active status or a locatable official website. Recommend manual verification before treating as active.</t>
         </is>
       </c>
     </row>
@@ -14949,6 +14949,11 @@
       <c r="C236" t="n">
         <v>4.67</v>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>789 West Pender Street, 750</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -14959,14 +14964,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>V6C 1H2</t>
+        </is>
+      </c>
       <c r="H236" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>investors@bmcminerals.com</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>+1 778 379 9262</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>www.bmcminerals.com</t>
+        </is>
+      </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png; not yet researched in depth</t>
+          <t>chat-listing-2026-08-10-06.png; not yet researched in depth; https://bmcminerals.com/contact-us/</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -14976,12 +15001,12 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch.</t>
+          <t>Not yet researched due to time constraints on this batch.; CONFLICT: province=British Columbia|BC (https://bmcminerals.com/contact-us/); Confirmed very active — recently completed an AU$100 million ASX IPO (July 2026), advancing the Kudz Ze Kayah project in Yukon. Registered office is separately listed at 2900-550 Burrard Street; recorded the principal place of business instead.</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15401,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-06.png; not researched in depth</t>
+          <t>chat-listing-2026-08-10-06.png; not researched in depth; search-engine snippets (Bloomberg, CSE listing page)</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
@@ -15391,7 +15416,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>Not yet researched due to time constraints on this batch.</t>
+          <t>Not yet researched due to time constraints on this batch.; REVIEW: this is an AR/VR, omnichannel-communications, and supply-chain software company (CSE: XRA), not a mining company. Likely a NAICS misclassification. Not a mining prospect.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10144,6 +10144,11 @@
       <c r="C143" t="n">
         <v>4.2</v>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>837 West Hastings Street, Suite 700</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10154,6 +10159,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>V6C 3N6</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -10161,7 +10171,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; search-engine snippets (scrapmonster.com, not the company's own site)</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -10171,7 +10181,12 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippets (scrapmonster.com, not the company's own site)); A privately-held North American midstream/upstream natural gas company, active since 2005. No email/phone located.</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11351,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; secondary sources (Taseko Mines acquisition press release, not fetched directly)</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -11346,7 +11361,12 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Taseko Mines Limited in 2019 for the Yellowhead Copper Project near Kamloops. Taseko Mines is already a verified row in this workbook (recently renamed Trekor Metals Limited). Not an independent prospect.</t>
         </is>
       </c>
     </row>
@@ -11439,6 +11459,11 @@
       <c r="C168" t="n">
         <v>3.15</v>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PO Box 17533, The Ritz PO</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11449,14 +11474,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>V6E 0B2</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>woodfibrelng.ca</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; search-engine snippet (mailing address only; the live contact page renders via JavaScript, no static content found)</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -11466,7 +11501,12 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (mailing address only; the live contact page renders via JavaScript, no static content found)); Confirmed active — a major LNG export project near Squamish, BC, operated by the privately-held Woodfibre Management Ltd. This is a mailing address (PO Box), not a street address; ILLEGIBLE: contact_email, contact_phone. Recommend re-verifying directly if a street address/phone matters.</t>
         </is>
       </c>
     </row>
@@ -12129,6 +12169,11 @@
       <c r="C183" t="n">
         <v>2.81</v>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>999 West Hastings Street, 1810</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12139,6 +12184,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>V6C 2W2</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -12146,7 +12196,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; search-engine snippet (D&amp;B directory listing for the address; ecobalt.com itself was checked directly and found squatted)</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
@@ -12156,7 +12206,12 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-engine snippet (D&amp;B directory listing for the address; ecobalt.com itself was checked directly and found squatted)); REVIEW / DOMAIN SQUATTED: ecobalt.com now serves unrelated online-casino/sweepstakes affiliate content, not the company's own material — the same domain-takeover pattern already flagged for Cache Exploration Inc earlier in this project. Did not use this domain for anything. The company's Idaho Cobalt Project funding is understood to have collapsed around 2019; likely defunct. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -12599,6 +12654,11 @@
       <c r="C193" t="n">
         <v>2.57</v>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1066 West Hastings Street</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12609,6 +12669,11 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>V6E 3X1</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -12616,7 +12681,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; secondary sources (name-change filings, not fetched directly)</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
@@ -12626,7 +12691,12 @@
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (secondary sources (name-change filings, not fetched directly)); REVIEW: the entity behind this name changed to 'Transoceanic Investments Inc.' effective April 13, 2026 — a very recent rename. Earlier corporate history includes a 2017 Entree Resources merger/name change and a 2018 Hudbay Minerals acquisition bid. Recommend treating this specific name as no longer current; verify Transoceanic Investments Inc. separately if this entity matters.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10099,6 +10099,11 @@
       <c r="C142" t="n">
         <v>4.26</v>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>201-38 Fell Avenue</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>North Vancouver</t>
@@ -10109,14 +10114,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>V7P 3S2</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>info@desmaint.com</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>604-984-3674</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>www.desmaint.com</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; search-indexed content (desmaint.com contact page; yellowpages.ca) — direct fetch of desmaint.com blocked in this session</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -10126,7 +10151,12 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-indexed content (desmaint.com contact page; yellowpages.ca) — direct fetch of desmaint.com blocked in this session); REVIEW: likely misclassified — condition-monitoring/predictive-maintenance software and instrumentation vendor to the mining industry, not itself a mining/materials producer. No named individual contact published.</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10251,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; no public record located</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -10231,7 +10261,12 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>REVIEW: no official website, BC registry entry, SEDAR+ filing, or exchange listing found under this exact name. Search surfaced only unrelated similarly-named entities (Voyager Oil &amp; Gas Inc, Voyageur Pharmaceuticals Ltd). Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10301,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; secondary sources (boereport.com, hartenergy.com, Siskinds LLP class-action notice)</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -10276,7 +10311,12 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>REVIEW: completed a name change/consolidation to Stonehaven Exploration Ltd effective Oct 29, 2014; Stonehaven later rebranded again to Arrow Exploration Corp. Also subject to a securities class action. No current office or contact exists under the original name; not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -10344,6 +10384,11 @@
       <c r="C147" t="n">
         <v>4.18</v>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1920-1188 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10354,14 +10399,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>V6E 4A2</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Mike Basha</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Interim CEO</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>epatterson@latin-explore.com</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>778-683-4324</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>latin-explore.com</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-01.png</t>
+          <t>chat-listing-2026-08-10-01.png; juniorminingnetwork.com, newsfilecorp.com press releases; latin-explore.com</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -10371,7 +10446,12 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (juniorminingnetwork.com, newsfilecorp.com press releases; latin-explore.com); Active, independent, TSXV-listed (LXE), incorporated 2025 as a spin-out of Latin Metals Inc, exploring the Para Cu-Mo project in Peru. Contact email/phone are for the named VP Investor Relations (Elyssia Patterson), the most current published contact found.</t>
         </is>
       </c>
     </row>
@@ -10946,7 +11026,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-02.png</t>
+          <t>chat-listing-2026-08-10-02.png; newswire.ca, karoraresources.com, vmsventures.com press releases</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -10956,7 +11036,12 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Royal Nickel Corporation via plan of arrangement, completed April 27, 2016 (30% JV interest in the Hudbay-operated Reed copper mine, Manitoba). Royal Nickel Corp is now known as Karora Resources Inc. Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -10974,6 +11059,11 @@
       <c r="C158" t="n">
         <v>3.5</v>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>310-850 West Hastings Street</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -10984,14 +11074,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>V6C 1E1</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>info@selectsandscorp.com</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>+1 844 806-7313</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>www.selectsands.com</t>
+        </is>
+      </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-02.png</t>
+          <t>chat-listing-2026-08-10-02.png; selectsands.com/contact, thenewswire.com, rockproducts.com</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -11001,7 +11111,12 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (selectsands.com/contact, thenewswire.com, rockproducts.com); REVIEW: functionally non-operating despite published contact info still live. BC Securities Commission cease-trade order effective May 8, 2024 for failure to file audited financials; primary lender foreclosed and auctioned all physical assets Oct 2, 2024. Not confirmed formally bankrupt but not a healthy live prospect.</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11151,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; no public record located</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -11046,7 +11161,12 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>REVIEW: no Vancouver/BC company found under this exact name; search surfaced only unrelated same/similar-name entities. Recommend manual verification via BC Registry before treating as a live prospect.</t>
         </is>
       </c>
     </row>
@@ -11079,9 +11199,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>lacgold.com</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; mining.com, yorbeauresources.com, lacgold.com, mining.com.au</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -11091,7 +11216,12 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>REVIEW: not an independent Vancouver-area company — a project-acquisition vehicle of ASX-listed Lac Gold Pty Ltd (Perth, Australia) holding the Rouyn gold property near Rouyn-Noranda, Quebec (purchased from Yorbeau Resources, sale closed Dec 2024). No Vancouver office or independent contact found; likely a geography misclassification for this candidate list.</t>
         </is>
       </c>
     </row>
@@ -11109,6 +11239,11 @@
       <c r="C161" t="n">
         <v>3.5</v>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1040 West Georgia Street, 14th Floor</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11119,14 +11254,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>V6E 4H1</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>info@hdimining.com</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>604-684-6365</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>www.hdimining.com</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; hdimining.com (search-indexed), dnb.com business directory</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -11136,7 +11291,12 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (hdimining.com (search-indexed), dnb.com business directory); REVIEW: this is a specific acquisition-vehicle entity within the private Hunter Dickinson Inc (HDI) group, not a standalone operating prospect. HDI privately manages several publicly traded mining companies (Northern Dynasty Minerals, Amarc Resources, Taseko Mines). No contact specific to the 'Acquisition Inc' entity found; address/phone/email are HDI's general Vancouver head-office contact, used as best-available proxy — not independently verified for this specific subsidiary.</t>
         </is>
       </c>
     </row>
@@ -11154,6 +11314,11 @@
       <c r="C162" t="n">
         <v>3.5</v>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2200-885 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11164,14 +11329,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>V6G 2Z6</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Adam Cegielski</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>604-609-6138</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>www.goldlineresources.com</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; investing.com company profile, dnb.com, juniorminingnetwork.com</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -11181,7 +11371,12 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (investing.com company profile, dnb.com, juniorminingnetwork.com); Active, TSXV-listed (GLDL)/OTCQB (TLLZF), Vancouver HQ; properties (Gold Line, Klippen Gold, Oijarvi Gold, Solvik Gold projects) are in Sweden/Finland, not local to BC. No general/IR email confirmed via an official source; leaving contact_email blank rather than guess. One source lists it as a possible subsidiary of Goldsky Resources Corp, not independently verified.</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11411,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; proactiveinvestors.co.uk, theglobeandmail.com</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -11226,7 +11421,12 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Hochschild Mining plc via cash merger (~US$17.5-22.5M), closing reported around March-May 2009. Company delisted; not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11461,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; canterraminerals.com press release</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -11271,7 +11471,12 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>REVIEW: became a wholly-owned subsidiary of Canterra Minerals Corporation (formerly Diamondex Resources Ltd) via Plan of Arrangement completed Dec 11, 2009; delisted from TSX-V. Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -11289,6 +11494,11 @@
       <c r="C165" t="n">
         <v>3.29</v>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>700-595 Howe Street</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11299,14 +11509,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>V6C 2T5</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>xxlenergy.com</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; opencorpdata.com (registered address, cross-referenced against SEDAR+); xxlenergy.com not directly fetched (network egress blocked)</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -11316,7 +11536,12 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (opencorpdata.com (registered address, cross-referenced against SEDAR+); xxlenergy.com not directly fetched (network egress blocked)); REVIEW: likely misclassified for this workbook's sector filter — an oil and gas exploration/production company (Wyoming/Colorado assets), not mining/materials; TSX-V ticker XL, still active/independent, not defunct. No named contact, email, or phone located.</t>
         </is>
       </c>
     </row>
@@ -11524,6 +11749,11 @@
       <c r="C169" t="n">
         <v>3.15</v>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1500-409 Granville Street</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11534,14 +11764,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>V6C 1T2</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>info@foxexploration.ca</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>604-315-1033</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>www.foxexploration.ca</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; cylex-canada.ca, foxexploration.ca (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -11551,7 +11801,12 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (cylex-canada.ca, foxexploration.ca (search-indexed, direct fetch blocked)); REVIEW: possible misclassification — this 'Fox Exploration' is a mineral-exploration field-services contractor (claim staking, camp ops, drilling support, reclamation), not itself a producing mining/materials company. No named individual contact located, only a general info@ email. Distinct from 'Fox Tungsten Ltd' (formerly Happy Creek Minerals) — watch for naming confusion.</t>
         </is>
       </c>
     </row>
@@ -11569,6 +11824,11 @@
       <c r="C170" t="n">
         <v>3.09</v>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>3123-595 Burrard Street</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11584,9 +11844,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>fuse-advisors.com</t>
+        </is>
+      </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; slrconsulting.com press release, ised-isde.canada.ca (Investment Canada Act notice)</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -11596,7 +11861,12 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (slrconsulting.com press release, ised-isde.canada.ca (Investment Canada Act notice)); REVIEW: acquired by SLR Consulting (Canada) Ltd, deal finalized Oct 31, 2025; now operates as SLR's 'Vancouver (Fuse Advisors)' office, not independent. Also a mining/process-engineering consulting firm, not an operating mining company — likely misclassified regardless of the acquisition.</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11901,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; listcorp.com, tipranks.com</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -11641,7 +11911,12 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (listcorp.com, tipranks.com); REVIEW: a Canadian subsidiary of ASX-listed Atrum Coal Limited (Australia) holding the Groundhog anthracite project, BC — not an independently operating company. A sale of this subsidiary (and Atrum Coal Panorama Inc) to Panorama Resources Pty Ltd was signed Aug 19, 2025, staged payments tied to permitting/production milestones. No separate registered office or contact found distinct from the Australian parent.</t>
         </is>
       </c>
     </row>
@@ -11659,6 +11934,11 @@
       <c r="C172" t="n">
         <v>3.06</v>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1111 West Hastings Street</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11674,9 +11954,34 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Ewan Webster; Kettina Cordero</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>President, CEO &amp; Director; VP Investor Relations</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Kettinac@thesisgold.com</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>604-417-2574</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>www.thesisgold.com</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -11686,7 +11991,12 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked)); REVIEW: this specific 'Holdings' subsidiary vehicle amalgamated vertically into parent Thesis Gold Inc in March 2025, ceasing to exist as a separate entity. The successor/parent later renamed to 'Thesis Gold &amp; Silver Inc' (per search results, ~Feb 2026) following a merger involving Centerra Gold/Benchmark. Contact above is for the surviving operating company at the same Vancouver office.</t>
         </is>
       </c>
     </row>
@@ -11704,6 +12014,11 @@
       <c r="C173" t="n">
         <v>3.06</v>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1400-1125 Howe Street</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11714,14 +12029,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>V6Z 2K8</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Dwayne Yaretz</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>info@natitanium.com</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>778-709-3396</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>natitanium.com</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; natitanium.com/contact (search-indexed, direct fetch blocked), proactiveinvestors.com</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -11731,7 +12076,12 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (natitanium.com/contact (search-indexed, direct fetch blocked), proactiveinvestors.com); Active, independent (CSE:NATO/OTC:NATQF). Formerly Muzhu Mining Ltd; renamed North Atlantic Titanium Corp January 2026. Primary project (Everett titanium deposit) is in Quebec, not BC, though head office is Vancouver.</t>
         </is>
       </c>
     </row>
@@ -11749,6 +12099,11 @@
       <c r="C174" t="n">
         <v>3.06</v>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1100-1111 Melville Street</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11759,14 +12114,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>V6E 3V6</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>John Karagiannidis</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>info@qimaterials.com</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>514-726-7058</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>www.qimaterials.com</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png</t>
+          <t>chat-listing-2026-08-10-03.png; qimaterials.com, issuers.thecse.com (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -11776,7 +12161,12 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (qimaterials.com, issuers.thecse.com (search-indexed, direct fetch blocked)); Active, independent (CSE:QIMC). Formerly Quebec Silica Resources Corp; renamed January 2023. Also has a Montreal office (2303 rue Guenette) with a separate phone. Projects (hydrogen, silica) are in Quebec/Ontario/Nova Scotia/Minnesota, not BC, though registered head office is Vancouver.</t>
         </is>
       </c>
     </row>
@@ -11794,6 +12184,11 @@
       <c r="C175" t="n">
         <v>3.06</v>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>804-750 West Pender Street</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -11804,14 +12199,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>V6C 2T7</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>info@canamexgold.com</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>604-833-4278</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>canamexgold.com</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; canamexgold.com/contacts (search-indexed, direct fetch blocked), thecse.com listing</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -11821,7 +12236,12 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (canamexgold.com/contacts (search-indexed, direct fetch blocked), thecse.com listing); Active, independent (CSE:CSQ/OTC:CNMXF). Formerly Canamex Resources Corp; renamed November 2017. Flagship projects (Bruner, Nevada; Aranka North, Guyana) are outside BC. No named individual contact located, only a general info@ email.</t>
         </is>
       </c>
     </row>
@@ -11854,9 +12274,14 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>ashmont.ca</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; search-indexed content from ashmont.ca (direct fetch blocked)</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -11866,7 +12291,12 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-indexed content from ashmont.ca (direct fetch blocked)); Appears active, private BC company focused on gold exploration/development in Colombia. Street address could not be reliably parsed from search snippets and was not recorded to avoid guessing. No contact email/phone located; excluded data-broker results per hard rules.</t>
         </is>
       </c>
     </row>
@@ -11901,7 +12331,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; SEC EDGAR filings, goldseiten.de/accessnewswire.com, Yahoo Finance</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -11911,7 +12341,12 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>REVIEW: changed name to Scandium International Mining Corp (TSX:SCY) effective November 2014; head office relocated to Reno, Nevada. No longer a Vancouver-based entity under this name; not a live Vancouver prospect.</t>
         </is>
       </c>
     </row>
@@ -12004,9 +12439,24 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Behrouz R. Hemami</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Managing Director / sole shareholder</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>bmhoilfield.com</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; search-indexed content from bmhoilfield.com (direct fetch blocked)</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -12016,7 +12466,12 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search-indexed content from bmhoilfield.com (direct fetch blocked)); REVIEW: small active company, Vancouver HQ with UAE/Iraq branch operations — an oilfield services/consulting/contracting firm, likely misclassified under a mining/materials NAICS code. Street address/email/phone appeared only mixed with data-broker (RocketReach) results, excluded per hard rules.</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12506,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; GlobeNewswire archive (2006 release only)</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -12061,7 +12516,12 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>REVIEW: formerly Irwin Energy Inc, renamed Irwin Resources Inc in 2006. No trace of activity, website, or corporate record found after ~2007; likely dormant/inactive shell. Not to be confused with the unrelated, currently active Irving Resources Inc (also Vancouver-based, ticker IRV).</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12556,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; no public record located</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -12106,7 +12566,12 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>REVIEW: no company by this name could be located as a distinct current entity; search returned only unrelated similarly-named firms. Likely dormant/very small shell or defunct listing.</t>
         </is>
       </c>
     </row>
@@ -12124,6 +12589,11 @@
       <c r="C182" t="n">
         <v>2.86</v>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2500-666 Burrard Street</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12134,14 +12604,39 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>V6C 2X8</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Chris Hilliard</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>info@northernprincelng.com</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>northernprincelng.com</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; northernprincelng.com/contact-1 (search-indexed, direct fetch blocked); Canada Energy Regulator REGDOCS filing C29880; canadacompanyregistry.com (address, lower confidence)</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -12151,7 +12646,12 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (northernprincelng.com/contact-1 (search-indexed, direct fetch blocked); Canada Energy Regulator REGDOCS filing C29880; canadacompanyregistry.com (address, lower confidence)); REVIEW: possible sector misclassification — active LNG export-development company (holds a CER export permit), not mining/materials. Street address from a corporate-registry aggregator, not confirmed directly on the official site. Personal contact details for the CEO surfaced only via data brokers and were excluded per hard rules.</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12746,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; GlobeNewswire press releases (2018-02-15, 2018-02-28)</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -12256,7 +12756,12 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by GFG Resources Inc via plan of arrangement, completed Feb 28, 2018 (Pen Gold Project near Timmins, ON). Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12796,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; kootenaysilver.com archived releases, MarketScreener/Junior Mining Network coverage</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -12301,7 +12806,12 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>REVIEW: renamed Northair Silver Corp in November 2014 (same legal entity, TSXV: INM), then acquired by Kootenay Silver Inc via completed business combination April 21, 2016, becoming a wholly-owned subsidiary. Not a live independent prospect — route to Kootenay Silver Inc if pursuing. No contact info recorded here since Kootenay's own contact info would not independently verify to this specific former entity.</t>
         </is>
       </c>
     </row>
@@ -12319,6 +12829,11 @@
       <c r="C186" t="n">
         <v>2.8</v>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2133-1177 West Hastings Street</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12329,14 +12844,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>V6E 2K3</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Dr. Jaap (Jacob) Verbaas, P.Geo</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>CEO and Director</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>info@miatametals.com</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>778-486-1500</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>miatametals.com</t>
+        </is>
+      </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; miatametals.com/contact and /corporate (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -12346,7 +12891,12 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (miatametals.com/contact and /corporate (search-indexed, direct fetch blocked)); Active, independent junior gold explorer (Sela Creek and Nassau gold projects, Suriname), incorporated 2021, trades TSXV/CSE/OTCQX under MMET.</t>
         </is>
       </c>
     </row>
@@ -12364,6 +12914,11 @@
       <c r="C187" t="n">
         <v>2.8</v>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2500-700 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12379,9 +12934,34 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Paul Durham</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>VP, Corporate Development</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>paul.durham@gemdale.eu</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>+1 203-940-2538</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>gemdalegold.com</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; gemdalegold.com/corporate/corporate-directory (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -12391,7 +12971,12 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (gemdalegold.com/corporate/corporate-directory (search-indexed, direct fetch blocked)); Active, independent, recently-listed junior explorer (Pontio Gold Project, Finland; received a C$2.4M strategic investment from Eldorado Gold), commenced TSXV trading Feb 11, 2026. Postal code not recorded — search-indexed snippet rendered an implausible code, likely a parsing artifact. Alternate contact: Executive Chairman Patrick Chidley, Patrick.chidley@gemdale.eu, +1 917-991-7701.</t>
         </is>
       </c>
     </row>
@@ -12426,7 +13011,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; globenewswire.com press release, osc.ca order, SEC EDGAR 20-F (historical)</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
@@ -12436,7 +13021,12 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Argonaut Gold Inc via plan of arrangement completed Jan 27, 2011 (~$137M deal). Not a live independent prospect. Historical pre-2011 office was 789 West Pender St, Vancouver — not recorded as current since it's a defunct address.</t>
         </is>
       </c>
     </row>
@@ -12454,6 +13044,11 @@
       <c r="C189" t="n">
         <v>2.68</v>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>500-666 Burrard Street</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12464,14 +13059,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>V6C 3P6</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Garth Johnson</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>info@pulseoilcorp.com</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>604-909-1152</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>www.pulseoilcorp.com</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-04.png</t>
+          <t>chat-listing-2026-08-10-04.png; globenewswire.com (Oct 2024 AGM release), pulseoilcorp.com/contact (search-indexed, direct fetch blocked), theglobeandmail.com</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
@@ -12481,7 +13106,12 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (globenewswire.com (Oct 2024 AGM release), pulseoilcorp.com/contact (search-indexed, direct fetch blocked), theglobeandmail.com); REVIEW: likely misclassified — TSXV-listed (PUL) oil &amp; gas exploration/production company (Alberta assets), not mining/materials. Recommend a human spot-check of the official site before outreach since it could not be independently fetched.</t>
         </is>
       </c>
     </row>
@@ -12516,7 +13146,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; en.wikipedia.org/wiki/Offsetters</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -12526,7 +13156,12 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (en.wikipedia.org/wiki/Offsetters); REVIEW: not live under this name — rebranded to NatureBank Asset Management Inc in 2015, subsequently absorbed into Ostrom Climate Solutions Inc (brand 'Ostrom Climate'). Also misclassified for a mining/materials list — a carbon-offset/GHG-consulting firm. Address candidates found only via LinkedIn-indexed listings; excluded per hard rule against using LinkedIn data.</t>
         </is>
       </c>
     </row>
@@ -12544,6 +13179,11 @@
       <c r="C191" t="n">
         <v>2.57</v>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1000-355 Burrard Street</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12554,14 +13194,44 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>V6C 2G8</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Allen D. Leschert; Malcolm Fraser</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer; President (interim CFO)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>info@esreyresources.com</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>604-925-5136</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>esreyresources.com</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; esreyresources.com/corporate-2 (search-indexed, direct fetch blocked), globenewswire.com (Feb 2020 management-change release), advfn.com</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -12571,7 +13241,12 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (esreyresources.com/corporate-2 (search-indexed, direct fetch blocked), globenewswire.com (Feb 2020 management-change release), advfn.com); REVIEW: likely dormant — trading halted by IIROC Feb 4, 2020 following a 2019 BCSC cease-trade order; no news or filings found after early 2020. Named principals are from the last located announcement (Feb 2020) and not confirmed as still current.</t>
         </is>
       </c>
     </row>
@@ -12714,6 +13389,11 @@
       <c r="C194" t="n">
         <v>2.52</v>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>1107-750 West Pender Street</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12724,14 +13404,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>V6C 2T8</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>info@geosciencebc.com</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>604-662-4147</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>www.geosciencebc.com</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; geosciencebc.com/contactus and /about-us (search-indexed, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
@@ -12741,7 +13441,12 @@
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (geosciencebc.com/contactus and /about-us (search-indexed, direct fetch blocked)); Not a mining company — a not-for-profit society that manages and co-funds independent geoscience research in BC with industry/government/community/Indigenous partners. Appears active. No named individual contact located.</t>
         </is>
       </c>
     </row>
@@ -12759,6 +13464,11 @@
       <c r="C195" t="n">
         <v>2.45</v>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>510-1190 Melville Street</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12769,14 +13479,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>V6E 3W1</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Graeme Rowland</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Chairman, President &amp; CEO, Director</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; marketwired.com press release, miningfeeds.com (secondary directory, address corroboration)</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -12786,7 +13511,12 @@
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (marketwired.com press release, miningfeeds.com (secondary directory, address corroboration)); REVIEW: likely dormant/inactive shell — TSXV:ADT junior mineral-exploration company (antimony/multi-metal, Ontario &amp; Italy), distinct from an unrelated California IT-staffing firm of the same name. Its own domain (adroitresources.ca) no longer resolves. Last substantive press coverage circa 2012-2016; no current filings found.</t>
         </is>
       </c>
     </row>
@@ -12821,7 +13551,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; seabridgegold.com press release, juniorminingnetwork.com</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -12831,7 +13561,12 @@
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Seabridge Gold Inc via plan of arrangement, completed June 21, 2016 (KSM copper-gold project interest). Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -12866,7 +13601,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; lexpert.ca, en.wikipedia.org/wiki/Fission_Uranium_Corp.</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -12876,7 +13611,12 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>REVIEW: acquired by Fission Uranium Corp via plan of arrangement, shareholder-approved November 2013 (~$168-189M deal, 50% Patterson Lake South JV interest). Non-PLS assets spun off into Alpha Exploration Inc. Not a live independent prospect under the original name.</t>
         </is>
       </c>
     </row>
@@ -12911,7 +13651,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; stale historical press releases (circa 2007, EQS News/ProQuest archive)</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -12921,7 +13661,12 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (stale historical press releases (circa 2007, EQS News/ProQuest archive)); REVIEW: TSXV:MXA, Guerrero Gold Belt (Mexico) explorer. All located material dates to ~2007; no evidence of continued operations, name change, or formal wind-down found. Likely dormant/defunct pending manual registry check.</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13701,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; fasken.com, angloamerican.com press release (2025-11-02)</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -12966,7 +13711,12 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (fasken.com, angloamerican.com press release (2025-11-02)); REVIEW: wholly-owned indirect subsidiary of Anglo American plc; co-formed Peace River Coal Limited Partnership (2006) with NEMI and Hillsborough Resources. Anglo American later took full ownership and, per its own Nov 2, 2025 release, has since sold the Peace River Coal operations to Conuma Resources Limited. Not a live standalone prospect.</t>
         </is>
       </c>
     </row>
@@ -12984,6 +13734,11 @@
       <c r="C200" t="n">
         <v>2.33</v>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>250-200 Burrard Street</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -12994,14 +13749,34 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>V6C 3L6</t>
+        </is>
+      </c>
       <c r="H200" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Janet Lee-Sheriff</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>www.goldenpredator.com</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; whitehorsechamber.ca, cambridgehouse.com, yellowpages.ca, globenewswire.com (2016 CFO appointment release)</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -13011,7 +13786,12 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (whitehorsechamber.ca, cambridgehouse.com, yellowpages.ca, globenewswire.com (2016 CFO appointment release)); Now trades as Golden Predator Mining Corp. Official site (goldenpredator.com) was unreachable in this session, so address could not be independently verified on the company's own site. No 2026 activity confirmed. contact_email/phone left blank — one summarized result rendered an email as a spam-obfuscation placeholder. Recommend manual re-check once the site is reachable.</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13826,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; sec.gov EDGAR filings, pitchbook.com</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -13056,7 +13836,12 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (sec.gov EDGAR filings, pitchbook.com); REVIEW: underwent a 2010 reverse takeover — Gold Standard Ventures Corp issued shares to JKR's shareholders, making JKR a subsidiary. Gold Standard Ventures Corp was itself acquired by Orla Mining in 2022. No independent Vancouver office or contact found since 2010; stale historic entity.</t>
         </is>
       </c>
     </row>
@@ -13074,6 +13859,11 @@
       <c r="C202" t="n">
         <v>2.33</v>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>900-570 Granville Street</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13084,14 +13874,29 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>V6C 3P1</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>604-682-3701</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>www.coralgold.com</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; sec.gov EDGAR Form 20-F (pre-acquisition), newswire.ca press release</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
@@ -13101,7 +13906,12 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (sec.gov EDGAR Form 20-F (pre-acquisition), newswire.ca press release); REVIEW: acquired by Nomad Royalty Company in 2020 (~$45.8M deal); Nomad itself later merged with Trident Royalties (2023) to become Elemental Altus Royalties. Address/phone are from Coral's own pre-acquisition SEC filing, not verified as current. Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -13119,6 +13929,11 @@
       <c r="C203" t="n">
         <v>2.33</v>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>810-789 West Pender Street</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13129,14 +13944,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>V6C 1H2</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>www.bearinglithium.com</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; globenewswire.com press releases (Dec 2022)</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
@@ -13146,7 +13971,12 @@
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (globenewswire.com press releases (Dec 2022)); REVIEW: acquired via plan of arrangement by a subsidiary of Lithium Power International Limited (ASX-listed, Australia), December 2022; Bearing ceased to exist independently. Route future outreach to Lithium Power International, not Bearing.</t>
         </is>
       </c>
     </row>
@@ -13164,6 +13994,11 @@
       <c r="C204" t="n">
         <v>2.33</v>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>501-570 Granville Street</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -13174,14 +14009,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>V6C 3P1</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>goldsourcemines.com</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; newsfilecorp.com press release, goldsourcemines.com/corporate/corporate-info (search-cached, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -13191,7 +14036,12 @@
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (newsfilecorp.com press release, goldsourcemines.com/corporate/corporate-info (search-cached, direct fetch blocked)); REVIEW: acquired by Mako Mining Corp, completed July 3, 2024. Not a live independent prospect — route future outreach to Mako Mining Corp instead.</t>
         </is>
       </c>
     </row>
@@ -13226,7 +14076,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-05.png</t>
+          <t>chat-listing-2026-08-10-05.png; biv.com, rttnews.com</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
@@ -13236,7 +14086,12 @@
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (biv.com, rttnews.com); REVIEW: acquired by Fortuna Silver Mines Inc (now Fortuna Mining Corp), closed March 6, 2009 (100% ownership of the San Jose silver/gold project, Oaxaca, Mexico). Dissolved into acquirer well over a decade ago; not a live prospect.</t>
         </is>
       </c>
     </row>
@@ -14686,7 +15541,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png</t>
+          <t>chat-listing-2026-08-10-08.png; search summary (Mitsubishi Corporation / Penn West Cordova Embayment JV reporting, 2010-2011)</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -14696,7 +15551,12 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (search summary (Mitsubishi Corporation / Penn West Cordova Embayment JV reporting, 2010-2011)); REVIEW: misclassified — this is 'Cordova Gas Resources Ltd', a shale-gas project JV subsidiary tied to Penn West Petroleum's Cordova Embayment assets in northeastern BC (oil &amp; gas, not mining). Chubu Electric Power, with Tokyo Gas and Osaka Gas via Mitsubishi Corporation, acquired a minority (~7.5%) JV stake around 2010-2011. No independent Vancouver head office or contact found; not a standalone prospect.</t>
         </is>
       </c>
     </row>
@@ -15521,7 +16381,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-09.png</t>
+          <t>chat-listing-2026-08-10-09.png; biv.com, globenewswire.com (May 2015 release)</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -15531,7 +16391,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>detail_only</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (biv.com, globenewswire.com (May 2015 release)); REVIEW: acquired by Timmins Gold Corp, completed May 26, 2015 (~$140M deal; Ana Paula and Ejutla projects, Mexico). Combined company later renamed Alio Gold, which merged with Argonaut Gold in 2020. Not a live independent prospect.</t>
         </is>
       </c>
     </row>
@@ -16484,6 +17349,11 @@
       <c r="C264" t="n">
         <v>2.04</v>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>1501-128 West Pender Street</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -16494,14 +17364,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>V6B 1R8</t>
+        </is>
+      </c>
       <c r="H264" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>globalcobaltcorp.com</t>
+        </is>
+      </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; juniorminingnetwork.com press release, globalcobaltcorp.com (search-cached, direct fetch blocked)</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -16511,7 +17391,12 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (juniorminingnetwork.com press release, globalcobaltcorp.com (search-cached, direct fetch blocked)); REVIEW: likely dormant shell — completed a spin-out of Global Energy Metals Corporation in January 2016 (Karakul Cobalt Deposit, Russia); no activity located after ~2016. Conflicting historic addresses found; the one given is most frequently cited but not independently verified via the company's own site.</t>
         </is>
       </c>
     </row>
@@ -16629,6 +17514,11 @@
       <c r="C267" t="n">
         <v>2.04</v>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>1890-1075 West Georgia Street</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>Vancouver</t>
@@ -16639,14 +17529,24 @@
           <t>British Columbia</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>V6E 3C9</t>
+        </is>
+      </c>
       <c r="H267" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>604-687-2038</t>
+        </is>
+      </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-11.png</t>
+          <t>chat-listing-2026-08-10-11.png; thenewswire.com, bcsc.bc.ca reporting-issuers list, globenewswire.com (name-change release, April 2024)</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -16656,7 +17556,12 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>listing_only</t>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>CONFLICT: province=British Columbia|BC (thenewswire.com, bcsc.bc.ca reporting-issuers list, globenewswire.com (name-change release, April 2024)); Formerly Major Precious Metals Corp, renamed Intrusion Precious Metals Corp effective May 2, 2024. Focused on the Skaergaard Project (palladium/gold), eastern Greenland. Sources conflict on exchange-listing status (one says unlisted, others reference NEO ticker SIZE) — not resolved, flag for confirmation. No official website confirmed reachable in this session; address/phone are third-party-sourced (news release/BCSC filing).</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$U$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U312"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-08.png; no public record located</t>
+          <t>chat-listing-2026-08-10-08.png; no public record located; chat-listing-2026-08-10-16.png</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>detail_only</t>
+          <t>listing_only</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.</t>
+          <t>REVIEW: no official website, news coverage, or financial-database listing could be located. Recommend manual verification via BC Registry before treating as a live prospect.; CONFLICT: revenue_raw=$5.14M|$1.84M (chat-listing-2026-08-10-16.png); CONFLICT: revenue_usd_millions=5.14|1.84 (chat-listing-2026-08-10-16.png)</t>
         </is>
       </c>
     </row>
@@ -19985,8 +19985,2178 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Global Met Coal Corporation</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Inca One Metals Corp</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>TAD Mineral Exploration Inc</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Curis Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Carolyn River Projects Ltd</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Kit Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Columbia Yukon Explorations Inc</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Lithium X Energy Corp</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Us Cobalt Inc</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Frontera Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Abraham Wong Lim Strategic Developments Inc.</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Wellgreen Platinum Ltd.</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Corex Gold Corporation</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Northern Iron Corp.</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Imbera Gold Corp</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Alamos Minerals Ltd.</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>$1.46M</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-15.png</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Cangold Limited</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Rizal Resources Corporation</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>$2.04M</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Kenorland Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>$2.03M</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Coloured Ties Capital Inc</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>$1.89M</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Arbios Biotech Canada (GP1) Ltd</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>$1.89M</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Canadian Kailuan Dehua Mines Co., Ltd</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>$1.88M</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Pacton Gold Inc</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>$1.87M</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Anfield Gold Corp</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>$1.87M</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Lateegra Gold Corp</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>$1.87M</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Ram River Coal Corp</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>$1.84M</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Reyna Silver Mining Inc</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>$1.84M</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>La Imperial Resources Inc</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>$1.84M</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Blue River Resources Ltd</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>$1.84M</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Arcturus Ventures Inc</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>$1.84M</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Computational Geosciences Inc</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>$1.72M</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-16.png</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>This company also appears in a second overlapping screenshot at a slightly different revenue figure ($1.63M) — treated as the same company (duplicate D&amp;B listing capture), not two entities; recording the higher of the two figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Black Tusk Geophysics Inc.</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>$1.68M</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Sedgman Canada Limited</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Granja Gold Inc</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Remo Resources Inc</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1040433 B.C. Ltd</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>First Nevada Mining Corp</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>North Vancouver</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Rift Basin Resources Corp</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>High Ridge Resources Inc</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>International Kodiak Resources Inc</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Dolly Verdon Resources Inc</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>$1.67M</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Consolidated Woodjam Copper Corp</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Osprey Gold Development Ltd</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Quest Mortgage Corp</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>REVIEW: likely misclassified — name indicates a mortgage/lending company, not mining/materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Aegean Metals Group Inc</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>American Pacific Mining Corp</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-17.png</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Revolve Renewable American Inc</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-18.png</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Argentex Mining Corporation</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>$1.63M</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>chat-listing-2026-08-10-18.png</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U312"/>
+  <autoFilter ref="A1:U360"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -11979,9 +11979,19 @@
           <t>www.thesisgold.com</t>
         </is>
       </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>expansion/new project: positive Prefeasibility Study for the Lawyers-Ranch gold-silver project — after-tax NPV5% of C$2.37 billion, 54.4% after-tax IRR, 15-year mine life, 1.1-year payback, completed by Ausenco (2025-12-01, NI 43-101 technical report filed on SEDAR+ 2026-01-14); management change: Coille van Alphen appointed to the Board of Directors (2026-01-21); IPO/listing change: renamed from Thesis Gold Inc to Thesis Gold &amp; Silver Inc, trading as TSXV:TAU (2026-02-06); capital raise: closed C$44.4 million strategic equity financing — AngloGold Ashanti took a 5.0% stake via 13,858,883 shares at C$2.79 and Centerra Gold exercised participation rights for 2,059,730 shares at C$2.79 to maintain its 9.9% position. AngloGold also received investor rights including technical committee participation (2026-02-26); expansion/new project: commenced 2026 exploration and project advancement programs at Lawyers-Ranch with approximately 20,000 metres of drilling planned (12,000 m exploration at Ranch/Ranch East plus 8,000 m geotechnical, hydrogeological, metallurgical and geochemical), targeting completion of a Feasibility Study before the end of 2027 (2026-06-17)</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/thesis-gold-announces-positive-prefeasibility-study-for-lawyers-ranch-project-after-tax-npv5-of-2-37-billion-and-54-4-irr-302628748.html; https://www.thesisgoldsilver.com/news-media/news/; https://www.barchart.com/story/news/251894/thesis-gold-rebrands-to-thesis-gold-silver; https://investingnews.com/thesis-gold-silver-closes-strategic-investment-by-anglogold-ashanti-and-participation-by-centerra-gold-for-c-44m/; https://www.prnewswire.com/news-releases/thesis-gold--silver-commences-2026-exploration-and-project-advancement-programs-at-lawyers-ranch-project-302802660.html</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-10-03.png; newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked)</t>
+          <t>chat-listing-2026-08-10-03.png; newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked); stage-3 news search (prnewswire.com, investingnews.com, barchart.com, newsfilecorp.com, miningnewsnorth.com, mining.com; direct fetches blocked in this environment so items are sourced from search-indexed press-release content)</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -11996,7 +12006,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>CONFLICT: province=British Columbia|BC (newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked)); REVIEW: this specific 'Holdings' subsidiary vehicle amalgamated vertically into parent Thesis Gold Inc in March 2025, ceasing to exist as a separate entity. The successor/parent later renamed to 'Thesis Gold &amp; Silver Inc' (per search results, ~Feb 2026) following a merger involving Centerra Gold/Benchmark. Contact above is for the surviving operating company at the same Vancouver office.</t>
+          <t>CONFLICT: province=British Columbia|BC (newswire.ca press release, thesisgold.com/contact (search-indexed, direct fetch blocked)); REVIEW: this specific 'Holdings' subsidiary vehicle amalgamated vertically into parent Thesis Gold Inc in March 2025, ceasing to exist as a separate entity. The successor/parent later renamed to 'Thesis Gold &amp; Silver Inc' (per search results, ~Feb 2026) following a merger involving Centerra Gold/Benchmark. Contact above is for the surviving operating company at the same Vancouver office.; CORRECTION to the batch-25 REVIEW note on this row: the corporate history recorded there was partly wrong. Accurate sequence is (1) 2023-08-23 Benchmark Metals Inc completed a court-approved plan of arrangement with Thesis Gold (Holdings) Inc and renamed itself Thesis Gold Inc, with Holdings becoming a subsidiary (Benchmark/Thesis shareholders held ~60/40 of the combined company); (2) March 2025 vertical short-form amalgamation dissolved the Holdings subsidiary into the parent; (3) 2026-02-06 the parent renamed to Thesis Gold &amp; Silver Inc. Centerra Gold was never a merger counterparty — it is an equity investor only, so the batch-25 phrase 'a merger involving Centerra Gold/Benchmark' should be disregarded. OUTSIDE the 12-month window but relevant context: Centerra Gold's initial 9.9% investment of C$24.2 million at C$1.03/share was announced 2025-04-22 and closed ~2025-04-28 — deliberately not recorded in recent_news since it predates the lookback cutoff. Note on sourcing: the Coille van Alphen board appointment is carried against the company's own news index rather than a direct press-release URL, the only source located for it. CRE READ: this is now one of the stronger prospects in the workbook — explorer transitioning to developer, C$44.4M freshly raised on top of the 2025 Centerra placement, two major-miner backers (AngloGold Ashanti, Centerra Gold), a PFS showing a C$2.37B NPV, and a Feasibility Study targeted for end-2027. That trajectory usually drives corporate headcount growth (office) plus procurement, laydown and warehousing needs. Caveat for industrial targeting: the Lawyers-Ranch project sits in the Toodoggone district roughly 300 km north of Smithers, so mine-site logistics would not be Lower Mainland industrial demand — any Vancouver-area requirement would be corporate office at 1111 West Hastings and possibly Prince George or Lower Mainland procurement/staging space rather than the project footprint itself.</t>
         </is>
       </c>
     </row>

--- a/output/mining_master.xlsx
+++ b/output/mining_master.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$1:$Y$362</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'People'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'People'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Aris Mining Corporation [same building only]; Aris Mining Holdings Corp [same building only]; Mcilvenna Bay Operating Ltd [same building only]</t>
+          <t>Aris Mining Corporation [same building only]; Aris Mining Holdings Corp [same building only]; Mcilvenna Bay Operating Ltd [same suite]</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Hunter Dickinson Acquisition Inc [same building only]; Hunter Dickinson Inc [same building only]</t>
+          <t>Amarc Resources Ltd [same building only]; Hunter Dickinson Acquisition Inc [same building only]; Hunter Dickinson Inc [same building only]; Northern Dynasty Minerals Ltd [same building only]</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/; stage-3 news check; alias registration for entity resolution (rename previously recorded in this workbook's notes)</t>
+          <t>chat-listing-2026-08-05-03.png; https://www.trekormetals.com/contact/; stage-3 news check; alias registration for entity resolution (rename previously recorded in this workbook's notes); https://www.tasekomines.com/about/board-of-directors/ (fetched directly, HTTP 200)</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.; This confirms and dates the Taseko-to-Trekor rename already noted in an earlier contact-verification batch.; Former names registered so staging entries naming the pre-rename entity resolve to this row instead of creating a duplicate.</t>
+          <t>Confirmed via official site: Trekor Metals Limited is a recent corporate rename of Taseko Mines Limited (same company, same Gibraltar/Florence Copper assets) — not a distinct new entity, but still an active, independent, currently operating company. General public email used; no named individual confirmed on the official contact page.; This confirms and dates the Taseko-to-Trekor rename already noted in an earlier contact-verification batch.; Former names registered so staging entries naming the pre-rename entity resolve to this row instead of creating a duplicate.; Rename to Trekor Metals CONFIRMED against the live site: tasekomines.com now serves pages titled 'Trekor Metals' and references trekormetals.com. The former_names alias on this row is correct.</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Aris Mining Corporation [same building only]; Aris Mining Holdings Corp [same building only]; Eldorado Gold Corporation [same building only]</t>
+          <t>Aris Mining Corporation [same building only]; Aris Mining Holdings Corp [same building only]; Eldorado Gold Corporation [same suite]</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Hunter Dickinson Acquisition Inc [same family]; Trekor Metals Limited [same building only]</t>
+          <t>Amarc Resources Ltd [same building only]; Hunter Dickinson Acquisition Inc [same family]; Northern Dynasty Minerals Ltd [same building only]; Trekor Metals Limited [same building only]</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>Northern Dynasty Minerals Ltd (via Bruce Jenkins, officer, tier2_website); Northern Dynasty Minerals Ltd (via Mark Peters, officer, tier2_website); Northern Dynasty Minerals Ltd (via Trevor Thomas, officer, tier2_website)</t>
+          <t>Amarc Resources Ltd (via Scott Cousens, director, tier2_website); Northern Dynasty Minerals Ltd (via Bruce Jenkins, officer, tier2_website); Northern Dynasty Minerals Ltd (via Mark Peters, officer, tier2_website); Northern Dynasty Minerals Ltd (via Trevor Thomas, officer, tier2_website)</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>Hunter Dickinson Inc [same family]; Trekor Metals Limited [same building only]</t>
+          <t>Amarc Resources Ltd [same suite]; Hunter Dickinson Inc [same family]; Northern Dynasty Minerals Ltd [same suite]; Trekor Metals Limited [same building only]</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -22597,11 +22597,51 @@
           <t>Northern Dynasty Minerals Ltd</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>14th Floor - 1040 West Georgia Street</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>V6E 4H1</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Ronald Thiessen</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>President, CEO and Director</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>northerndynastyminerals.com</t>
         </is>
       </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd [same suite]; Hunter Dickinson Acquisition Inc [same suite]; Hunter Dickinson Inc [same building only]; Trekor Metals Limited [same building only]</t>
+        </is>
+      </c>
       <c r="T361" t="inlineStr">
         <is>
           <t>Amarc Resources Ltd (via Robert Dickinson, officer, tier2_website); Hunter Dickinson Inc (via Bruce Jenkins, officer, tier2_website); Hunter Dickinson Inc (via Mark Peters, officer, tier2_website); Hunter Dickinson Inc (via Trevor Thomas, officer, tier2_website); Trekor Metals Limited (via Robert Dickinson, director, tier2_website); Trekor Metals Limited (via Ronald Thiessen, director, tier2_website)</t>
@@ -22614,7 +22654,7 @@
       </c>
       <c r="V361" t="inlineStr">
         <is>
-          <t>relationship-graph discovery (northerndynastyminerals.com management and board pages, search-indexed; direct fetch blocked in this environment)</t>
+          <t>relationship-graph discovery (northerndynastyminerals.com management and board pages, search-indexed; direct fetch blocked in this environment); https://northerndynastyminerals.com/about-us/company-information/ and /about-us/management/ (fetched directly, HTTP 200)</t>
         </is>
       </c>
       <c r="W361" t="inlineStr">
@@ -22629,7 +22669,7 @@
       </c>
       <c r="Y361" t="inlineStr">
         <is>
-          <t>DISCOVERED VIA RELATIONSHIP GRAPH, not the D&amp;B candidate list — surfaced through shared HDI officers. Vancouver-headquartered, holds the Pebble copper-gold project in Alaska. ILLEGIBLE: street_address, contact_email, contact_phone — not researched in this pilot, which was scoped to validating the people-graph method. Recommend a normal stage-2 contact pass before treating as an outreach-ready prospect.</t>
+          <t>DISCOVERED VIA RELATIONSHIP GRAPH, not the D&amp;B candidate list — surfaced through shared HDI officers. Vancouver-headquartered, holds the Pebble copper-gold project in Alaska. ILLEGIBLE: street_address, contact_email, contact_phone — not researched in this pilot, which was scoped to validating the people-graph method. Recommend a normal stage-2 contact pass before treating as an outreach-ready prospect.; Corporate Address per the company's own company-information page, fetched directly. Same floor as Amarc Resources and Hunter Dickinson Acquisition Inc, one floor below Hunter Dickinson Inc — the HDI management cluster at 1040 West Georgia.</t>
         </is>
       </c>
     </row>
@@ -22639,14 +22679,64 @@
           <t>Amarc Resources Ltd</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>14th Floor - 1040 West Georgia Street</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>V6E 4H1</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Dr. Diane Nicolson</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>604-684-6365</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>amarcresources.com</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Hunter Dickinson Acquisition Inc [same suite]; Hunter Dickinson Inc [same building only]; Northern Dynasty Minerals Ltd [same suite]; Trekor Metals Limited [same building only]</t>
+        </is>
+      </c>
       <c r="T362" t="inlineStr">
         <is>
-          <t>Northern Dynasty Minerals Ltd (via Robert Dickinson, director, tier2_website); Trekor Metals Limited (via Robert Dickinson, director, tier2_website)</t>
+          <t>Hunter Dickinson Inc (via Scott Cousens, officer, tier2_website); Northern Dynasty Minerals Ltd (via Robert Dickinson, director, tier2_website); Trekor Metals Limited (via Robert Dickinson, director, tier2_website)</t>
         </is>
       </c>
       <c r="V362" t="inlineStr">
         <is>
-          <t>relationship-graph discovery (search-indexed board/management references; direct fetch blocked in this environment)</t>
+          <t>relationship-graph discovery (search-indexed board/management references; direct fetch blocked in this environment); https://www.amarcresources.com/about-us/corporate-information/ and /about-us/management-directors/ (fetched directly, HTTP 200)</t>
         </is>
       </c>
       <c r="W362" t="inlineStr">
@@ -22661,7 +22751,7 @@
       </c>
       <c r="Y362" t="inlineStr">
         <is>
-          <t>DISCOVERED VIA RELATIONSHIP GRAPH, not the D&amp;B candidate list — surfaced through shared HDI principals. Vancouver-headquartered BC-focused explorer. ILLEGIBLE: street_address, contact_email, contact_phone — not researched in this pilot. Recommend a normal stage-2 contact pass before treating as an outreach-ready prospect.</t>
+          <t>DISCOVERED VIA RELATIONSHIP GRAPH, not the D&amp;B candidate list — surfaced through shared HDI principals. Vancouver-headquartered BC-focused explorer. ILLEGIBLE: street_address, contact_email, contact_phone — not researched in this pilot. Recommend a normal stage-2 contact pass before treating as an outreach-ready prospect.; Corporate Address and phone taken from the labelled 'Corporate Address' block, distinguished from the transfer agent (Computershare, 510 Burrard) and auditor (DeVisser Gray, 905 West Pender) addresses also on that page. NOTE: the phone number 604-684-6365 is identical to the one already recorded for Hunter Dickinson Inc — a shared switchboard, which is stronger evidence of a shared management company than a shared building is.</t>
         </is>
       </c>
     </row>
@@ -22677,7 +22767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23272,8 +23362,861 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ronald Thiessen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>President, CEO and Director</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Re-sourced from the live page, replacing the earlier search-snippet assertion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trevor Thomas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>General Counsel and Secretary</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CORRECTION: the pilot recorded this as 'Corporate Secretary' from a search snippet. The live page states 'General Counsel and Secretary'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bruce Jenkins</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Executive Vice President Environment and Sustainability</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CORRECTION: the pilot recorded a described function rather than a title because the snippet gave none. The live page gives a formal title, identical to his HDI title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Adam Chodos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Executive Vice President, Corporate Development</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stephen Hodgson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Vice President, Engineering</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mike Westerlund</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Northern Dynasty Minerals Ltd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Executive Vice President, Investor Relations</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://northerndynastyminerals.com/about-us/management/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dr. Diane Nicolson</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Carol Li</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Published as 'Carol Li, CPA, CGA'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gavin Titley</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vice President, Exploration</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Published as 'Gavin Titley, P.Geo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tom McMillan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vice President, Investor Relations</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Robert Dickinson</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>CORRECTION to the pilot's 'Executive Chairman since 2004'. The live page says 'As Chair of Amarc' and states he 'serves as both director and as part of the management for a number of public companies associated with Hunter Dickinson Inc' — which supports role_type 'both' but not the specific title or start year previously asserted, so both were dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Scott Cousens</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NEW cross-link found on re-sourcing: the same bio states he was Director Capital Finance for Hunter Dickinson Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Scott Cousens</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hunter Dickinson Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Director Capital Finance</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>officer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>director biography on an affiliated company page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Asserted from an Amarc bio rather than an HDI page — HDI's own site (hdimining.com, titled 'HDSI') returned 404 for its team page. Lower-grade provenance for an HDI role; re-verify against an HDI source or a circular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Barry Coughlan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Amarc Resources Ltd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>company management page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.amarcresources.com/about-us/management-directors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ronald W. Thiessen</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chairman of the Board</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>company board page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.tasekomines.com/about/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Published with a middle initial here and without one at Northern Dynasty. Same person, but normalize_person deliberately does not merge across a differing middle initial — this is a known limitation and needs a circular or insider ID to resolve properly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Robert A. Dickinson</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>company board page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.tasekomines.com/about/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Middle-initial variant of the Robert Dickinson recorded at Amarc and Northern Dynasty. Same caveat as Thiessen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Stuart McDonald</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>President, CEO &amp; Director</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>company board page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.tasekomines.com/about/board-of-directors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Russell Hallbauer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>company board page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.tasekomines.com/about/board-of-directors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kenneth Pickering</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Trekor Metals Limited</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>tier2_website</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>company board page (fetched directly)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.tasekomines.com/about/board-of-directors/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>